--- a/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA066B3-29FF-4F0C-A074-4DA3640DAA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -237,8 +243,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,13 +307,1566 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Pecepatan</a:t>
+            </a:r>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.8650000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5612E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.69623E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.110197</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BDS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.352E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0061E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3339999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7858200000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.2789999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5832000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7669000000000011E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6599900000000004E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.2620000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0154000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.36829E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9039199999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.2739999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3472E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0197000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.15891E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.5029999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6337000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7054099999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1104907</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.2230000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4174999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.48261E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9208500000000005E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-58D9-46F3-98EA-032C686D8C63}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="480179391"/>
+        <c:axId val="470352431"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="480179391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="470352431"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="470352431"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="480179391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDED432-0F1B-A698-0F60-6FF65BA6E744}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -345,7 +1904,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -379,6 +1938,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -413,9 +1973,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,11 +2149,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +2176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -623,22 +2184,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0003865</v>
+        <v>3.8650000000000002E-4</v>
       </c>
       <c r="D2">
-        <v>0.0025612</v>
+        <v>2.5612E-3</v>
       </c>
       <c r="E2">
-        <v>0.0169623</v>
+        <v>1.69623E-2</v>
       </c>
       <c r="F2">
         <v>0.110197</v>
       </c>
       <c r="G2">
-        <v>0.03252674999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>3.2526749999999993E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -646,22 +2207,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0002352</v>
+        <v>2.352E-4</v>
       </c>
       <c r="D3">
-        <v>0.0010061</v>
+        <v>1.0061E-3</v>
       </c>
       <c r="E3">
-        <v>0.004333999999999999</v>
+        <v>4.3339999999999993E-3</v>
       </c>
       <c r="F3">
-        <v>0.0178582</v>
+        <v>1.7858200000000001E-2</v>
       </c>
       <c r="G3">
-        <v>0.005858374999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>5.858374999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -669,22 +2230,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0004279</v>
+        <v>4.2789999999999999E-4</v>
       </c>
       <c r="D4">
-        <v>0.0015832</v>
+        <v>1.5832000000000001E-3</v>
       </c>
       <c r="E4">
-        <v>0.008766900000000001</v>
+        <v>8.7669000000000011E-3</v>
       </c>
       <c r="F4">
-        <v>0.0665999</v>
+        <v>6.6599900000000004E-2</v>
       </c>
       <c r="G4">
-        <v>0.019344475</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1.9344475E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -692,22 +2253,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0003262</v>
+        <v>3.2620000000000001E-4</v>
       </c>
       <c r="D5">
-        <v>0.0020154</v>
+        <v>2.0154000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>0.0136829</v>
+        <v>1.36829E-2</v>
       </c>
       <c r="F5">
-        <v>0.0890392</v>
+        <v>8.9039199999999999E-2</v>
       </c>
       <c r="G5">
-        <v>0.026265925</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>2.6265924999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -715,22 +2276,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.0004274</v>
+        <v>4.2739999999999998E-4</v>
       </c>
       <c r="D6">
-        <v>0.0013472</v>
+        <v>1.3472E-3</v>
       </c>
       <c r="E6">
-        <v>0.0050197</v>
+        <v>5.0197000000000002E-3</v>
       </c>
       <c r="F6">
-        <v>0.0215891</v>
+        <v>2.15891E-2</v>
       </c>
       <c r="G6">
-        <v>0.00709585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>7.0958499999999999E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -738,22 +2299,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0004503</v>
+        <v>4.5029999999999999E-4</v>
       </c>
       <c r="D7">
-        <v>0.0026337</v>
+        <v>2.6337000000000001E-3</v>
       </c>
       <c r="E7">
-        <v>0.0170541</v>
+        <v>1.7054099999999999E-2</v>
       </c>
       <c r="F7">
         <v>0.1104907</v>
       </c>
       <c r="G7">
-        <v>0.0326572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>3.2657199999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -761,22 +2322,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0004223</v>
+        <v>4.2230000000000002E-4</v>
       </c>
       <c r="D8">
-        <v>0.0024175</v>
+        <v>2.4174999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>0.0148261</v>
+        <v>1.48261E-2</v>
       </c>
       <c r="F8">
-        <v>0.09920850000000001</v>
+        <v>9.9208500000000005E-2</v>
       </c>
       <c r="G8">
-        <v>0.0292186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>2.9218600000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -784,22 +2345,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.0003112999999999999</v>
+        <v>3.1129999999999992E-4</v>
       </c>
       <c r="D9">
-        <v>0.0011968</v>
+        <v>1.1968E-3</v>
       </c>
       <c r="E9">
-        <v>0.0046809</v>
+        <v>4.6809E-3</v>
       </c>
       <c r="F9">
-        <v>0.02167460000000001</v>
+        <v>2.1674600000000009E-2</v>
       </c>
       <c r="G9">
-        <v>0.006965900000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>6.9659000000000014E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,22 +2368,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0002051</v>
+        <v>2.051E-4</v>
       </c>
       <c r="D10">
-        <v>0.0008747</v>
+        <v>8.7469999999999996E-4</v>
       </c>
       <c r="E10">
-        <v>0.0040442</v>
+        <v>4.0442000000000004E-3</v>
       </c>
       <c r="F10">
-        <v>0.0174603</v>
+        <v>1.7460300000000002E-2</v>
       </c>
       <c r="G10">
-        <v>0.005646075</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>5.6460750000000004E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -830,22 +2391,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.0002812</v>
+        <v>2.812E-4</v>
       </c>
       <c r="D11">
-        <v>0.0011001</v>
+        <v>1.1000999999999999E-3</v>
       </c>
       <c r="E11">
-        <v>0.004535200000000001</v>
+        <v>4.5352000000000014E-3</v>
       </c>
       <c r="F11">
-        <v>0.0185876</v>
+        <v>1.8587599999999999E-2</v>
       </c>
       <c r="G11">
-        <v>0.006126025</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>6.1260250000000002E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -853,22 +2414,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0002506</v>
+        <v>2.5060000000000002E-4</v>
       </c>
       <c r="D12">
-        <v>0.0010769</v>
+        <v>1.0769E-3</v>
       </c>
       <c r="E12">
-        <v>0.0043631</v>
+        <v>4.3631E-3</v>
       </c>
       <c r="F12">
-        <v>0.0183709</v>
+        <v>1.8370899999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.006015375000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>6.0153750000000008E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -876,22 +2437,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0005059</v>
+        <v>5.0589999999999999E-4</v>
       </c>
       <c r="D13">
-        <v>0.0017123</v>
+        <v>1.7122999999999999E-3</v>
       </c>
       <c r="E13">
-        <v>0.0089468</v>
+        <v>8.9467999999999995E-3</v>
       </c>
       <c r="F13">
-        <v>0.06733910000000001</v>
+        <v>6.7339100000000013E-2</v>
       </c>
       <c r="G13">
-        <v>0.019626025</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1.9626024999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -899,22 +2460,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0004391</v>
+        <v>4.3909999999999999E-4</v>
       </c>
       <c r="D14">
-        <v>0.0023418</v>
+        <v>2.3417999999999998E-3</v>
       </c>
       <c r="E14">
-        <v>0.0101272</v>
+        <v>1.0127199999999999E-2</v>
       </c>
       <c r="F14">
-        <v>0.09568159999999999</v>
+        <v>9.5681599999999992E-2</v>
       </c>
       <c r="G14">
-        <v>0.027147425</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>2.7147424999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -922,22 +2483,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.000515</v>
+        <v>5.1500000000000005E-4</v>
       </c>
       <c r="D15">
-        <v>0.0018718</v>
+        <v>1.8718000000000001E-3</v>
       </c>
       <c r="E15">
-        <v>0.0105198</v>
+        <v>1.0519799999999999E-2</v>
       </c>
       <c r="F15">
-        <v>0.06781509999999999</v>
+        <v>6.7815099999999989E-2</v>
       </c>
       <c r="G15">
-        <v>0.020180425</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>2.0180424999999998E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -945,22 +2506,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0003872</v>
+        <v>3.8719999999999998E-4</v>
       </c>
       <c r="D16">
-        <v>0.0021209</v>
+        <v>2.1209000000000002E-3</v>
       </c>
       <c r="E16">
-        <v>0.0138365</v>
+        <v>1.38365E-2</v>
       </c>
       <c r="F16">
-        <v>0.09007970000000001</v>
+        <v>9.0079700000000013E-2</v>
       </c>
       <c r="G16">
-        <v>0.026606075</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>2.6606075E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -968,22 +2529,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0003732</v>
+        <v>3.7320000000000002E-4</v>
       </c>
       <c r="D17">
-        <v>0.0022373</v>
+        <v>2.2372999999999998E-3</v>
       </c>
       <c r="E17">
-        <v>0.0135952</v>
+        <v>1.35952E-2</v>
       </c>
       <c r="F17">
-        <v>0.08449390000000001</v>
+        <v>8.4493900000000011E-2</v>
       </c>
       <c r="G17">
-        <v>0.0251749</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>2.51749E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -991,22 +2552,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0002903</v>
+        <v>2.9030000000000001E-4</v>
       </c>
       <c r="D18">
-        <v>0.0009649000000000001</v>
+        <v>9.6490000000000009E-4</v>
       </c>
       <c r="E18">
-        <v>0.0041219</v>
+        <v>4.1219000000000004E-3</v>
       </c>
       <c r="F18">
-        <v>0.0160094</v>
+        <v>1.60094E-2</v>
       </c>
       <c r="G18">
-        <v>0.005346625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>5.3466249999999998E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1014,22 +2575,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0003562</v>
+        <v>3.5619999999999998E-4</v>
       </c>
       <c r="D19">
-        <v>0.0006833000000000001</v>
+        <v>6.8330000000000007E-4</v>
       </c>
       <c r="E19">
-        <v>0.0019604</v>
+        <v>1.9604000000000002E-3</v>
       </c>
       <c r="F19">
-        <v>0.007794000000000001</v>
+        <v>7.7940000000000006E-3</v>
       </c>
       <c r="G19">
-        <v>0.002698475</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>2.6984750000000001E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1037,22 +2598,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0003747</v>
+        <v>3.747E-4</v>
       </c>
       <c r="D20">
-        <v>0.0012193</v>
+        <v>1.2193E-3</v>
       </c>
       <c r="E20">
-        <v>0.0040626</v>
+        <v>4.0626000000000004E-3</v>
       </c>
       <c r="F20">
-        <v>0.0146006</v>
+        <v>1.46006E-2</v>
       </c>
       <c r="G20">
-        <v>0.0050643</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>5.0642999999999999E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1060,22 +2621,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0004781</v>
+        <v>4.7810000000000002E-4</v>
       </c>
       <c r="D21">
-        <v>0.0014165</v>
+        <v>1.4165E-3</v>
       </c>
       <c r="E21">
-        <v>0.0050514</v>
+        <v>5.0514000000000002E-3</v>
       </c>
       <c r="F21">
-        <v>0.0216055</v>
+        <v>2.16055E-2</v>
       </c>
       <c r="G21">
-        <v>0.007137875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>7.1378750000000001E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1083,22 +2644,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.0004663000000000001</v>
+        <v>4.6630000000000011E-4</v>
       </c>
       <c r="D22">
-        <v>0.0013659</v>
+        <v>1.3659E-3</v>
       </c>
       <c r="E22">
-        <v>0.004760499999999999</v>
+        <v>4.7604999999999991E-3</v>
       </c>
       <c r="F22">
-        <v>0.0204785</v>
+        <v>2.04785E-2</v>
       </c>
       <c r="G22">
-        <v>0.006767799999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>6.7677999999999992E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1106,22 +2667,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0004693</v>
+        <v>4.6930000000000002E-4</v>
       </c>
       <c r="D23">
-        <v>0.002568</v>
+        <v>2.568E-3</v>
       </c>
       <c r="E23">
-        <v>0.0153584</v>
+        <v>1.5358399999999999E-2</v>
       </c>
       <c r="F23">
-        <v>0.0998144</v>
+        <v>9.9814399999999998E-2</v>
       </c>
       <c r="G23">
-        <v>0.029552525</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>2.9552525E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1129,22 +2690,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.000357</v>
+        <v>3.57E-4</v>
       </c>
       <c r="D24">
-        <v>0.0013277</v>
+        <v>1.3277E-3</v>
       </c>
       <c r="E24">
-        <v>0.004921699999999999</v>
+        <v>4.9216999999999993E-3</v>
       </c>
       <c r="F24">
-        <v>0.0221448</v>
+        <v>2.2144799999999999E-2</v>
       </c>
       <c r="G24">
-        <v>0.007187799999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>7.1877999999999994E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1152,22 +2713,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0003804</v>
+        <v>3.8039999999999998E-4</v>
       </c>
       <c r="D25">
-        <v>0.0014211</v>
+        <v>1.4211E-3</v>
       </c>
       <c r="E25">
-        <v>0.005647399999999999</v>
+        <v>5.6473999999999986E-3</v>
       </c>
       <c r="F25">
-        <v>0.0284379</v>
+        <v>2.8437899999999999E-2</v>
       </c>
       <c r="G25">
-        <v>0.008971699999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>8.9716999999999991E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1175,22 +2736,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.0003497</v>
+        <v>3.4969999999999999E-4</v>
       </c>
       <c r="D26">
-        <v>0.0014182</v>
+        <v>1.4182000000000001E-3</v>
       </c>
       <c r="E26">
-        <v>0.006864600000000001</v>
+        <v>6.8646000000000011E-3</v>
       </c>
       <c r="F26">
-        <v>0.0380562</v>
+        <v>3.8056199999999998E-2</v>
       </c>
       <c r="G26">
-        <v>0.011672175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1.1672175E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1198,22 +2759,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0002511</v>
+        <v>2.5109999999999998E-4</v>
       </c>
       <c r="D27">
-        <v>0.0009774000000000002</v>
+        <v>9.7740000000000023E-4</v>
       </c>
       <c r="E27">
-        <v>0.0042303</v>
+        <v>4.2303000000000002E-3</v>
       </c>
       <c r="F27">
-        <v>0.0181839</v>
+        <v>1.8183899999999999E-2</v>
       </c>
       <c r="G27">
-        <v>0.005910675000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>5.9106750000000007E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1221,22 +2782,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0002686</v>
+        <v>2.6860000000000002E-4</v>
       </c>
       <c r="D28">
-        <v>0.0009577</v>
+        <v>9.5770000000000002E-4</v>
       </c>
       <c r="E28">
-        <v>0.004128</v>
+        <v>4.1279999999999997E-3</v>
       </c>
       <c r="F28">
-        <v>0.0177172</v>
+        <v>1.7717199999999999E-2</v>
       </c>
       <c r="G28">
-        <v>0.005767874999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>5.7678749999999987E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1244,22 +2805,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.0003063</v>
+        <v>3.0630000000000002E-4</v>
       </c>
       <c r="D29">
-        <v>0.001172</v>
+        <v>1.1720000000000001E-3</v>
       </c>
       <c r="E29">
-        <v>0.0045479</v>
+        <v>4.5478999999999997E-3</v>
       </c>
       <c r="F29">
-        <v>0.019021</v>
+        <v>1.9021E-2</v>
       </c>
       <c r="G29">
-        <v>0.006261799999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>6.2617999999999988E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1267,22 +2828,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0004891</v>
+        <v>4.8910000000000002E-4</v>
       </c>
       <c r="D30">
-        <v>0.0023507</v>
+        <v>2.3506999999999998E-3</v>
       </c>
       <c r="E30">
-        <v>0.010331</v>
+        <v>1.0331E-2</v>
       </c>
       <c r="F30">
-        <v>0.0964098</v>
+        <v>9.6409800000000004E-2</v>
       </c>
       <c r="G30">
-        <v>0.02739515</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>2.739515E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1290,22 +2851,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0005433</v>
+        <v>5.4330000000000003E-4</v>
       </c>
       <c r="D31">
-        <v>0.0019174</v>
+        <v>1.9174000000000001E-3</v>
       </c>
       <c r="E31">
-        <v>0.0107913</v>
+        <v>1.07913E-2</v>
       </c>
       <c r="F31">
-        <v>0.06810590000000001</v>
+        <v>6.8105900000000011E-2</v>
       </c>
       <c r="G31">
-        <v>0.020339475</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>2.0339474999999999E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1313,22 +2874,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0004685000000000001</v>
+        <v>4.6850000000000011E-4</v>
       </c>
       <c r="D32">
-        <v>0.0019461</v>
+        <v>1.9461000000000001E-3</v>
       </c>
       <c r="E32">
-        <v>0.0106905</v>
+        <v>1.06905E-2</v>
       </c>
       <c r="F32">
-        <v>0.06839629999999999</v>
+        <v>6.8396299999999993E-2</v>
       </c>
       <c r="G32">
-        <v>0.02037535</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>2.037535E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1336,22 +2897,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0004171</v>
+        <v>4.171E-4</v>
       </c>
       <c r="D33">
-        <v>0.0022172</v>
+        <v>2.2171999999999999E-3</v>
       </c>
       <c r="E33">
-        <v>0.013691</v>
+        <v>1.3691E-2</v>
       </c>
       <c r="F33">
-        <v>0.0848579</v>
+        <v>8.48579E-2</v>
       </c>
       <c r="G33">
-        <v>0.0252958</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>2.52958E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1359,22 +2920,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0003085</v>
+        <v>3.0850000000000002E-4</v>
       </c>
       <c r="D34">
-        <v>0.0007581</v>
+        <v>7.5810000000000005E-4</v>
       </c>
       <c r="E34">
-        <v>0.0023665</v>
+        <v>2.3665000000000001E-3</v>
       </c>
       <c r="F34">
-        <v>0.009682400000000001</v>
+        <v>9.6824000000000007E-3</v>
       </c>
       <c r="G34">
-        <v>0.003278875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>3.2788750000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1382,22 +2943,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0002498</v>
+        <v>2.498E-4</v>
       </c>
       <c r="D35">
-        <v>0.0009082</v>
+        <v>9.0819999999999996E-4</v>
       </c>
       <c r="E35">
-        <v>0.0027965</v>
+        <v>2.7964999999999999E-3</v>
       </c>
       <c r="F35">
-        <v>0.010708</v>
+        <v>1.0708000000000001E-2</v>
       </c>
       <c r="G35">
-        <v>0.003665625</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>3.665625E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1405,22 +2966,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.0003365</v>
+        <v>3.3649999999999999E-4</v>
       </c>
       <c r="D36">
-        <v>0.0010177</v>
+        <v>1.0177000000000001E-3</v>
       </c>
       <c r="E36">
-        <v>0.004231</v>
+        <v>4.2310000000000004E-3</v>
       </c>
       <c r="F36">
-        <v>0.0161585</v>
+        <v>1.6158499999999999E-2</v>
       </c>
       <c r="G36">
-        <v>0.005435924999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>5.4359249999999986E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1428,22 +2989,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0003236</v>
+        <v>3.2360000000000001E-4</v>
       </c>
       <c r="D37">
-        <v>0.0008583999999999999</v>
+        <v>8.5839999999999994E-4</v>
       </c>
       <c r="E37">
-        <v>0.0033271</v>
+        <v>3.3270999999999999E-3</v>
       </c>
       <c r="F37">
-        <v>0.0138598</v>
+        <v>1.38598E-2</v>
       </c>
       <c r="G37">
-        <v>0.004592225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>4.5922250000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1451,22 +3012,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0003852</v>
+        <v>3.8519999999999998E-4</v>
       </c>
       <c r="D38">
-        <v>0.0007454</v>
+        <v>7.4540000000000001E-4</v>
       </c>
       <c r="E38">
-        <v>0.0020654</v>
+        <v>2.0653999999999998E-3</v>
       </c>
       <c r="F38">
-        <v>0.007921800000000001</v>
+        <v>7.9218000000000014E-3</v>
       </c>
       <c r="G38">
-        <v>0.00277945</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>2.7794500000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1474,22 +3035,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.000343</v>
+        <v>3.4299999999999999E-4</v>
       </c>
       <c r="D39">
-        <v>0.0006773</v>
+        <v>6.7730000000000004E-4</v>
       </c>
       <c r="E39">
-        <v>0.0020196</v>
+        <v>2.0195999999999999E-3</v>
       </c>
       <c r="F39">
-        <v>0.0077637</v>
+        <v>7.7637000000000001E-3</v>
       </c>
       <c r="G39">
-        <v>0.0027009</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>2.7009E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1497,22 +3058,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0003698</v>
+        <v>3.6979999999999999E-4</v>
       </c>
       <c r="D40">
-        <v>0.0009492999999999999</v>
+        <v>9.4929999999999993E-4</v>
       </c>
       <c r="E40">
-        <v>0.0026348</v>
+        <v>2.6348000000000001E-3</v>
       </c>
       <c r="F40">
-        <v>0.0104215</v>
+        <v>1.04215E-2</v>
       </c>
       <c r="G40">
-        <v>0.00359385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>3.59385E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1520,22 +3081,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0004327</v>
+        <v>4.327E-4</v>
       </c>
       <c r="D41">
-        <v>0.0013071</v>
+        <v>1.3071000000000001E-3</v>
       </c>
       <c r="E41">
-        <v>0.004128000000000001</v>
+        <v>4.1280000000000006E-3</v>
       </c>
       <c r="F41">
-        <v>0.014741</v>
+        <v>1.4741000000000001E-2</v>
       </c>
       <c r="G41">
-        <v>0.0051522</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>5.1522E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1543,22 +3104,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0003994</v>
+        <v>3.994E-4</v>
       </c>
       <c r="D42">
-        <v>0.0012647</v>
+        <v>1.2646999999999999E-3</v>
       </c>
       <c r="E42">
-        <v>0.004000200000000001</v>
+        <v>4.0002000000000006E-3</v>
       </c>
       <c r="F42">
-        <v>0.0150702</v>
+        <v>1.5070200000000001E-2</v>
       </c>
       <c r="G42">
-        <v>0.005183625000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>5.1836250000000007E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1566,22 +3127,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.0005004</v>
+        <v>5.0040000000000002E-4</v>
       </c>
       <c r="D43">
-        <v>0.0014257</v>
+        <v>1.4257E-3</v>
       </c>
       <c r="E43">
-        <v>0.0048312</v>
+        <v>4.8311999999999999E-3</v>
       </c>
       <c r="F43">
-        <v>0.0205914</v>
+        <v>2.0591399999999999E-2</v>
       </c>
       <c r="G43">
-        <v>0.006837175</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>6.837175E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1589,22 +3150,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0004187</v>
+        <v>4.1869999999999999E-4</v>
       </c>
       <c r="D44">
-        <v>0.0015562</v>
+        <v>1.5562E-3</v>
       </c>
       <c r="E44">
-        <v>0.0058873</v>
+        <v>5.8872999999999998E-3</v>
       </c>
       <c r="F44">
-        <v>0.029292</v>
+        <v>2.9291999999999999E-2</v>
       </c>
       <c r="G44">
-        <v>0.00928855</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>9.2885499999999996E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1612,22 +3173,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0004037</v>
+        <v>4.037E-4</v>
       </c>
       <c r="D45">
-        <v>0.0015082</v>
+        <v>1.5081999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>0.0070943</v>
+        <v>7.0943000000000004E-3</v>
       </c>
       <c r="F45">
-        <v>0.0387302</v>
+        <v>3.8730199999999999E-2</v>
       </c>
       <c r="G45">
-        <v>0.0119341</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>1.19341E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1635,22 +3196,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.000398</v>
+        <v>3.9800000000000002E-4</v>
       </c>
       <c r="D46">
-        <v>0.001491</v>
+        <v>1.4909999999999999E-3</v>
       </c>
       <c r="E46">
-        <v>0.0067892</v>
+        <v>6.7891999999999996E-3</v>
       </c>
       <c r="F46">
-        <v>0.035798</v>
+        <v>3.5798000000000003E-2</v>
       </c>
       <c r="G46">
-        <v>0.01111905</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>1.111905E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1658,22 +3219,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0003128</v>
+        <v>3.1280000000000001E-4</v>
       </c>
       <c r="D47">
-        <v>0.0010612</v>
+        <v>1.0612E-3</v>
       </c>
       <c r="E47">
-        <v>0.004392699999999999</v>
+        <v>4.3926999999999994E-3</v>
       </c>
       <c r="F47">
-        <v>0.0184484</v>
+        <v>1.84484E-2</v>
       </c>
       <c r="G47">
-        <v>0.006053774999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>6.0537749999999991E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1681,22 +3242,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0005257</v>
+        <v>5.2570000000000004E-4</v>
       </c>
       <c r="D48">
-        <v>0.002034</v>
+        <v>2.0339999999999998E-3</v>
       </c>
       <c r="E48">
-        <v>0.0113156</v>
+        <v>1.13156E-2</v>
       </c>
       <c r="F48">
-        <v>0.06909230000000001</v>
+        <v>6.9092300000000009E-2</v>
       </c>
       <c r="G48">
-        <v>0.0207419</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>2.0741900000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1704,22 +3265,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0003535</v>
+        <v>3.5349999999999997E-4</v>
       </c>
       <c r="D49">
-        <v>0.0008357</v>
+        <v>8.3569999999999998E-4</v>
       </c>
       <c r="E49">
-        <v>0.0024978</v>
+        <v>2.4978000000000001E-3</v>
       </c>
       <c r="F49">
-        <v>0.0098365</v>
+        <v>9.8364999999999998E-3</v>
       </c>
       <c r="G49">
-        <v>0.003380875</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>3.3808750000000002E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1727,22 +3288,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>0.0003485</v>
+        <v>3.4850000000000001E-4</v>
       </c>
       <c r="D50">
-        <v>0.0009824</v>
+        <v>9.8240000000000003E-4</v>
       </c>
       <c r="E50">
-        <v>0.003401</v>
+        <v>3.4009999999999999E-3</v>
       </c>
       <c r="F50">
-        <v>0.0116383</v>
+        <v>1.1638300000000001E-2</v>
       </c>
       <c r="G50">
-        <v>0.004092549999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>4.0925499999999986E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1750,22 +3311,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>0.0003246</v>
+        <v>3.2459999999999998E-4</v>
       </c>
       <c r="D51">
-        <v>0.0010714</v>
+        <v>1.0713999999999999E-3</v>
       </c>
       <c r="E51">
-        <v>0.0030594</v>
+        <v>3.0593999999999999E-3</v>
       </c>
       <c r="F51">
-        <v>0.0115334</v>
+        <v>1.1533399999999999E-2</v>
       </c>
       <c r="G51">
-        <v>0.003997199999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>3.9971999999999994E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1773,22 +3334,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>0.0002936</v>
+        <v>2.9359999999999998E-4</v>
       </c>
       <c r="D52">
-        <v>0.0009465000000000001</v>
+        <v>9.4650000000000008E-4</v>
       </c>
       <c r="E52">
-        <v>0.002878</v>
+        <v>2.8779999999999999E-3</v>
       </c>
       <c r="F52">
-        <v>0.0108367</v>
+        <v>1.0836699999999999E-2</v>
       </c>
       <c r="G52">
-        <v>0.0037387</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>3.7387000000000002E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1796,22 +3357,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>0.0003143</v>
+        <v>3.143E-4</v>
       </c>
       <c r="D53">
-        <v>0.0009337000000000002</v>
+        <v>9.337000000000002E-4</v>
       </c>
       <c r="E53">
-        <v>0.003489</v>
+        <v>3.4889999999999999E-3</v>
       </c>
       <c r="F53">
-        <v>0.0174405</v>
+        <v>1.7440500000000001E-2</v>
       </c>
       <c r="G53">
-        <v>0.005544375000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>5.5443750000000007E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1819,22 +3380,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>0.0003728000000000001</v>
+        <v>3.7280000000000012E-4</v>
       </c>
       <c r="D54">
-        <v>0.0009551000000000001</v>
+        <v>9.5510000000000007E-4</v>
       </c>
       <c r="E54">
-        <v>0.0034294</v>
+        <v>3.4294E-3</v>
       </c>
       <c r="F54">
-        <v>0.0140676</v>
+        <v>1.40676E-2</v>
       </c>
       <c r="G54">
-        <v>0.004706225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>4.7062249999999996E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1842,22 +3403,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>0.0003995</v>
+        <v>3.9950000000000001E-4</v>
       </c>
       <c r="D55">
-        <v>0.0007915999999999999</v>
+        <v>7.9159999999999994E-4</v>
       </c>
       <c r="E55">
-        <v>0.0021414</v>
+        <v>2.1413999999999999E-3</v>
       </c>
       <c r="F55">
-        <v>0.007889000000000002</v>
+        <v>7.8890000000000019E-3</v>
       </c>
       <c r="G55">
-        <v>0.002805375000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>2.805375000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1865,22 +3426,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>0.0003953999999999999</v>
+        <v>3.9539999999999991E-4</v>
       </c>
       <c r="D56">
-        <v>0.0009863000000000001</v>
+        <v>9.8630000000000007E-4</v>
       </c>
       <c r="E56">
-        <v>0.0027351</v>
+        <v>2.7350999999999999E-3</v>
       </c>
       <c r="F56">
-        <v>0.0106295</v>
+        <v>1.06295E-2</v>
       </c>
       <c r="G56">
-        <v>0.003686575</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>3.6865750000000001E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1888,22 +3449,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>0.000361</v>
+        <v>3.6099999999999999E-4</v>
       </c>
       <c r="D57">
-        <v>0.0009362999999999999</v>
+        <v>9.3629999999999994E-4</v>
       </c>
       <c r="E57">
-        <v>0.0027069</v>
+        <v>2.7068999999999999E-3</v>
       </c>
       <c r="F57">
-        <v>0.0104853</v>
+        <v>1.0485299999999999E-2</v>
       </c>
       <c r="G57">
-        <v>0.003622375</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>3.6223750000000002E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1911,22 +3472,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>0.0004349000000000001</v>
+        <v>4.3490000000000011E-4</v>
       </c>
       <c r="D58">
-        <v>0.0013145</v>
+        <v>1.3144999999999999E-3</v>
       </c>
       <c r="E58">
-        <v>0.0040983</v>
+        <v>4.0983E-3</v>
       </c>
       <c r="F58">
-        <v>0.0151961</v>
+        <v>1.5196100000000001E-2</v>
       </c>
       <c r="G58">
-        <v>0.005260949999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>5.2609499999999986E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1934,22 +3495,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>0.0004196</v>
+        <v>4.1960000000000001E-4</v>
       </c>
       <c r="D59">
-        <v>0.0016225</v>
+        <v>1.6225E-3</v>
       </c>
       <c r="E59">
-        <v>0.0071785</v>
+        <v>7.1785E-3</v>
       </c>
       <c r="F59">
-        <v>0.0362147</v>
+        <v>3.6214700000000002E-2</v>
       </c>
       <c r="G59">
-        <v>0.011358825</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>1.1358824999999999E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1957,22 +3518,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>0.0003943999999999999</v>
+        <v>3.9439999999999988E-4</v>
       </c>
       <c r="D60">
-        <v>0.0010487</v>
+        <v>1.0487000000000001E-3</v>
       </c>
       <c r="E60">
-        <v>0.0035047</v>
+        <v>3.5046999999999999E-3</v>
       </c>
       <c r="F60">
-        <v>0.0117286</v>
+        <v>1.17286E-2</v>
       </c>
       <c r="G60">
-        <v>0.0041691</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>4.1691000000000002E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1980,22 +3541,22 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>0.0003826</v>
+        <v>3.8259999999999998E-4</v>
       </c>
       <c r="D61">
-        <v>0.0012117</v>
+        <v>1.2117E-3</v>
       </c>
       <c r="E61">
-        <v>0.0031707</v>
+        <v>3.1706999999999998E-3</v>
       </c>
       <c r="F61">
-        <v>0.0117317</v>
+        <v>1.1731699999999999E-2</v>
       </c>
       <c r="G61">
-        <v>0.004124175000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>4.1241750000000008E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2003,22 +3564,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>0.0003373</v>
+        <v>3.3730000000000001E-4</v>
       </c>
       <c r="D62">
-        <v>0.0010638</v>
+        <v>1.0637999999999999E-3</v>
       </c>
       <c r="E62">
-        <v>0.0037087</v>
+        <v>3.7087000000000001E-3</v>
       </c>
       <c r="F62">
-        <v>0.0178663</v>
+        <v>1.7866300000000002E-2</v>
       </c>
       <c r="G62">
-        <v>0.005744025000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>5.7440250000000007E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -2026,22 +3587,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>0.0003557</v>
+        <v>3.5570000000000003E-4</v>
       </c>
       <c r="D63">
-        <v>0.0009733000000000001</v>
+        <v>9.7330000000000008E-4</v>
       </c>
       <c r="E63">
-        <v>0.0036327</v>
+        <v>3.6327E-3</v>
       </c>
       <c r="F63">
-        <v>0.0176529</v>
+        <v>1.7652899999999999E-2</v>
       </c>
       <c r="G63">
-        <v>0.00565365</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>5.6536499999999996E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -2049,22 +3610,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>0.0004158</v>
+        <v>4.1580000000000002E-4</v>
       </c>
       <c r="D64">
-        <v>0.0009920999999999999</v>
+        <v>9.9209999999999988E-4</v>
       </c>
       <c r="E64">
-        <v>0.0027417</v>
+        <v>2.7417000000000001E-3</v>
       </c>
       <c r="F64">
-        <v>0.0106456</v>
+        <v>1.06456E-2</v>
       </c>
       <c r="G64">
-        <v>0.0036988</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>3.6987999999999999E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2072,32 +3633,33 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>0.0003821</v>
+        <v>3.8210000000000002E-4</v>
       </c>
       <c r="D65">
-        <v>0.0010941</v>
+        <v>1.0941E-3</v>
       </c>
       <c r="E65">
-        <v>0.0037259</v>
+        <v>3.7258999999999999E-3</v>
       </c>
       <c r="F65">
-        <v>0.0180604</v>
+        <v>1.8060400000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.005815625</v>
+        <v>5.8156249999999996E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +3682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +3705,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2166,7 +3728,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2189,7 +3751,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2212,7 +3774,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2235,7 +3797,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2258,7 +3820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2281,7 +3843,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2304,7 +3866,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2327,7 +3889,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2350,7 +3912,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2373,7 +3935,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2396,7 +3958,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2419,7 +3981,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2442,7 +4004,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2465,7 +4027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2488,7 +4050,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2511,7 +4073,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2534,7 +4096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2557,7 +4119,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2580,7 +4142,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2603,7 +4165,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2626,7 +4188,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2649,7 +4211,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2672,7 +4234,7 @@
         <v>95.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2695,7 +4257,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2718,7 +4280,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2741,7 +4303,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2764,7 +4326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2787,7 +4349,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2810,7 +4372,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2833,7 +4395,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2856,7 +4418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2879,7 +4441,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2902,7 +4464,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2925,7 +4487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2948,7 +4510,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2971,7 +4533,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -2994,7 +4556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3017,7 +4579,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -3040,7 +4602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -3063,7 +4625,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -3086,7 +4648,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3109,7 +4671,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3132,7 +4694,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3155,7 +4717,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3178,7 +4740,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -3201,7 +4763,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -3224,7 +4786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3247,7 +4809,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -3270,7 +4832,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -3293,7 +4855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3316,7 +4878,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -3339,7 +4901,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -3362,7 +4924,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -3385,7 +4947,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -3408,7 +4970,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -3431,7 +4993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3454,7 +5016,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -3477,7 +5039,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -3500,7 +5062,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3523,7 +5085,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -3546,7 +5108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -3569,7 +5131,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -3598,11 +5160,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3633,22 +5195,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D2">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E2">
         <v>105.4974746830583</v>
       </c>
       <c r="F2">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G2">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3656,7 +5218,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D3">
         <v>52.87005768508881</v>
@@ -3665,13 +5227,13 @@
         <v>106.3259018078045</v>
       </c>
       <c r="F3">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G3">
-        <v>99.4368145112785</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>99.436814511278499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3679,22 +5241,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D4">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E4">
         <v>111.8406204335659</v>
       </c>
       <c r="F4">
-        <v>226.8528137423857</v>
+        <v>226.85281374238571</v>
       </c>
       <c r="G4">
-        <v>104.865746699413</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>104.86574669941299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3702,22 +5264,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D5">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E5">
         <v>105.4974746830583</v>
       </c>
       <c r="F5">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G5">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3725,22 +5287,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D6">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E6">
         <v>105.4974746830583</v>
       </c>
       <c r="F6">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G6">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3748,22 +5310,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>25.09083264970256</v>
+        <v>25.090832649702559</v>
       </c>
       <c r="D7">
-        <v>50.85195240643645</v>
+        <v>50.851952406436453</v>
       </c>
       <c r="E7">
-        <v>102.2208989357328</v>
+        <v>102.22089893573281</v>
       </c>
       <c r="F7">
-        <v>206.20172566371</v>
+        <v>206.20172566370999</v>
       </c>
       <c r="G7">
-        <v>96.09135241389544</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>96.091352413895436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3771,22 +5333,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D8">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E8">
         <v>105.4974746830583</v>
       </c>
       <c r="F8">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G8">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3794,7 +5356,7 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D9">
         <v>54.87005768508881</v>
@@ -3803,13 +5365,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F9">
-        <v>220.4091629284898</v>
+        <v>220.40916292848979</v>
       </c>
       <c r="G9">
         <v>102.8761543394987</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3817,22 +5379,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D10">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E10">
         <v>108.6690475583121</v>
       </c>
       <c r="F10">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G10">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3840,22 +5402,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D11">
-        <v>50.94267710322084</v>
+        <v>50.942677103220838</v>
       </c>
       <c r="E11">
         <v>102.3124613687156</v>
       </c>
       <c r="F11">
-        <v>204.6073265451839</v>
+        <v>204.60732654518389</v>
       </c>
       <c r="G11">
-        <v>95.79404337902628</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>95.794043379026277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3863,22 +5425,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D12">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E12">
         <v>106.3259018078045</v>
       </c>
       <c r="F12">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G12">
-        <v>99.22970773009197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>99.229707730091974</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3889,19 +5451,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D13">
-        <v>53.15544097087485</v>
+        <v>53.155440970874849</v>
       </c>
       <c r="E13">
         <v>108.4816898532232</v>
       </c>
       <c r="F13">
-        <v>219.2487673982965</v>
+        <v>219.24876739829651</v>
       </c>
       <c r="G13">
         <v>101.8589186747198</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3909,22 +5471,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D14">
-        <v>57.21320343559641</v>
+        <v>57.213203435596412</v>
       </c>
       <c r="E14">
-        <v>117.3553390593274</v>
+        <v>117.35533905932741</v>
       </c>
       <c r="F14">
-        <v>237.2964645562816</v>
+        <v>237.29646455628159</v>
       </c>
       <c r="G14">
         <v>109.6482322781408</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3932,22 +5494,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D15">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E15">
-        <v>111.254833995939</v>
+        <v>111.25483399593899</v>
       </c>
       <c r="F15">
-        <v>221.3380951166243</v>
+        <v>221.33809511662429</v>
       </c>
       <c r="G15">
         <v>103.3406204335659</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3955,22 +5517,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D16">
-        <v>50.53627320613764</v>
+        <v>50.536273206137643</v>
       </c>
       <c r="E16">
         <v>101.5116887917378</v>
       </c>
       <c r="F16">
-        <v>203.6202038485505</v>
+        <v>203.62020384855049</v>
       </c>
       <c r="G16">
-        <v>95.24546858635269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>95.245468586352686</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3978,22 +5540,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D17">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E17">
         <v>105.4974746830583</v>
       </c>
       <c r="F17">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G17">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4001,22 +5563,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D18">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E18">
         <v>105.4974746830583</v>
       </c>
       <c r="F18">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G18">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4024,22 +5586,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D19">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E19">
         <v>105.4974746830583</v>
       </c>
       <c r="F19">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G19">
-        <v>99.31549416771887</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>99.315494167718867</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4047,22 +5609,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D20">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E20">
         <v>105.4974746830583</v>
       </c>
       <c r="F20">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G20">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4070,10 +5632,10 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D21">
-        <v>51.78969465813791</v>
+        <v>51.789694658137911</v>
       </c>
       <c r="E21">
         <v>104.870607101803</v>
@@ -4082,10 +5644,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G21">
-        <v>98.25915590201265</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>98.259155902012651</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4093,22 +5655,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D22">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E22">
         <v>105.4974746830583</v>
       </c>
       <c r="F22">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G22">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4116,22 +5678,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D23">
-        <v>49.84694171698072</v>
+        <v>49.846941716980723</v>
       </c>
       <c r="E23">
-        <v>101.4739771831186</v>
+        <v>101.47397718311861</v>
       </c>
       <c r="F23">
-        <v>204.9824557992469</v>
+        <v>204.98245579924691</v>
       </c>
       <c r="G23">
-        <v>95.40427079958275</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>95.404270799582747</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4142,19 +5704,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D24">
-        <v>53.83171371476478</v>
+        <v>53.831713714764781</v>
       </c>
       <c r="E24">
         <v>107.0191148045464</v>
       </c>
       <c r="F24">
-        <v>216.3179808690437</v>
+        <v>216.31798086904371</v>
       </c>
       <c r="G24">
         <v>100.9296464662099</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4162,22 +5724,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D25">
-        <v>56.62741699796952</v>
+        <v>56.627416997969519</v>
       </c>
       <c r="E25">
         <v>113.8406204335659</v>
       </c>
       <c r="F25">
-        <v>230.2670273047588</v>
+        <v>230.26702730475881</v>
       </c>
       <c r="G25">
-        <v>106.865746699413</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>106.86574669941299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4185,22 +5747,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D26">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E26">
         <v>110.6690475583121</v>
       </c>
       <c r="F26">
-        <v>219.5807358037436</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G26">
-        <v>102.754833995939</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>102.75483399593899</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4211,19 +5773,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D27">
-        <v>52.18190712280661</v>
+        <v>52.181907122806606</v>
       </c>
       <c r="E27">
-        <v>104.1172869980445</v>
+        <v>104.11728699804451</v>
       </c>
       <c r="F27">
-        <v>208.2406136569161</v>
+        <v>208.24061365691611</v>
       </c>
       <c r="G27">
-        <v>97.77239606356295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>97.772396063562951</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4231,7 +5793,7 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D28">
         <v>54.87005768508881</v>
@@ -4240,13 +5802,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F28">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G28">
-        <v>102.254833995939</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>102.25483399593899</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -4254,22 +5816,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D29">
-        <v>50.44506335783473</v>
+        <v>50.445063357834727</v>
       </c>
       <c r="E29">
         <v>102.0661260637976</v>
       </c>
       <c r="F29">
-        <v>205.4907084230159</v>
+        <v>205.49070842301589</v>
       </c>
       <c r="G29">
-        <v>95.82890158590824</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>95.828901585908241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -4280,7 +5842,7 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D30">
-        <v>54.33331983263714</v>
+        <v>54.333319832637137</v>
       </c>
       <c r="E30">
         <v>109.8662799826854</v>
@@ -4292,7 +5854,7 @@
         <v>103.2143522535132</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -4309,13 +5871,13 @@
         <v>105.0403618691834</v>
       </c>
       <c r="F31">
-        <v>211.7340790314746</v>
+        <v>211.73407903147461</v>
       </c>
       <c r="G31">
-        <v>98.95532963718236</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>98.955329637182359</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4323,22 +5885,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D32">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E32">
-        <v>111.254833995939</v>
+        <v>111.25483399593899</v>
       </c>
       <c r="F32">
         <v>224.9949493661166</v>
       </c>
       <c r="G32">
-        <v>104.254833995939</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>104.25483399593899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4346,22 +5908,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D33">
-        <v>50.53627320613764</v>
+        <v>50.536273206137643</v>
       </c>
       <c r="E33">
         <v>101.5116887917378</v>
       </c>
       <c r="F33">
-        <v>203.6202038485505</v>
+        <v>203.62020384855049</v>
       </c>
       <c r="G33">
-        <v>95.24546858635269</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>95.245468586352686</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4369,22 +5931,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D34">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E34">
         <v>105.4974746830583</v>
       </c>
       <c r="F34">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G34">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4392,22 +5954,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D35">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E35">
         <v>108.6690475583121</v>
       </c>
       <c r="F35">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G35">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4415,10 +5977,10 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D36">
-        <v>50.94267710322084</v>
+        <v>50.942677103220838</v>
       </c>
       <c r="E36">
         <v>102.6712897929513</v>
@@ -4427,10 +5989,10 @@
         <v>206.2505164179251</v>
       </c>
       <c r="G36">
-        <v>96.2945479532705</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>96.294547953270495</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4438,10 +6000,10 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D37">
-        <v>54.38477631085023</v>
+        <v>54.384776310850228</v>
       </c>
       <c r="E37">
         <v>110.1837661840736</v>
@@ -4450,10 +6012,10 @@
         <v>221.7817459305202</v>
       </c>
       <c r="G37">
-        <v>102.9159992311072</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>102.91599923110719</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4461,10 +6023,10 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D38">
-        <v>53.78969465813791</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E38">
         <v>104.870607101803</v>
@@ -4473,10 +6035,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G38">
-        <v>98.75915590201265</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>98.759155902012651</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4484,22 +6046,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D39">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E39">
         <v>105.4974746830583</v>
       </c>
       <c r="F39">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G39">
-        <v>99.31549416771887</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>99.315494167718867</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4507,22 +6069,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D40">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E40">
         <v>108.6690475583121</v>
       </c>
       <c r="F40">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G40">
         <v>101.4870670429727</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4530,10 +6092,10 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D41">
-        <v>51.78969465813791</v>
+        <v>51.789694658137911</v>
       </c>
       <c r="E41">
         <v>104.870607101803</v>
@@ -4542,10 +6104,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G41">
-        <v>98.25915590201265</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>98.259155902012651</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4553,22 +6115,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D42">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E42">
         <v>105.4974746830583</v>
       </c>
       <c r="F42">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G42">
-        <v>98.81549416771887</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>98.815494167718867</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4576,10 +6138,10 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D43">
-        <v>51.78969465813791</v>
+        <v>51.789694658137911</v>
       </c>
       <c r="E43">
         <v>104.870607101803</v>
@@ -4588,10 +6150,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G43">
-        <v>98.25915590201265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>98.259155902012651</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4602,19 +6164,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D44">
-        <v>54.03806702219917</v>
+        <v>54.038067022199172</v>
       </c>
       <c r="E44">
-        <v>108.6629955793343</v>
+        <v>108.66299557933429</v>
       </c>
       <c r="F44">
         <v>219.4050796727812</v>
       </c>
       <c r="G44">
-        <v>102.1639796876998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>102.16397968769979</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4631,13 +6193,13 @@
         <v>104.7154540633544</v>
       </c>
       <c r="F45">
-        <v>211.2974610344121</v>
+        <v>211.29746103441209</v>
       </c>
       <c r="G45">
-        <v>98.76494818645951</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>98.764948186459506</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4645,22 +6207,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D46">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E46">
         <v>110.6690475583121</v>
       </c>
       <c r="F46">
-        <v>223.2375900532359</v>
+        <v>223.23759005323589</v>
       </c>
       <c r="G46">
         <v>103.6690475583121</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4671,19 +6233,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D47">
-        <v>52.18190712280661</v>
+        <v>52.181907122806606</v>
       </c>
       <c r="E47">
         <v>104.3277853366118</v>
       </c>
       <c r="F47">
-        <v>208.2406136569161</v>
+        <v>208.24061365691611</v>
       </c>
       <c r="G47">
         <v>97.82502064820477</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4700,13 +6262,13 @@
         <v>105.0924763437464</v>
       </c>
       <c r="F48">
-        <v>213.871746544051</v>
+        <v>213.87174654405101</v>
       </c>
       <c r="G48">
-        <v>99.50277513396722</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>99.502775133967219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -4714,22 +6276,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D49">
-        <v>51.28582285372848</v>
+        <v>51.285822853728483</v>
       </c>
       <c r="E49">
         <v>103.6168719392922</v>
       </c>
       <c r="F49">
-        <v>208.3695141903953</v>
+        <v>208.36951419039531</v>
       </c>
       <c r="G49">
         <v>97.14647937060019</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -4737,22 +6299,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D50">
-        <v>54.38477631085023</v>
+        <v>54.384776310850228</v>
       </c>
       <c r="E50">
         <v>110.1837661840736</v>
       </c>
       <c r="F50">
-        <v>254.6101730552664</v>
+        <v>254.61017305526639</v>
       </c>
       <c r="G50">
         <v>111.1231060122937</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -4760,22 +6322,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D51">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E51">
         <v>108.6690475583121</v>
       </c>
       <c r="F51">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G51">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -4786,19 +6348,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D52">
-        <v>53.49858672138247</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E52">
         <v>106.8493377268543</v>
       </c>
       <c r="F52">
-        <v>214.3364735781256</v>
+        <v>214.33647357812561</v>
       </c>
       <c r="G52">
-        <v>100.3085436257117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>100.30854362571171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -4806,22 +6368,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D53">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E53">
         <v>105.4974746830583</v>
       </c>
       <c r="F53">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G53">
-        <v>99.66904755831214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>99.669047558312144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -4829,22 +6391,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D54">
-        <v>53.36911568474508</v>
+        <v>53.369115684745083</v>
       </c>
       <c r="E54">
         <v>107.3529870742077</v>
       </c>
       <c r="F54">
-        <v>215.389391816042</v>
+        <v>215.38939181604201</v>
       </c>
       <c r="G54">
         <v>100.3563007684949</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -4852,10 +6414,10 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D55">
-        <v>53.78969465813791</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E55">
         <v>104.870607101803</v>
@@ -4864,10 +6426,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G55">
-        <v>98.75915590201265</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>98.759155902012651</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -4875,22 +6437,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D56">
-        <v>53.78969465813791</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E56">
         <v>108.0421799770567</v>
       </c>
       <c r="F56">
-        <v>216.5773319748864</v>
+        <v>216.57733197488639</v>
       </c>
       <c r="G56">
         <v>100.9307287772664</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4898,22 +6460,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D57">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E57">
         <v>108.6690475583121</v>
       </c>
       <c r="F57">
-        <v>217.9238815542512</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G57">
         <v>101.4870670429727</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4921,10 +6483,10 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D58">
-        <v>51.78969465813791</v>
+        <v>51.789694658137911</v>
       </c>
       <c r="E58">
         <v>104.870607101803</v>
@@ -4933,10 +6495,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G58">
-        <v>98.25915590201265</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>98.259155902012651</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -4953,13 +6515,13 @@
         <v>104.7675685379174</v>
       </c>
       <c r="F59">
-        <v>213.4351285469886</v>
+        <v>213.43512854698861</v>
       </c>
       <c r="G59">
-        <v>99.31239368324435</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>99.312393683244352</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -4967,10 +6529,10 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D60">
-        <v>53.36911568474508</v>
+        <v>53.369115684745083</v>
       </c>
       <c r="E60">
         <v>107.3529870742077</v>
@@ -4979,10 +6541,10 @@
         <v>250.8077936418064</v>
       </c>
       <c r="G60">
-        <v>109.210901224936</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>109.21090122493599</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -4993,19 +6555,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D61">
-        <v>53.49858672138247</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E61">
         <v>106.8493377268543</v>
       </c>
       <c r="F61">
-        <v>214.3364735781256</v>
+        <v>214.33647357812561</v>
       </c>
       <c r="G61">
-        <v>100.3085436257117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>100.30854362571171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5013,22 +6575,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>26.72792206135786</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D62">
-        <v>54.04163056034262</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E62">
         <v>108.6690475583121</v>
       </c>
       <c r="F62">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G62">
         <v>100.4619407771256</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5039,19 +6601,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D63">
-        <v>53.49858672138247</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E63">
         <v>103.6168719392922</v>
       </c>
       <c r="F63">
-        <v>206.0406506963519</v>
+        <v>206.04065069635189</v>
       </c>
       <c r="G63">
-        <v>97.42647145837776</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>97.426471458377762</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5059,22 +6621,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D64">
-        <v>53.78969465813791</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E64">
         <v>108.0421799770567</v>
       </c>
       <c r="F64">
-        <v>216.5773319748864</v>
+        <v>216.57733197488639</v>
       </c>
       <c r="G64">
         <v>100.9307287772664</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5085,16 +6647,16 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D65">
-        <v>53.49858672138247</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E65">
         <v>107.6902241629822</v>
       </c>
       <c r="F65">
-        <v>206.0406506963519</v>
+        <v>206.04065069635189</v>
       </c>
       <c r="G65">
-        <v>98.44480951430027</v>
+        <v>98.444809514300275</v>
       </c>
     </row>
   </sheetData>
@@ -5103,11 +6665,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5130,7 +6692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5153,7 +6715,7 @@
         <v>111.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5176,7 +6738,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5199,7 +6761,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5222,7 +6784,7 @@
         <v>116.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5245,7 +6807,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5268,7 +6830,7 @@
         <v>111.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5291,7 +6853,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5314,7 +6876,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5337,7 +6899,7 @@
         <v>178.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5360,7 +6922,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5383,7 +6945,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5406,7 +6968,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5429,7 +6991,7 @@
         <v>179.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5452,7 +7014,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5475,7 +7037,7 @@
         <v>116.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +7060,7 @@
         <v>122.75</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5521,7 +7083,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5544,7 +7106,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5567,7 +7129,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5590,7 +7152,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5613,7 +7175,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5636,7 +7198,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5659,7 +7221,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5682,7 +7244,7 @@
         <v>204.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -5705,7 +7267,7 @@
         <v>190.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -5728,7 +7290,7 @@
         <v>178.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -5751,7 +7313,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5774,7 +7336,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5797,7 +7359,7 @@
         <v>179.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5820,7 +7382,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5843,7 +7405,7 @@
         <v>214.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5866,7 +7428,7 @@
         <v>122.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5889,7 +7451,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5912,7 +7474,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5935,7 +7497,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5958,7 +7520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5981,7 +7543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6004,7 +7566,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -6027,7 +7589,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6050,7 +7612,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6073,7 +7635,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6096,7 +7658,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6119,7 +7681,7 @@
         <v>204.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6142,7 +7704,7 @@
         <v>190.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6165,7 +7727,7 @@
         <v>204.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6188,7 +7750,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -6211,7 +7773,7 @@
         <v>214.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -6234,7 +7796,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -6257,7 +7819,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -6280,7 +7842,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -6303,7 +7865,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -6326,7 +7888,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -6349,7 +7911,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -6372,7 +7934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -6395,7 +7957,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -6418,7 +7980,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6441,7 +8003,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -6464,7 +8026,7 @@
         <v>204.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -6487,7 +8049,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -6510,7 +8072,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -6533,7 +8095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -6556,7 +8118,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6579,7 +8141,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -6608,11 +8170,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6635,7 +8197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6658,7 +8220,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6681,7 +8243,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6704,7 +8266,7 @@
         <v>376.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6727,7 +8289,7 @@
         <v>923.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6750,7 +8312,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6773,7 +8335,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6796,7 +8358,7 @@
         <v>1314.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6819,7 +8381,7 @@
         <v>347.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6842,7 +8404,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6865,7 +8427,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6888,7 +8450,7 @@
         <v>943.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6911,7 +8473,7 @@
         <v>376.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6934,7 +8496,7 @@
         <v>523.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6957,7 +8519,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6980,7 +8542,7 @@
         <v>923.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7003,7 +8565,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7026,7 +8588,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7049,7 +8611,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7072,7 +8634,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7095,7 +8657,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7118,7 +8680,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -7141,7 +8703,7 @@
         <v>1314.25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7164,7 +8726,7 @@
         <v>347.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7187,7 +8749,7 @@
         <v>453.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7210,7 +8772,7 @@
         <v>443.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7233,7 +8795,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7256,7 +8818,7 @@
         <v>653.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7279,7 +8841,7 @@
         <v>943.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7302,7 +8864,7 @@
         <v>523.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7325,7 +8887,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7348,7 +8910,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7371,7 +8933,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7394,7 +8956,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7417,7 +8979,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7440,7 +9002,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7463,7 +9025,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7486,7 +9048,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -7509,7 +9071,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -7532,7 +9094,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -7555,7 +9117,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -7578,7 +9140,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -7601,7 +9163,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7624,7 +9186,7 @@
         <v>453.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7647,7 +9209,7 @@
         <v>443.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7670,7 +9232,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7693,7 +9255,7 @@
         <v>653.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -7716,7 +9278,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -7739,7 +9301,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -7762,7 +9324,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -7785,7 +9347,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -7808,7 +9370,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -7831,7 +9393,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -7854,7 +9416,7 @@
         <v>35.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -7877,7 +9439,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -7900,7 +9462,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -7923,7 +9485,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -7946,7 +9508,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -7969,7 +9531,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -7992,7 +9554,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -8015,7 +9577,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -8038,7 +9600,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -8061,7 +9623,7 @@
         <v>37.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -8084,7 +9646,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -8113,11 +9675,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +9702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8163,7 +9725,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8186,7 +9748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8209,7 +9771,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8232,7 +9794,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8255,7 +9817,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8278,7 +9840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8301,7 +9863,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8324,7 +9886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8347,7 +9909,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8370,7 +9932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8393,7 +9955,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8416,7 +9978,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8439,7 +10001,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8462,7 +10024,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8485,7 +10047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8508,7 +10070,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8531,7 +10093,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8554,7 +10116,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8577,7 +10139,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8600,7 +10162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8623,7 +10185,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -8646,7 +10208,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8669,7 +10231,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8692,7 +10254,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8715,7 +10277,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8738,7 +10300,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8761,7 +10323,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8784,7 +10346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8807,7 +10369,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8830,7 +10392,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8853,7 +10415,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8876,7 +10438,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8899,7 +10461,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8922,7 +10484,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8945,7 +10507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8968,7 +10530,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8991,7 +10553,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9014,7 +10576,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -9037,7 +10599,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -9060,7 +10622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -9083,7 +10645,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -9106,7 +10668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -9129,7 +10691,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -9152,7 +10714,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -9175,7 +10737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -9198,7 +10760,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -9221,7 +10783,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -9244,7 +10806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -9267,7 +10829,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -9290,7 +10852,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -9313,7 +10875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -9336,7 +10898,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -9359,7 +10921,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -9382,7 +10944,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -9405,7 +10967,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -9428,7 +10990,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -9451,7 +11013,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -9474,7 +11036,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -9497,7 +11059,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -9520,7 +11082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -9543,7 +11105,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -9566,7 +11128,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -9589,7 +11151,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA066B3-29FF-4F0C-A074-4DA3640DAA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAD274F-60C7-45BA-9E5C-CB90F03FDB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="55">
   <si>
     <t>Jumlah Kombinasi</t>
   </si>
@@ -108,9 +108,6 @@
     <t>JPS-PPO</t>
   </si>
   <si>
-    <t>JPS-TPF</t>
-  </si>
-  <si>
     <t>TPF-PPO</t>
   </si>
   <si>
@@ -153,25 +150,13 @@
     <t>JPS-BDS-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-TPF</t>
-  </si>
-  <si>
     <t>JPS-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF</t>
   </si>
   <si>
     <t>JPS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-GL-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-BRC-TPF-PPO</t>
@@ -192,52 +177,19 @@
     <t>JPS-BDS-BRC-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC</t>
   </si>
   <si>
     <t>JPS-BDS-GL-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-GL-TPF-PPO</t>
   </si>
   <si>
     <t>BDS-GL-BRC-TPF-PPO</t>
   </si>
   <si>
-    <t>JPS-BDS-BRC-TPF-PPO</t>
-  </si>
-  <si>
     <t>JPS-BDS-GL-BRC-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-GL-BRC-TPF-PPO</t>
-  </si>
-  <si>
-    <t>JPS-BDS-GL-BRC-TPF-PPO</t>
   </si>
 </sst>
 </file>
@@ -333,32 +285,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Pecepatan</a:t>
-            </a:r>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -459,16 +385,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.8650000000000002E-4</c:v>
+                  <c:v>3.7740000000000012E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5612E-3</c:v>
+                  <c:v>2.4805999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.69623E-2</c:v>
+                  <c:v>1.5901999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.110197</c:v>
+                  <c:v>0.1046846</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -476,7 +402,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000000-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -545,16 +471,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.352E-4</c:v>
+                  <c:v>2.4309999999999989E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0061E-3</c:v>
+                  <c:v>9.7880000000000016E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3339999999999993E-3</c:v>
+                  <c:v>4.0415E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.7858200000000001E-2</c:v>
+                  <c:v>1.6605200000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -562,7 +488,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000001-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -631,16 +557,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.2789999999999999E-4</c:v>
+                  <c:v>4.1469999999999989E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5832000000000001E-3</c:v>
+                  <c:v>1.4946E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.7669000000000011E-3</c:v>
+                  <c:v>8.2117000000000023E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.6599900000000004E-2</c:v>
+                  <c:v>6.3046099999999994E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -648,7 +574,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000002-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -717,16 +643,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.2620000000000001E-4</c:v>
+                  <c:v>3.1710000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0154000000000001E-3</c:v>
+                  <c:v>1.8938E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.36829E-2</c:v>
+                  <c:v>1.28144E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.9039199999999999E-2</c:v>
+                  <c:v>8.4270999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -734,7 +660,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000003-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -803,16 +729,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.2739999999999998E-4</c:v>
+                  <c:v>4.4240000000000002E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3472E-3</c:v>
+                  <c:v>1.3186000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.0197000000000002E-3</c:v>
+                  <c:v>4.6888999999999993E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.15891E-2</c:v>
+                  <c:v>2.0214099999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -820,7 +746,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000004-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -889,16 +815,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.5029999999999999E-4</c:v>
+                  <c:v>4.1530000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6337000000000001E-3</c:v>
+                  <c:v>2.5517999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7054099999999999E-2</c:v>
+                  <c:v>1.6799000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1104907</c:v>
+                  <c:v>0.1053622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -906,7 +832,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000005-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -981,16 +907,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.2230000000000002E-4</c:v>
+                  <c:v>4.0360000000000011E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4174999999999999E-3</c:v>
+                  <c:v>2.2745999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.48261E-2</c:v>
+                  <c:v>1.40956E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.9208500000000005E-2</c:v>
+                  <c:v>9.3898200000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -998,7 +924,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-58D9-46F3-98EA-032C686D8C63}"/>
+              <c16:uniqueId val="{00000006-60DB-40DE-BFAC-2EDC9A2074EB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1026,11 +952,11 @@
         </c:hiLowLines>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="480179391"/>
-        <c:axId val="470352431"/>
+        <c:axId val="693605423"/>
+        <c:axId val="693605903"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="480179391"/>
+        <c:axId val="693605423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1103,7 +1029,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470352431"/>
+        <c:crossAx val="693605903"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1111,7 +1037,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="470352431"/>
+        <c:axId val="693605903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1192,7 +1118,7 @@
             <a:endParaRPr lang="id-ID"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480179391"/>
+        <c:crossAx val="693605423"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1826,23 +1752,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDED432-0F1B-A698-0F60-6FF65BA6E744}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{708ACB0B-8CB7-5EF8-1E6C-60130EA28C72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1866,7 +1792,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Red Orange">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1874,34 +1800,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="505046"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="E84C22"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="FFBD47"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="B64926"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FF8427"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="CC9900"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="B22600"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="CC9900"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="666699"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
@@ -2150,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -2184,19 +2110,19 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3.8650000000000002E-4</v>
+        <v>3.7740000000000012E-4</v>
       </c>
       <c r="D2">
-        <v>2.5612E-3</v>
+        <v>2.4805999999999999E-3</v>
       </c>
       <c r="E2">
-        <v>1.69623E-2</v>
+        <v>1.5901999999999999E-2</v>
       </c>
       <c r="F2">
-        <v>0.110197</v>
+        <v>0.1046846</v>
       </c>
       <c r="G2">
-        <v>3.2526749999999993E-2</v>
+        <v>3.086115E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -2207,19 +2133,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.352E-4</v>
+        <v>2.4309999999999989E-4</v>
       </c>
       <c r="D3">
-        <v>1.0061E-3</v>
+        <v>9.7880000000000016E-4</v>
       </c>
       <c r="E3">
-        <v>4.3339999999999993E-3</v>
+        <v>4.0415E-3</v>
       </c>
       <c r="F3">
-        <v>1.7858200000000001E-2</v>
+        <v>1.6605200000000001E-2</v>
       </c>
       <c r="G3">
-        <v>5.858374999999999E-3</v>
+        <v>5.4671499999999987E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2230,19 +2156,19 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4.2789999999999999E-4</v>
+        <v>4.1469999999999989E-4</v>
       </c>
       <c r="D4">
-        <v>1.5832000000000001E-3</v>
+        <v>1.4946E-3</v>
       </c>
       <c r="E4">
-        <v>8.7669000000000011E-3</v>
+        <v>8.2117000000000023E-3</v>
       </c>
       <c r="F4">
-        <v>6.6599900000000004E-2</v>
+        <v>6.3046099999999994E-2</v>
       </c>
       <c r="G4">
-        <v>1.9344475E-2</v>
+        <v>1.8291775E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2253,19 +2179,19 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>3.2620000000000001E-4</v>
+        <v>3.1710000000000001E-4</v>
       </c>
       <c r="D5">
-        <v>2.0154000000000001E-3</v>
+        <v>1.8938E-3</v>
       </c>
       <c r="E5">
-        <v>1.36829E-2</v>
+        <v>1.28144E-2</v>
       </c>
       <c r="F5">
-        <v>8.9039199999999999E-2</v>
+        <v>8.4270999999999999E-2</v>
       </c>
       <c r="G5">
-        <v>2.6265924999999999E-2</v>
+        <v>2.4824075000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2276,19 +2202,19 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>4.2739999999999998E-4</v>
+        <v>4.4240000000000002E-4</v>
       </c>
       <c r="D6">
-        <v>1.3472E-3</v>
+        <v>1.3186000000000001E-3</v>
       </c>
       <c r="E6">
-        <v>5.0197000000000002E-3</v>
+        <v>4.6888999999999993E-3</v>
       </c>
       <c r="F6">
-        <v>2.15891E-2</v>
+        <v>2.0214099999999999E-2</v>
       </c>
       <c r="G6">
-        <v>7.0958499999999999E-3</v>
+        <v>6.6660000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2299,19 +2225,19 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>4.5029999999999999E-4</v>
+        <v>4.1530000000000001E-4</v>
       </c>
       <c r="D7">
-        <v>2.6337000000000001E-3</v>
+        <v>2.5517999999999999E-3</v>
       </c>
       <c r="E7">
-        <v>1.7054099999999999E-2</v>
+        <v>1.6799000000000001E-2</v>
       </c>
       <c r="F7">
-        <v>0.1104907</v>
+        <v>0.1053622</v>
       </c>
       <c r="G7">
-        <v>3.2657199999999997E-2</v>
+        <v>3.1282074999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2322,19 +2248,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>4.2230000000000002E-4</v>
+        <v>4.0360000000000011E-4</v>
       </c>
       <c r="D8">
-        <v>2.4174999999999999E-3</v>
+        <v>2.2745999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>1.48261E-2</v>
+        <v>1.40956E-2</v>
       </c>
       <c r="F8">
-        <v>9.9208500000000005E-2</v>
+        <v>9.3898200000000001E-2</v>
       </c>
       <c r="G8">
-        <v>2.9218600000000001E-2</v>
+        <v>2.7668000000000002E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2345,19 +2271,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>3.1129999999999992E-4</v>
+        <v>3.1359999999999992E-4</v>
       </c>
       <c r="D9">
-        <v>1.1968E-3</v>
+        <v>1.2271000000000001E-3</v>
       </c>
       <c r="E9">
-        <v>4.6809E-3</v>
+        <v>4.5177000000000004E-3</v>
       </c>
       <c r="F9">
-        <v>2.1674600000000009E-2</v>
+        <v>2.0596199999999999E-2</v>
       </c>
       <c r="G9">
-        <v>6.9659000000000014E-3</v>
+        <v>6.6636500000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2368,19 +2294,19 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>2.051E-4</v>
+        <v>2.2100000000000001E-4</v>
       </c>
       <c r="D10">
-        <v>8.7469999999999996E-4</v>
+        <v>8.6260000000000004E-4</v>
       </c>
       <c r="E10">
-        <v>4.0442000000000004E-3</v>
+        <v>3.7323999999999999E-3</v>
       </c>
       <c r="F10">
-        <v>1.7460300000000002E-2</v>
+        <v>1.6401099999999998E-2</v>
       </c>
       <c r="G10">
-        <v>5.6460750000000004E-3</v>
+        <v>5.3042750000000007E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2391,19 +2317,19 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>2.812E-4</v>
+        <v>2.4879999999999998E-4</v>
       </c>
       <c r="D11">
-        <v>1.1000999999999999E-3</v>
+        <v>1.0869E-3</v>
       </c>
       <c r="E11">
-        <v>4.5352000000000014E-3</v>
+        <v>4.3001999999999997E-3</v>
       </c>
       <c r="F11">
-        <v>1.8587599999999999E-2</v>
+        <v>1.7132600000000001E-2</v>
       </c>
       <c r="G11">
-        <v>6.1260250000000002E-3</v>
+        <v>5.6921250000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2414,19 +2340,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>2.5060000000000002E-4</v>
+        <v>2.6150000000000012E-4</v>
       </c>
       <c r="D12">
-        <v>1.0769E-3</v>
+        <v>1.0522000000000001E-3</v>
       </c>
       <c r="E12">
-        <v>4.3631E-3</v>
+        <v>4.9437999999999999E-3</v>
       </c>
       <c r="F12">
-        <v>1.8370899999999999E-2</v>
+        <v>1.7220300000000001E-2</v>
       </c>
       <c r="G12">
-        <v>6.0153750000000008E-3</v>
+        <v>5.86945E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2437,19 +2363,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>5.0589999999999999E-4</v>
+        <v>4.5570000000000002E-4</v>
       </c>
       <c r="D13">
-        <v>1.7122999999999999E-3</v>
+        <v>1.6961000000000001E-3</v>
       </c>
       <c r="E13">
-        <v>8.9467999999999995E-3</v>
+        <v>8.3831999999999986E-3</v>
       </c>
       <c r="F13">
-        <v>6.7339100000000013E-2</v>
+        <v>6.2768099999999993E-2</v>
       </c>
       <c r="G13">
-        <v>1.9626024999999998E-2</v>
+        <v>1.8325774999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2460,19 +2386,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.3909999999999999E-4</v>
+        <v>4.4880000000000012E-4</v>
       </c>
       <c r="D14">
-        <v>2.3417999999999998E-3</v>
+        <v>2.2880000000000001E-3</v>
       </c>
       <c r="E14">
-        <v>1.0127199999999999E-2</v>
+        <v>9.6121000000000002E-3</v>
       </c>
       <c r="F14">
-        <v>9.5681599999999992E-2</v>
+        <v>9.1022999999999993E-2</v>
       </c>
       <c r="G14">
-        <v>2.7147424999999999E-2</v>
+        <v>2.5842975000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2483,19 +2409,19 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>5.1500000000000005E-4</v>
+        <v>4.8789999999999999E-4</v>
       </c>
       <c r="D15">
-        <v>1.8718000000000001E-3</v>
+        <v>1.7971E-3</v>
       </c>
       <c r="E15">
-        <v>1.0519799999999999E-2</v>
+        <v>9.8158000000000013E-3</v>
       </c>
       <c r="F15">
-        <v>6.7815099999999989E-2</v>
+        <v>6.3780300000000012E-2</v>
       </c>
       <c r="G15">
-        <v>2.0180424999999998E-2</v>
+        <v>1.8970275000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2506,19 +2432,19 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>3.8719999999999998E-4</v>
+        <v>4.105E-4</v>
       </c>
       <c r="D16">
-        <v>2.1209000000000002E-3</v>
+        <v>1.9686E-3</v>
       </c>
       <c r="E16">
-        <v>1.38365E-2</v>
+        <v>1.3065E-2</v>
       </c>
       <c r="F16">
-        <v>9.0079700000000013E-2</v>
+        <v>8.49192E-2</v>
       </c>
       <c r="G16">
-        <v>2.6606075E-2</v>
+        <v>2.5090825000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2529,19 +2455,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>3.7320000000000002E-4</v>
+        <v>3.6190000000000001E-4</v>
       </c>
       <c r="D17">
-        <v>2.2372999999999998E-3</v>
+        <v>2.0758999999999999E-3</v>
       </c>
       <c r="E17">
-        <v>1.35952E-2</v>
+        <v>1.27727E-2</v>
       </c>
       <c r="F17">
-        <v>8.4493900000000011E-2</v>
+        <v>7.9210799999999998E-2</v>
       </c>
       <c r="G17">
-        <v>2.51749E-2</v>
+        <v>2.3605325E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2552,19 +2478,19 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>2.9030000000000001E-4</v>
+        <v>3.0370000000000001E-4</v>
       </c>
       <c r="D18">
-        <v>9.6490000000000009E-4</v>
+        <v>9.2440000000000003E-4</v>
       </c>
       <c r="E18">
-        <v>4.1219000000000004E-3</v>
+        <v>3.9212000000000014E-3</v>
       </c>
       <c r="F18">
-        <v>1.60094E-2</v>
+        <v>1.4966E-2</v>
       </c>
       <c r="G18">
-        <v>5.3466249999999998E-3</v>
+        <v>5.0288250000000007E-3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2575,19 +2501,19 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.5619999999999998E-4</v>
+        <v>3.255E-4</v>
       </c>
       <c r="D19">
-        <v>6.8330000000000007E-4</v>
+        <v>6.6510000000000007E-4</v>
       </c>
       <c r="E19">
-        <v>1.9604000000000002E-3</v>
+        <v>1.8821E-3</v>
       </c>
       <c r="F19">
-        <v>7.7940000000000006E-3</v>
+        <v>7.3771999999999987E-3</v>
       </c>
       <c r="G19">
-        <v>2.6984750000000001E-3</v>
+        <v>2.5624749999999998E-3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2598,19 +2524,19 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>3.747E-4</v>
+        <v>3.613E-4</v>
       </c>
       <c r="D20">
-        <v>1.2193E-3</v>
+        <v>1.1864E-3</v>
       </c>
       <c r="E20">
-        <v>4.0626000000000004E-3</v>
+        <v>3.7368000000000002E-3</v>
       </c>
       <c r="F20">
-        <v>1.46006E-2</v>
+        <v>1.36928E-2</v>
       </c>
       <c r="G20">
-        <v>5.0642999999999999E-3</v>
+        <v>4.7443249999999998E-3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2621,19 +2547,19 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>4.7810000000000002E-4</v>
+        <v>4.5760000000000001E-4</v>
       </c>
       <c r="D21">
-        <v>1.4165E-3</v>
+        <v>1.3073E-3</v>
       </c>
       <c r="E21">
-        <v>5.0514000000000002E-3</v>
+        <v>4.7841999999999997E-3</v>
       </c>
       <c r="F21">
-        <v>2.16055E-2</v>
+        <v>2.0043800000000001E-2</v>
       </c>
       <c r="G21">
-        <v>7.1378750000000001E-3</v>
+        <v>6.6482250000000007E-3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2644,42 +2570,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>4.6630000000000011E-4</v>
+        <v>4.5750000000000001E-4</v>
       </c>
       <c r="D22">
-        <v>1.3659E-3</v>
+        <v>2.4611999999999989E-3</v>
       </c>
       <c r="E22">
-        <v>4.7604999999999991E-3</v>
+        <v>1.41183E-2</v>
       </c>
       <c r="F22">
-        <v>2.04785E-2</v>
+        <v>9.3971299999999994E-2</v>
       </c>
       <c r="G22">
-        <v>6.7677999999999992E-3</v>
+        <v>2.7752075000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>4.6930000000000002E-4</v>
+        <v>3.412E-4</v>
       </c>
       <c r="D23">
-        <v>2.568E-3</v>
+        <v>1.3068999999999999E-3</v>
       </c>
       <c r="E23">
-        <v>1.5358399999999999E-2</v>
+        <v>4.5806000000000006E-3</v>
       </c>
       <c r="F23">
-        <v>9.9814399999999998E-2</v>
+        <v>2.0691899999999999E-2</v>
       </c>
       <c r="G23">
-        <v>2.9552525E-2</v>
+        <v>6.7301499999999998E-3</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2690,19 +2616,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>3.57E-4</v>
+        <v>4.0020000000000002E-4</v>
       </c>
       <c r="D24">
-        <v>1.3277E-3</v>
+        <v>1.377E-3</v>
       </c>
       <c r="E24">
-        <v>4.9216999999999993E-3</v>
+        <v>5.4014999999999992E-3</v>
       </c>
       <c r="F24">
-        <v>2.2144799999999999E-2</v>
+        <v>2.6498299999999999E-2</v>
       </c>
       <c r="G24">
-        <v>7.1877999999999994E-3</v>
+        <v>8.4192499999999997E-3</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2713,19 +2639,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>3.8039999999999998E-4</v>
+        <v>3.4660000000000002E-4</v>
       </c>
       <c r="D25">
-        <v>1.4211E-3</v>
+        <v>1.3347999999999999E-3</v>
       </c>
       <c r="E25">
-        <v>5.6473999999999986E-3</v>
+        <v>6.3047999999999993E-3</v>
       </c>
       <c r="F25">
-        <v>2.8437899999999999E-2</v>
+        <v>3.5663500000000001E-2</v>
       </c>
       <c r="G25">
-        <v>8.9716999999999991E-3</v>
+        <v>1.0912425E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2736,19 +2662,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>3.4969999999999999E-4</v>
+        <v>2.3389999999999999E-4</v>
       </c>
       <c r="D26">
-        <v>1.4182000000000001E-3</v>
+        <v>9.1959999999999991E-4</v>
       </c>
       <c r="E26">
-        <v>6.8646000000000011E-3</v>
+        <v>3.8601E-3</v>
       </c>
       <c r="F26">
-        <v>3.8056199999999998E-2</v>
+        <v>1.73811E-2</v>
       </c>
       <c r="G26">
-        <v>1.1672175E-2</v>
+        <v>5.5986750000000009E-3</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2759,19 +2685,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>2.5109999999999998E-4</v>
+        <v>2.296E-4</v>
       </c>
       <c r="D27">
-        <v>9.7740000000000023E-4</v>
+        <v>9.8780000000000005E-4</v>
       </c>
       <c r="E27">
-        <v>4.2303000000000002E-3</v>
+        <v>3.9772000000000002E-3</v>
       </c>
       <c r="F27">
-        <v>1.8183899999999999E-2</v>
+        <v>1.6949499999999999E-2</v>
       </c>
       <c r="G27">
-        <v>5.9106750000000007E-3</v>
+        <v>5.536025E-3</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2782,19 +2708,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>2.6860000000000002E-4</v>
+        <v>3.0430000000000002E-4</v>
       </c>
       <c r="D28">
-        <v>9.5770000000000002E-4</v>
+        <v>1.1307000000000001E-3</v>
       </c>
       <c r="E28">
-        <v>4.1279999999999997E-3</v>
+        <v>4.3836999999999999E-3</v>
       </c>
       <c r="F28">
-        <v>1.7717199999999999E-2</v>
+        <v>1.7761200000000001E-2</v>
       </c>
       <c r="G28">
-        <v>5.7678749999999987E-3</v>
+        <v>5.8949749999999993E-3</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2805,19 +2731,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>3.0630000000000002E-4</v>
+        <v>5.0700000000000007E-4</v>
       </c>
       <c r="D29">
-        <v>1.1720000000000001E-3</v>
+        <v>2.3268E-3</v>
       </c>
       <c r="E29">
-        <v>4.5478999999999997E-3</v>
+        <v>9.9332999999999991E-3</v>
       </c>
       <c r="F29">
-        <v>1.9021E-2</v>
+        <v>9.2549800000000002E-2</v>
       </c>
       <c r="G29">
-        <v>6.2617999999999988E-3</v>
+        <v>2.6329225000000001E-2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2828,19 +2754,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>4.8910000000000002E-4</v>
+        <v>5.2720000000000002E-4</v>
       </c>
       <c r="D30">
-        <v>2.3506999999999998E-3</v>
+        <v>1.8767E-3</v>
       </c>
       <c r="E30">
-        <v>1.0331E-2</v>
+        <v>1.00535E-2</v>
       </c>
       <c r="F30">
-        <v>9.6409800000000004E-2</v>
+        <v>6.3950399999999991E-2</v>
       </c>
       <c r="G30">
-        <v>2.739515E-2</v>
+        <v>1.9101949999999999E-2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2851,19 +2777,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>5.4330000000000003E-4</v>
+        <v>4.9010000000000004E-4</v>
       </c>
       <c r="D31">
-        <v>1.9174000000000001E-3</v>
+        <v>1.8992E-3</v>
       </c>
       <c r="E31">
-        <v>1.07913E-2</v>
+        <v>1.00938E-2</v>
       </c>
       <c r="F31">
-        <v>6.8105900000000011E-2</v>
+        <v>6.5059400000000003E-2</v>
       </c>
       <c r="G31">
-        <v>2.0339474999999999E-2</v>
+        <v>1.9385625E-2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2874,19 +2800,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>4.6850000000000011E-4</v>
+        <v>4.0190000000000001E-4</v>
       </c>
       <c r="D32">
-        <v>1.9461000000000001E-3</v>
+        <v>2.1258000000000002E-3</v>
       </c>
       <c r="E32">
-        <v>1.06905E-2</v>
+        <v>1.27438E-2</v>
       </c>
       <c r="F32">
-        <v>6.8396299999999993E-2</v>
+        <v>7.9895900000000006E-2</v>
       </c>
       <c r="G32">
-        <v>2.037535E-2</v>
+        <v>2.379185E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2897,19 +2823,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>4.171E-4</v>
+        <v>3.2479999999999998E-4</v>
       </c>
       <c r="D33">
-        <v>2.2171999999999999E-3</v>
+        <v>7.3510000000000003E-4</v>
       </c>
       <c r="E33">
-        <v>1.3691E-2</v>
+        <v>2.2307999999999998E-3</v>
       </c>
       <c r="F33">
-        <v>8.48579E-2</v>
+        <v>9.0025999999999995E-3</v>
       </c>
       <c r="G33">
-        <v>2.52958E-2</v>
+        <v>3.073325E-3</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2920,19 +2846,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>3.0850000000000002E-4</v>
+        <v>2.4860000000000003E-4</v>
       </c>
       <c r="D34">
-        <v>7.5810000000000005E-4</v>
+        <v>8.7519999999999991E-4</v>
       </c>
       <c r="E34">
-        <v>2.3665000000000001E-3</v>
+        <v>2.634200000000001E-3</v>
       </c>
       <c r="F34">
-        <v>9.6824000000000007E-3</v>
+        <v>1.01519E-2</v>
       </c>
       <c r="G34">
-        <v>3.2788750000000001E-3</v>
+        <v>3.4774750000000011E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2943,19 +2869,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>2.498E-4</v>
+        <v>3.1300000000000002E-4</v>
       </c>
       <c r="D35">
-        <v>9.0819999999999996E-4</v>
+        <v>9.9259999999999995E-4</v>
       </c>
       <c r="E35">
-        <v>2.7964999999999999E-3</v>
+        <v>3.9971E-3</v>
       </c>
       <c r="F35">
-        <v>1.0708000000000001E-2</v>
+        <v>1.5155999999999999E-2</v>
       </c>
       <c r="G35">
-        <v>3.665625E-3</v>
+        <v>5.114675E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2966,19 +2892,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.3649999999999999E-4</v>
+        <v>3.9390000000000009E-4</v>
       </c>
       <c r="D36">
-        <v>1.0177000000000001E-3</v>
+        <v>7.3220000000000002E-4</v>
       </c>
       <c r="E36">
-        <v>4.2310000000000004E-3</v>
+        <v>1.89E-3</v>
       </c>
       <c r="F36">
-        <v>1.6158499999999999E-2</v>
+        <v>7.3714000000000002E-3</v>
       </c>
       <c r="G36">
-        <v>5.4359249999999986E-3</v>
+        <v>2.5968749999999998E-3</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2989,19 +2915,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>3.2360000000000001E-4</v>
+        <v>3.635E-4</v>
       </c>
       <c r="D37">
-        <v>8.5839999999999994E-4</v>
+        <v>9.0679999999999992E-4</v>
       </c>
       <c r="E37">
-        <v>3.3270999999999999E-3</v>
+        <v>2.4930999999999998E-3</v>
       </c>
       <c r="F37">
-        <v>1.38598E-2</v>
+        <v>9.791300000000001E-3</v>
       </c>
       <c r="G37">
-        <v>4.5922250000000001E-3</v>
+        <v>3.3886749999999998E-3</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -3012,134 +2938,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>3.8519999999999998E-4</v>
+        <v>4.0979999999999999E-4</v>
       </c>
       <c r="D38">
-        <v>7.4540000000000001E-4</v>
+        <v>1.2853999999999999E-3</v>
       </c>
       <c r="E38">
-        <v>2.0653999999999998E-3</v>
+        <v>3.8685E-3</v>
       </c>
       <c r="F38">
-        <v>7.9218000000000014E-3</v>
+        <v>1.4049499999999999E-2</v>
       </c>
       <c r="G38">
-        <v>2.7794500000000001E-3</v>
+        <v>4.9032999999999993E-3</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>3.4299999999999999E-4</v>
+        <v>3.9550000000000002E-4</v>
       </c>
       <c r="D39">
-        <v>6.7730000000000004E-4</v>
+        <v>1.5529999999999999E-3</v>
       </c>
       <c r="E39">
-        <v>2.0195999999999999E-3</v>
+        <v>5.5418999999999998E-3</v>
       </c>
       <c r="F39">
-        <v>7.7637000000000001E-3</v>
+        <v>2.7463100000000001E-2</v>
       </c>
       <c r="G39">
-        <v>2.7009E-3</v>
+        <v>8.7383749999999996E-3</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>3.6979999999999999E-4</v>
+        <v>3.6309999999999999E-4</v>
       </c>
       <c r="D40">
-        <v>9.4929999999999993E-4</v>
+        <v>1.5108000000000001E-3</v>
       </c>
       <c r="E40">
-        <v>2.6348000000000001E-3</v>
+        <v>6.8602999999999997E-3</v>
       </c>
       <c r="F40">
-        <v>1.04215E-2</v>
+        <v>3.7648599999999997E-2</v>
       </c>
       <c r="G40">
-        <v>3.59385E-3</v>
+        <v>1.15957E-2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>4.327E-4</v>
+        <v>3.5970000000000002E-4</v>
       </c>
       <c r="D41">
-        <v>1.3071000000000001E-3</v>
+        <v>1.5156E-3</v>
       </c>
       <c r="E41">
-        <v>4.1280000000000006E-3</v>
+        <v>6.6635000000000002E-3</v>
       </c>
       <c r="F41">
-        <v>1.4741000000000001E-2</v>
+        <v>3.4248199999999993E-2</v>
       </c>
       <c r="G41">
-        <v>5.1522E-3</v>
+        <v>1.069675E-2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>3.994E-4</v>
+        <v>2.8729999999999999E-4</v>
       </c>
       <c r="D42">
-        <v>1.2646999999999999E-3</v>
+        <v>1.0277999999999999E-3</v>
       </c>
       <c r="E42">
-        <v>4.0002000000000006E-3</v>
+        <v>4.1537999999999992E-3</v>
       </c>
       <c r="F42">
-        <v>1.5070200000000001E-2</v>
+        <v>1.7581300000000001E-2</v>
       </c>
       <c r="G42">
-        <v>5.1836250000000007E-3</v>
+        <v>5.76255E-3</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.0040000000000002E-4</v>
+        <v>5.4379999999999999E-4</v>
       </c>
       <c r="D43">
-        <v>1.4257E-3</v>
+        <v>2.026E-3</v>
       </c>
       <c r="E43">
-        <v>4.8311999999999999E-3</v>
+        <v>1.04452E-2</v>
       </c>
       <c r="F43">
-        <v>2.0591399999999999E-2</v>
+        <v>6.6992499999999996E-2</v>
       </c>
       <c r="G43">
-        <v>6.837175E-3</v>
+        <v>2.0001874999999999E-2</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -3150,19 +3076,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>4.1869999999999999E-4</v>
+        <v>3.3270000000000001E-4</v>
       </c>
       <c r="D44">
-        <v>1.5562E-3</v>
+        <v>8.0160000000000008E-4</v>
       </c>
       <c r="E44">
-        <v>5.8872999999999998E-3</v>
+        <v>2.3365999999999999E-3</v>
       </c>
       <c r="F44">
-        <v>2.9291999999999999E-2</v>
+        <v>9.0867000000000014E-3</v>
       </c>
       <c r="G44">
-        <v>9.2885499999999996E-3</v>
+        <v>3.139400000000001E-3</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -3173,19 +3099,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>4.037E-4</v>
+        <v>3.4390000000000001E-4</v>
       </c>
       <c r="D45">
-        <v>1.5081999999999999E-3</v>
+        <v>1.0326999999999999E-3</v>
       </c>
       <c r="E45">
-        <v>7.0943000000000004E-3</v>
+        <v>2.9713000000000009E-3</v>
       </c>
       <c r="F45">
-        <v>3.8730199999999999E-2</v>
+        <v>1.0685500000000001E-2</v>
       </c>
       <c r="G45">
-        <v>1.19341E-2</v>
+        <v>3.7583500000000001E-3</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -3196,19 +3122,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>3.9800000000000002E-4</v>
+        <v>2.7099999999999997E-4</v>
       </c>
       <c r="D46">
-        <v>1.4909999999999999E-3</v>
+        <v>9.1430000000000005E-4</v>
       </c>
       <c r="E46">
-        <v>6.7891999999999996E-3</v>
+        <v>2.7100000000000002E-3</v>
       </c>
       <c r="F46">
-        <v>3.5798000000000003E-2</v>
+        <v>1.02296E-2</v>
       </c>
       <c r="G46">
-        <v>1.111905E-2</v>
+        <v>3.5312249999999998E-3</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -3219,433 +3145,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>3.1280000000000001E-4</v>
+        <v>3.6650000000000002E-4</v>
       </c>
       <c r="D47">
-        <v>1.0612E-3</v>
+        <v>9.0700000000000004E-4</v>
       </c>
       <c r="E47">
-        <v>4.3926999999999994E-3</v>
+        <v>2.6023000000000001E-3</v>
       </c>
       <c r="F47">
-        <v>1.84484E-2</v>
+        <v>1.00707E-2</v>
       </c>
       <c r="G47">
-        <v>6.0537749999999991E-3</v>
+        <v>3.4866250000000001E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>5.2570000000000004E-4</v>
+        <v>3.8020000000000003E-4</v>
       </c>
       <c r="D48">
-        <v>2.0339999999999998E-3</v>
+        <v>1.6184999999999999E-3</v>
       </c>
       <c r="E48">
-        <v>1.13156E-2</v>
+        <v>6.7567E-3</v>
       </c>
       <c r="F48">
-        <v>6.9092300000000009E-2</v>
+        <v>3.5299200000000003E-2</v>
       </c>
       <c r="G48">
-        <v>2.0741900000000001E-2</v>
+        <v>1.101365E-2</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>3.5349999999999997E-4</v>
+        <v>3.3720000000000001E-4</v>
       </c>
       <c r="D49">
-        <v>8.3569999999999998E-4</v>
+        <v>1.1295999999999999E-3</v>
       </c>
       <c r="E49">
-        <v>2.4978000000000001E-3</v>
+        <v>2.9031999999999999E-3</v>
       </c>
       <c r="F49">
-        <v>9.8364999999999998E-3</v>
+        <v>1.0902800000000001E-2</v>
       </c>
       <c r="G49">
-        <v>3.3808750000000002E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>3.4850000000000001E-4</v>
-      </c>
-      <c r="D50">
-        <v>9.8240000000000003E-4</v>
-      </c>
-      <c r="E50">
-        <v>3.4009999999999999E-3</v>
-      </c>
-      <c r="F50">
-        <v>1.1638300000000001E-2</v>
-      </c>
-      <c r="G50">
-        <v>4.0925499999999986E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>3.2459999999999998E-4</v>
-      </c>
-      <c r="D51">
-        <v>1.0713999999999999E-3</v>
-      </c>
-      <c r="E51">
-        <v>3.0593999999999999E-3</v>
-      </c>
-      <c r="F51">
-        <v>1.1533399999999999E-2</v>
-      </c>
-      <c r="G51">
-        <v>3.9971999999999994E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>2.9359999999999998E-4</v>
-      </c>
-      <c r="D52">
-        <v>9.4650000000000008E-4</v>
-      </c>
-      <c r="E52">
-        <v>2.8779999999999999E-3</v>
-      </c>
-      <c r="F52">
-        <v>1.0836699999999999E-2</v>
-      </c>
-      <c r="G52">
-        <v>3.7387000000000002E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>3.143E-4</v>
-      </c>
-      <c r="D53">
-        <v>9.337000000000002E-4</v>
-      </c>
-      <c r="E53">
-        <v>3.4889999999999999E-3</v>
-      </c>
-      <c r="F53">
-        <v>1.7440500000000001E-2</v>
-      </c>
-      <c r="G53">
-        <v>5.5443750000000007E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>3.7280000000000012E-4</v>
-      </c>
-      <c r="D54">
-        <v>9.5510000000000007E-4</v>
-      </c>
-      <c r="E54">
-        <v>3.4294E-3</v>
-      </c>
-      <c r="F54">
-        <v>1.40676E-2</v>
-      </c>
-      <c r="G54">
-        <v>4.7062249999999996E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>3.9950000000000001E-4</v>
-      </c>
-      <c r="D55">
-        <v>7.9159999999999994E-4</v>
-      </c>
-      <c r="E55">
-        <v>2.1413999999999999E-3</v>
-      </c>
-      <c r="F55">
-        <v>7.8890000000000019E-3</v>
-      </c>
-      <c r="G55">
-        <v>2.805375000000001E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>3.9539999999999991E-4</v>
-      </c>
-      <c r="D56">
-        <v>9.8630000000000007E-4</v>
-      </c>
-      <c r="E56">
-        <v>2.7350999999999999E-3</v>
-      </c>
-      <c r="F56">
-        <v>1.06295E-2</v>
-      </c>
-      <c r="G56">
-        <v>3.6865750000000001E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>3.6099999999999999E-4</v>
-      </c>
-      <c r="D57">
-        <v>9.3629999999999994E-4</v>
-      </c>
-      <c r="E57">
-        <v>2.7068999999999999E-3</v>
-      </c>
-      <c r="F57">
-        <v>1.0485299999999999E-2</v>
-      </c>
-      <c r="G57">
-        <v>3.6223750000000002E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>4.3490000000000011E-4</v>
-      </c>
-      <c r="D58">
-        <v>1.3144999999999999E-3</v>
-      </c>
-      <c r="E58">
-        <v>4.0983E-3</v>
-      </c>
-      <c r="F58">
-        <v>1.5196100000000001E-2</v>
-      </c>
-      <c r="G58">
-        <v>5.2609499999999986E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>4.1960000000000001E-4</v>
-      </c>
-      <c r="D59">
-        <v>1.6225E-3</v>
-      </c>
-      <c r="E59">
-        <v>7.1785E-3</v>
-      </c>
-      <c r="F59">
-        <v>3.6214700000000002E-2</v>
-      </c>
-      <c r="G59">
-        <v>1.1358824999999999E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>3.9439999999999988E-4</v>
-      </c>
-      <c r="D60">
-        <v>1.0487000000000001E-3</v>
-      </c>
-      <c r="E60">
-        <v>3.5046999999999999E-3</v>
-      </c>
-      <c r="F60">
-        <v>1.17286E-2</v>
-      </c>
-      <c r="G60">
-        <v>4.1691000000000002E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>3.8259999999999998E-4</v>
-      </c>
-      <c r="D61">
-        <v>1.2117E-3</v>
-      </c>
-      <c r="E61">
-        <v>3.1706999999999998E-3</v>
-      </c>
-      <c r="F61">
-        <v>1.1731699999999999E-2</v>
-      </c>
-      <c r="G61">
-        <v>4.1241750000000008E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>3.3730000000000001E-4</v>
-      </c>
-      <c r="D62">
-        <v>1.0637999999999999E-3</v>
-      </c>
-      <c r="E62">
-        <v>3.7087000000000001E-3</v>
-      </c>
-      <c r="F62">
-        <v>1.7866300000000002E-2</v>
-      </c>
-      <c r="G62">
-        <v>5.7440250000000007E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>3.5570000000000003E-4</v>
-      </c>
-      <c r="D63">
-        <v>9.7330000000000008E-4</v>
-      </c>
-      <c r="E63">
-        <v>3.6327E-3</v>
-      </c>
-      <c r="F63">
-        <v>1.7652899999999999E-2</v>
-      </c>
-      <c r="G63">
-        <v>5.6536499999999996E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>4.1580000000000002E-4</v>
-      </c>
-      <c r="D64">
-        <v>9.9209999999999988E-4</v>
-      </c>
-      <c r="E64">
-        <v>2.7417000000000001E-3</v>
-      </c>
-      <c r="F64">
-        <v>1.06456E-2</v>
-      </c>
-      <c r="G64">
-        <v>3.6987999999999999E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>3.8210000000000002E-4</v>
-      </c>
-      <c r="D65">
-        <v>1.0941E-3</v>
-      </c>
-      <c r="E65">
-        <v>3.7258999999999999E-3</v>
-      </c>
-      <c r="F65">
-        <v>1.8060400000000001E-2</v>
-      </c>
-      <c r="G65">
-        <v>5.8156249999999996E-3</v>
+        <v>3.8181999999999999E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3656,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -3969,7 +3527,7 @@
         <v>24</v>
       </c>
       <c r="D14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14">
         <v>108</v>
@@ -3978,7 +3536,7 @@
         <v>218</v>
       </c>
       <c r="G14">
-        <v>100.5</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -4150,42 +3708,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D22">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>21.75</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F23">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G23">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -4196,19 +3754,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="G24">
-        <v>16.5</v>
+        <v>95.75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -4222,16 +3780,16 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E25">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F25">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G25">
-        <v>95.75</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4242,19 +3800,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D26">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="F26">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="G26">
-        <v>90.5</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4265,19 +3823,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="G27">
-        <v>16.75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -4288,19 +3846,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E28">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>192</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -4311,19 +3869,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29">
         <v>15</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4343,10 +3901,10 @@
         <v>16</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -4357,19 +3915,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="F31">
-        <v>17</v>
+        <v>197</v>
       </c>
       <c r="G31">
-        <v>16.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -4380,19 +3938,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D32">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E32">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="G32">
-        <v>92</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -4403,19 +3961,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D33">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>15</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -4426,7 +3984,7 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D34">
         <v>24</v>
@@ -4438,7 +3996,7 @@
         <v>24</v>
       </c>
       <c r="G34">
-        <v>22.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -4449,19 +4007,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D35">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>22.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -4475,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36">
         <v>15</v>
@@ -4484,7 +4042,7 @@
         <v>15</v>
       </c>
       <c r="G36">
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -4495,19 +4053,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G37">
-        <v>18.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -4521,7 +4079,7 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>15</v>
@@ -4530,122 +4088,122 @@
         <v>15</v>
       </c>
       <c r="G38">
-        <v>15.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D39">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E39">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G39">
-        <v>23</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D40">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G40">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="F41">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D42">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G42">
-        <v>22.5</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F43">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G43">
-        <v>14</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -4656,19 +4214,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F44">
         <v>15</v>
       </c>
       <c r="G44">
-        <v>15.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -4679,19 +4237,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D45">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E45">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G45">
-        <v>16.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -4702,19 +4260,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D46">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E46">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G46">
-        <v>91</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -4725,7 +4283,7 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>17</v>
@@ -4737,12 +4295,12 @@
         <v>17</v>
       </c>
       <c r="G47">
-        <v>16.75</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -4765,393 +4323,25 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>17</v>
-      </c>
-      <c r="D50">
-        <v>19</v>
-      </c>
-      <c r="E50">
-        <v>19</v>
-      </c>
-      <c r="F50">
-        <v>22</v>
-      </c>
-      <c r="G50">
-        <v>19.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>19</v>
-      </c>
-      <c r="D51">
-        <v>24</v>
-      </c>
-      <c r="E51">
-        <v>24</v>
-      </c>
-      <c r="F51">
-        <v>24</v>
-      </c>
-      <c r="G51">
-        <v>22.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
         <v>16</v>
-      </c>
-      <c r="D52">
-        <v>16</v>
-      </c>
-      <c r="E52">
-        <v>16</v>
-      </c>
-      <c r="F52">
-        <v>16</v>
-      </c>
-      <c r="G52">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>19</v>
-      </c>
-      <c r="D53">
-        <v>24</v>
-      </c>
-      <c r="E53">
-        <v>24</v>
-      </c>
-      <c r="F53">
-        <v>22</v>
-      </c>
-      <c r="G53">
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>15</v>
-      </c>
-      <c r="D54">
-        <v>9</v>
-      </c>
-      <c r="E54">
-        <v>9</v>
-      </c>
-      <c r="F54">
-        <v>9</v>
-      </c>
-      <c r="G54">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>15</v>
-      </c>
-      <c r="D55">
-        <v>17</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-      <c r="F55">
-        <v>15</v>
-      </c>
-      <c r="G55">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>15</v>
-      </c>
-      <c r="D56">
-        <v>17</v>
-      </c>
-      <c r="E56">
-        <v>17</v>
-      </c>
-      <c r="F56">
-        <v>17</v>
-      </c>
-      <c r="G56">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>19</v>
-      </c>
-      <c r="D57">
-        <v>25</v>
-      </c>
-      <c r="E57">
-        <v>25</v>
-      </c>
-      <c r="F57">
-        <v>25</v>
-      </c>
-      <c r="G57">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>15</v>
-      </c>
-      <c r="D58">
-        <v>15</v>
-      </c>
-      <c r="E58">
-        <v>15</v>
-      </c>
-      <c r="F58">
-        <v>15</v>
-      </c>
-      <c r="G58">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>16</v>
-      </c>
-      <c r="D59">
-        <v>17</v>
-      </c>
-      <c r="E59">
-        <v>17</v>
-      </c>
-      <c r="F59">
-        <v>17</v>
-      </c>
-      <c r="G59">
-        <v>16.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>15</v>
-      </c>
-      <c r="D60">
-        <v>9</v>
-      </c>
-      <c r="E60">
-        <v>9</v>
-      </c>
-      <c r="F60">
-        <v>13</v>
-      </c>
-      <c r="G60">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>16</v>
-      </c>
-      <c r="D61">
-        <v>16</v>
-      </c>
-      <c r="E61">
-        <v>16</v>
-      </c>
-      <c r="F61">
-        <v>16</v>
-      </c>
-      <c r="G61">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>19</v>
-      </c>
-      <c r="D62">
-        <v>24</v>
-      </c>
-      <c r="E62">
-        <v>24</v>
-      </c>
-      <c r="F62">
-        <v>22</v>
-      </c>
-      <c r="G62">
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>16</v>
-      </c>
-      <c r="D63">
-        <v>16</v>
-      </c>
-      <c r="E63">
-        <v>15</v>
-      </c>
-      <c r="F63">
-        <v>13</v>
-      </c>
-      <c r="G63">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>15</v>
-      </c>
-      <c r="D64">
-        <v>17</v>
-      </c>
-      <c r="E64">
-        <v>17</v>
-      </c>
-      <c r="F64">
-        <v>17</v>
-      </c>
-      <c r="G64">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>16</v>
-      </c>
-      <c r="D65">
-        <v>16</v>
-      </c>
-      <c r="E65">
-        <v>16</v>
-      </c>
-      <c r="F65">
-        <v>13</v>
-      </c>
-      <c r="G65">
-        <v>15.25</v>
       </c>
     </row>
   </sheetData>
@@ -5161,7 +4351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -5474,7 +4664,7 @@
         <v>26.727922061357859</v>
       </c>
       <c r="D14">
-        <v>57.213203435596412</v>
+        <v>57.798989873223341</v>
       </c>
       <c r="E14">
         <v>117.35533905932741</v>
@@ -5483,7 +4673,7 @@
         <v>237.29646455628159</v>
       </c>
       <c r="G14">
-        <v>109.6482322781408</v>
+        <v>109.79467888754751</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -5658,39 +4848,39 @@
         <v>25.313708498984759</v>
       </c>
       <c r="D22">
-        <v>52.041630560342618</v>
+        <v>49.846941716980723</v>
       </c>
       <c r="E22">
-        <v>105.4974746830583</v>
+        <v>101.47397718311861</v>
       </c>
       <c r="F22">
-        <v>212.40916292848979</v>
+        <v>204.98245579924691</v>
       </c>
       <c r="G22">
-        <v>98.815494167718867</v>
+        <v>95.404270799582747</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D23">
-        <v>49.846941716980723</v>
+        <v>53.831713714764781</v>
       </c>
       <c r="E23">
-        <v>101.47397718311861</v>
+        <v>107.0191148045464</v>
       </c>
       <c r="F23">
-        <v>204.98245579924691</v>
+        <v>216.31798086904371</v>
       </c>
       <c r="G23">
-        <v>95.404270799582747</v>
+        <v>100.9296464662099</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -5701,19 +4891,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>26.54977647648456</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D24">
-        <v>53.831713714764781</v>
+        <v>56.627416997969519</v>
       </c>
       <c r="E24">
-        <v>107.0191148045464</v>
+        <v>113.8406204335659</v>
       </c>
       <c r="F24">
-        <v>216.31798086904371</v>
+        <v>230.26702730475881</v>
       </c>
       <c r="G24">
-        <v>100.9296464662099</v>
+        <v>106.86574669941299</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -5727,16 +4917,16 @@
         <v>26.727922061357859</v>
       </c>
       <c r="D25">
-        <v>56.627416997969519</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E25">
-        <v>113.8406204335659</v>
+        <v>110.6690475583121</v>
       </c>
       <c r="F25">
-        <v>230.26702730475881</v>
+        <v>219.58073580374361</v>
       </c>
       <c r="G25">
-        <v>106.86574669941299</v>
+        <v>102.75483399593899</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -5747,19 +4937,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>26.727922061357859</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D26">
-        <v>54.041630560342618</v>
+        <v>52.181907122806606</v>
       </c>
       <c r="E26">
-        <v>110.6690475583121</v>
+        <v>104.11728699804451</v>
       </c>
       <c r="F26">
-        <v>219.58073580374361</v>
+        <v>208.24061365691611</v>
       </c>
       <c r="G26">
-        <v>102.75483399593899</v>
+        <v>97.772396063562951</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -5770,19 +4960,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>26.54977647648456</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D27">
-        <v>52.181907122806606</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E27">
-        <v>104.11728699804451</v>
+        <v>109.4974746830583</v>
       </c>
       <c r="F27">
-        <v>208.24061365691611</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G27">
-        <v>97.772396063562951</v>
+        <v>102.25483399593899</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -5793,19 +4983,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>26.727922061357859</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D28">
-        <v>54.87005768508881</v>
+        <v>50.445063357834727</v>
       </c>
       <c r="E28">
-        <v>109.4974746830583</v>
+        <v>102.0661260637976</v>
       </c>
       <c r="F28">
-        <v>217.92388155425121</v>
+        <v>205.49070842301589</v>
       </c>
       <c r="G28">
-        <v>102.25483399593899</v>
+        <v>95.828901585908241</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -5816,19 +5006,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D29">
-        <v>50.445063357834727</v>
+        <v>55.193957223724922</v>
       </c>
       <c r="E29">
-        <v>102.0661260637976</v>
+        <v>109.8662799826854</v>
       </c>
       <c r="F29">
-        <v>205.49070842301589</v>
+        <v>222.1080327222457</v>
       </c>
       <c r="G29">
-        <v>95.828901585908241</v>
+        <v>103.4295116012851</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -5842,16 +5032,16 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D30">
-        <v>54.333319832637137</v>
+        <v>52.49710117158692</v>
       </c>
       <c r="E30">
-        <v>109.8662799826854</v>
+        <v>105.0403618691834</v>
       </c>
       <c r="F30">
-        <v>222.1080327222457</v>
+        <v>211.73407903147461</v>
       </c>
       <c r="G30">
-        <v>103.2143522535132</v>
+        <v>98.955329637182359</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -5862,19 +5052,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>26.54977647648456</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D31">
-        <v>52.49710117158692</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E31">
-        <v>105.0403618691834</v>
+        <v>111.25483399593899</v>
       </c>
       <c r="F31">
-        <v>211.73407903147461</v>
+        <v>224.9949493661166</v>
       </c>
       <c r="G31">
-        <v>98.955329637182359</v>
+        <v>104.25483399593899</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -5885,19 +5075,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>26.727922061357859</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D32">
-        <v>54.041630560342618</v>
+        <v>50.536273206137643</v>
       </c>
       <c r="E32">
-        <v>111.25483399593899</v>
+        <v>101.5116887917378</v>
       </c>
       <c r="F32">
-        <v>224.9949493661166</v>
+        <v>203.62020384855049</v>
       </c>
       <c r="G32">
-        <v>104.25483399593899</v>
+        <v>95.245468586352686</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -5911,16 +5101,16 @@
         <v>25.313708498984759</v>
       </c>
       <c r="D33">
-        <v>50.536273206137643</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E33">
-        <v>101.5116887917378</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="F33">
-        <v>203.62020384855049</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G33">
-        <v>95.245468586352686</v>
+        <v>98.815494167718867</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -5931,19 +5121,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>25.313708498984759</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D34">
-        <v>52.041630560342618</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E34">
-        <v>105.4974746830583</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F34">
-        <v>212.40916292848979</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G34">
-        <v>98.815494167718867</v>
+        <v>101.8406204335659</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -5954,19 +5144,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>26.727922061357859</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D35">
-        <v>54.041630560342618</v>
+        <v>50.942677103220838</v>
       </c>
       <c r="E35">
-        <v>108.6690475583121</v>
+        <v>102.6712897929513</v>
       </c>
       <c r="F35">
-        <v>217.92388155425121</v>
+        <v>206.2505164179251</v>
       </c>
       <c r="G35">
-        <v>101.8406204335659</v>
+        <v>96.294547953270495</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5980,16 +5170,16 @@
         <v>25.313708498984759</v>
       </c>
       <c r="D36">
-        <v>50.942677103220838</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E36">
-        <v>102.6712897929513</v>
+        <v>104.870607101803</v>
       </c>
       <c r="F36">
-        <v>206.2505164179251</v>
+        <v>211.062613349125</v>
       </c>
       <c r="G36">
-        <v>96.294547953270495</v>
+        <v>98.759155902012651</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -6003,16 +5193,16 @@
         <v>25.313708498984759</v>
       </c>
       <c r="D37">
-        <v>54.384776310850228</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E37">
-        <v>110.1837661840736</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F37">
-        <v>221.7817459305202</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G37">
-        <v>102.91599923110719</v>
+        <v>101.4870670429727</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -6026,7 +5216,7 @@
         <v>25.313708498984759</v>
       </c>
       <c r="D38">
-        <v>53.789694658137911</v>
+        <v>51.789694658137911</v>
       </c>
       <c r="E38">
         <v>104.870607101803</v>
@@ -6035,122 +5225,122 @@
         <v>211.062613349125</v>
       </c>
       <c r="G38">
-        <v>98.759155902012651</v>
+        <v>98.259155902012651</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D39">
-        <v>54.041630560342618</v>
+        <v>54.038067022199172</v>
       </c>
       <c r="E39">
-        <v>105.4974746830583</v>
+        <v>108.66299557933429</v>
       </c>
       <c r="F39">
-        <v>212.40916292848979</v>
+        <v>219.4050796727812</v>
       </c>
       <c r="G39">
-        <v>99.315494167718867</v>
+        <v>102.16397968769979</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D40">
-        <v>54.041630560342618</v>
+        <v>52.49710117158692</v>
       </c>
       <c r="E40">
-        <v>108.6690475583121</v>
+        <v>104.7154540633544</v>
       </c>
       <c r="F40">
-        <v>217.92388155425121</v>
+        <v>211.29746103441209</v>
       </c>
       <c r="G40">
-        <v>101.4870670429727</v>
+        <v>98.764948186459506</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>25.313708498984759</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D41">
-        <v>51.789694658137911</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E41">
-        <v>104.870607101803</v>
+        <v>110.6690475583121</v>
       </c>
       <c r="F41">
-        <v>211.062613349125</v>
+        <v>223.23759005323589</v>
       </c>
       <c r="G41">
-        <v>98.259155902012651</v>
+        <v>103.6690475583121</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D42">
-        <v>52.041630560342618</v>
+        <v>52.181907122806606</v>
       </c>
       <c r="E42">
-        <v>105.4974746830583</v>
+        <v>104.5993450099368</v>
       </c>
       <c r="F42">
-        <v>212.40916292848979</v>
+        <v>208.24061365691611</v>
       </c>
       <c r="G42">
-        <v>98.815494167718867</v>
+        <v>97.892910566535988</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D43">
-        <v>51.789694658137911</v>
+        <v>52.49710117158692</v>
       </c>
       <c r="E43">
-        <v>104.870607101803</v>
+        <v>105.0924763437464</v>
       </c>
       <c r="F43">
-        <v>211.062613349125</v>
+        <v>213.87174654405101</v>
       </c>
       <c r="G43">
-        <v>98.259155902012651</v>
+        <v>99.502775133967219</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6161,19 +5351,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>26.54977647648456</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D44">
-        <v>54.038067022199172</v>
+        <v>51.285822853728483</v>
       </c>
       <c r="E44">
-        <v>108.66299557933429</v>
+        <v>103.6168719392922</v>
       </c>
       <c r="F44">
-        <v>219.4050796727812</v>
+        <v>208.36951419039531</v>
       </c>
       <c r="G44">
-        <v>102.16397968769979</v>
+        <v>97.14647937060019</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -6184,19 +5374,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>26.54977647648456</v>
+        <v>26.727922061357859</v>
       </c>
       <c r="D45">
-        <v>52.49710117158692</v>
+        <v>54.041630560342618</v>
       </c>
       <c r="E45">
-        <v>104.7154540633544</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F45">
-        <v>211.29746103441209</v>
+        <v>217.92388155425121</v>
       </c>
       <c r="G45">
-        <v>98.764948186459506</v>
+        <v>101.8406204335659</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -6207,19 +5397,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>26.727922061357859</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D46">
-        <v>54.041630560342618</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E46">
-        <v>110.6690475583121</v>
+        <v>106.8493377268543</v>
       </c>
       <c r="F46">
-        <v>223.23759005323589</v>
+        <v>214.33647357812561</v>
       </c>
       <c r="G46">
-        <v>103.6690475583121</v>
+        <v>100.30854362571171</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -6230,24 +5420,24 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>26.54977647648456</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D47">
-        <v>52.181907122806606</v>
+        <v>53.789694658137911</v>
       </c>
       <c r="E47">
-        <v>104.3277853366118</v>
+        <v>108.0421799770567</v>
       </c>
       <c r="F47">
-        <v>208.24061365691611</v>
+        <v>216.57733197488639</v>
       </c>
       <c r="G47">
-        <v>97.82502064820477</v>
+        <v>100.9307287772664</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -6259,404 +5449,36 @@
         <v>52.49710117158692</v>
       </c>
       <c r="E48">
-        <v>105.0924763437464</v>
+        <v>104.7675685379174</v>
       </c>
       <c r="F48">
-        <v>213.87174654405101</v>
+        <v>213.43512854698861</v>
       </c>
       <c r="G48">
-        <v>99.502775133967219</v>
+        <v>99.312393683244352</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>25.313708498984759</v>
+        <v>26.54977647648456</v>
       </c>
       <c r="D49">
-        <v>51.285822853728483</v>
+        <v>53.498586721382473</v>
       </c>
       <c r="E49">
-        <v>103.6168719392922</v>
+        <v>106.8493377268543</v>
       </c>
       <c r="F49">
-        <v>208.36951419039531</v>
+        <v>214.33647357812561</v>
       </c>
       <c r="G49">
-        <v>97.14647937060019</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D50">
-        <v>54.384776310850228</v>
-      </c>
-      <c r="E50">
-        <v>110.1837661840736</v>
-      </c>
-      <c r="F50">
-        <v>254.61017305526639</v>
-      </c>
-      <c r="G50">
-        <v>111.1231060122937</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D51">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E51">
-        <v>108.6690475583121</v>
-      </c>
-      <c r="F51">
-        <v>217.92388155425121</v>
-      </c>
-      <c r="G51">
-        <v>101.8406204335659</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>26.54977647648456</v>
-      </c>
-      <c r="D52">
-        <v>53.498586721382473</v>
-      </c>
-      <c r="E52">
-        <v>106.8493377268543</v>
-      </c>
-      <c r="F52">
-        <v>214.33647357812561</v>
-      </c>
-      <c r="G52">
         <v>100.30854362571171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D53">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E53">
-        <v>105.4974746830583</v>
-      </c>
-      <c r="F53">
-        <v>212.40916292848979</v>
-      </c>
-      <c r="G53">
-        <v>99.669047558312144</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D54">
-        <v>53.369115684745083</v>
-      </c>
-      <c r="E54">
-        <v>107.3529870742077</v>
-      </c>
-      <c r="F54">
-        <v>215.38939181604201</v>
-      </c>
-      <c r="G54">
-        <v>100.3563007684949</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D55">
-        <v>53.789694658137911</v>
-      </c>
-      <c r="E55">
-        <v>104.870607101803</v>
-      </c>
-      <c r="F55">
-        <v>211.062613349125</v>
-      </c>
-      <c r="G55">
-        <v>98.759155902012651</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D56">
-        <v>53.789694658137911</v>
-      </c>
-      <c r="E56">
-        <v>108.0421799770567</v>
-      </c>
-      <c r="F56">
-        <v>216.57733197488639</v>
-      </c>
-      <c r="G56">
-        <v>100.9307287772664</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D57">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E57">
-        <v>108.6690475583121</v>
-      </c>
-      <c r="F57">
-        <v>217.92388155425121</v>
-      </c>
-      <c r="G57">
-        <v>101.4870670429727</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D58">
-        <v>51.789694658137911</v>
-      </c>
-      <c r="E58">
-        <v>104.870607101803</v>
-      </c>
-      <c r="F58">
-        <v>211.062613349125</v>
-      </c>
-      <c r="G58">
-        <v>98.259155902012651</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>26.54977647648456</v>
-      </c>
-      <c r="D59">
-        <v>52.49710117158692</v>
-      </c>
-      <c r="E59">
-        <v>104.7675685379174</v>
-      </c>
-      <c r="F59">
-        <v>213.43512854698861</v>
-      </c>
-      <c r="G59">
-        <v>99.312393683244352</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D60">
-        <v>53.369115684745083</v>
-      </c>
-      <c r="E60">
-        <v>107.3529870742077</v>
-      </c>
-      <c r="F60">
-        <v>250.8077936418064</v>
-      </c>
-      <c r="G60">
-        <v>109.21090122493599</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>26.54977647648456</v>
-      </c>
-      <c r="D61">
-        <v>53.498586721382473</v>
-      </c>
-      <c r="E61">
-        <v>106.8493377268543</v>
-      </c>
-      <c r="F61">
-        <v>214.33647357812561</v>
-      </c>
-      <c r="G61">
-        <v>100.30854362571171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>26.727922061357859</v>
-      </c>
-      <c r="D62">
-        <v>54.041630560342618</v>
-      </c>
-      <c r="E62">
-        <v>108.6690475583121</v>
-      </c>
-      <c r="F62">
-        <v>212.40916292848979</v>
-      </c>
-      <c r="G62">
-        <v>100.4619407771256</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>26.54977647648456</v>
-      </c>
-      <c r="D63">
-        <v>53.498586721382473</v>
-      </c>
-      <c r="E63">
-        <v>103.6168719392922</v>
-      </c>
-      <c r="F63">
-        <v>206.04065069635189</v>
-      </c>
-      <c r="G63">
-        <v>97.426471458377762</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>25.313708498984759</v>
-      </c>
-      <c r="D64">
-        <v>53.789694658137911</v>
-      </c>
-      <c r="E64">
-        <v>108.0421799770567</v>
-      </c>
-      <c r="F64">
-        <v>216.57733197488639</v>
-      </c>
-      <c r="G64">
-        <v>100.9307287772664</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>26.54977647648456</v>
-      </c>
-      <c r="D65">
-        <v>53.498586721382473</v>
-      </c>
-      <c r="E65">
-        <v>107.6902241629822</v>
-      </c>
-      <c r="F65">
-        <v>206.04065069635189</v>
-      </c>
-      <c r="G65">
-        <v>98.444809514300275</v>
       </c>
     </row>
   </sheetData>
@@ -6666,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -6838,19 +5660,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F8">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G8">
-        <v>102</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6930,19 +5752,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G12">
-        <v>129</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -6979,16 +5801,16 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F14">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G14">
-        <v>179.75</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -7051,13 +5873,13 @@
         <v>54</v>
       </c>
       <c r="E17">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F17">
         <v>283</v>
       </c>
       <c r="G17">
-        <v>122.75</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -7160,42 +5982,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>247</v>
       </c>
       <c r="G22">
-        <v>7.5</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E23">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="F23">
-        <v>248</v>
+        <v>513</v>
       </c>
       <c r="G23">
-        <v>102</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -7206,19 +6028,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E24">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F24">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="G24">
-        <v>203.75</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -7229,19 +6051,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D25">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E25">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F25">
-        <v>536</v>
+        <v>460</v>
       </c>
       <c r="G25">
-        <v>204.25</v>
+        <v>190.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -7252,19 +6074,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D26">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E26">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F26">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="G26">
-        <v>190.75</v>
+        <v>178.25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -7275,19 +6097,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E27">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F27">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G27">
-        <v>178.25</v>
+        <v>180.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -7298,19 +6120,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D28">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E28">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="F28">
-        <v>456</v>
+        <v>303</v>
       </c>
       <c r="G28">
-        <v>189</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -7321,19 +6143,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D29">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E29">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="F29">
-        <v>306</v>
+        <v>426</v>
       </c>
       <c r="G29">
-        <v>129</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7344,19 +6166,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E30">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="F30">
-        <v>437</v>
+        <v>571</v>
       </c>
       <c r="G30">
-        <v>179.75</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -7367,19 +6189,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E31">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F31">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="G31">
-        <v>217.5</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -7390,19 +6212,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D32">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E32">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="F32">
-        <v>541</v>
+        <v>283</v>
       </c>
       <c r="G32">
-        <v>214.25</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -7413,19 +6235,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F33">
-        <v>283</v>
+        <v>14</v>
       </c>
       <c r="G33">
-        <v>122.75</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -7436,19 +6258,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G34">
-        <v>13.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -7459,19 +6281,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G35">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -7482,19 +6304,19 @@
         <v>41</v>
       </c>
       <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36">
         <v>12</v>
       </c>
-      <c r="D36">
-        <v>14</v>
-      </c>
       <c r="E36">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G36">
-        <v>14.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -7505,19 +6327,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F37">
         <v>16</v>
       </c>
       <c r="G37">
-        <v>14</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -7528,134 +6350,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>11</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E39">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>532</v>
       </c>
       <c r="G39">
-        <v>11</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>460</v>
       </c>
       <c r="G40">
-        <v>14.25</v>
+        <v>190.75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="F41">
-        <v>15</v>
+        <v>494</v>
       </c>
       <c r="G41">
-        <v>12.25</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>201</v>
       </c>
       <c r="F42">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="G42">
-        <v>12.25</v>
+        <v>180.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="F43">
-        <v>11</v>
+        <v>540</v>
       </c>
       <c r="G43">
-        <v>7.5</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -7666,19 +6488,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D44">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="F44">
-        <v>536</v>
+        <v>14</v>
       </c>
       <c r="G44">
-        <v>204.25</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -7689,19 +6511,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D45">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="E45">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="G45">
-        <v>190.75</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -7712,19 +6534,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D46">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="E46">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="F46">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="G46">
-        <v>204.75</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -7735,47 +6557,47 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E47">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>456</v>
+        <v>16</v>
       </c>
       <c r="G47">
-        <v>189</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D48">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E48">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F48">
-        <v>541</v>
+        <v>494</v>
       </c>
       <c r="G48">
-        <v>214.25</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -7784,384 +6606,16 @@
         <v>12</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G49">
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>13</v>
-      </c>
-      <c r="D50">
-        <v>15</v>
-      </c>
-      <c r="E50">
-        <v>16</v>
-      </c>
-      <c r="F50">
-        <v>15</v>
-      </c>
-      <c r="G50">
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>12</v>
-      </c>
-      <c r="D51">
-        <v>22</v>
-      </c>
-      <c r="E51">
-        <v>20</v>
-      </c>
-      <c r="F51">
-        <v>20</v>
-      </c>
-      <c r="G51">
         <v>18.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>11</v>
-      </c>
-      <c r="D52">
-        <v>21</v>
-      </c>
-      <c r="E52">
-        <v>19</v>
-      </c>
-      <c r="F52">
-        <v>19</v>
-      </c>
-      <c r="G52">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>13</v>
-      </c>
-      <c r="D53">
-        <v>21</v>
-      </c>
-      <c r="E53">
-        <v>16</v>
-      </c>
-      <c r="F53">
-        <v>19</v>
-      </c>
-      <c r="G53">
-        <v>17.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>12</v>
-      </c>
-      <c r="D54">
-        <v>14</v>
-      </c>
-      <c r="E54">
-        <v>14</v>
-      </c>
-      <c r="F54">
-        <v>16</v>
-      </c>
-      <c r="G54">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>10</v>
-      </c>
-      <c r="D55">
-        <v>12</v>
-      </c>
-      <c r="E55">
-        <v>11</v>
-      </c>
-      <c r="F55">
-        <v>11</v>
-      </c>
-      <c r="G55">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>16</v>
-      </c>
-      <c r="E56">
-        <v>15</v>
-      </c>
-      <c r="F56">
-        <v>16</v>
-      </c>
-      <c r="G56">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>10</v>
-      </c>
-      <c r="D57">
-        <v>16</v>
-      </c>
-      <c r="E57">
-        <v>15</v>
-      </c>
-      <c r="F57">
-        <v>16</v>
-      </c>
-      <c r="G57">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>8</v>
-      </c>
-      <c r="D58">
-        <v>13</v>
-      </c>
-      <c r="E58">
-        <v>13</v>
-      </c>
-      <c r="F58">
-        <v>15</v>
-      </c>
-      <c r="G58">
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>22</v>
-      </c>
-      <c r="D59">
-        <v>78</v>
-      </c>
-      <c r="E59">
-        <v>219</v>
-      </c>
-      <c r="F59">
-        <v>500</v>
-      </c>
-      <c r="G59">
-        <v>204.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>13</v>
-      </c>
-      <c r="D60">
-        <v>15</v>
-      </c>
-      <c r="E60">
-        <v>16</v>
-      </c>
-      <c r="F60">
-        <v>15</v>
-      </c>
-      <c r="G60">
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>12</v>
-      </c>
-      <c r="D61">
-        <v>22</v>
-      </c>
-      <c r="E61">
-        <v>20</v>
-      </c>
-      <c r="F61">
-        <v>20</v>
-      </c>
-      <c r="G61">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>12</v>
-      </c>
-      <c r="D62">
-        <v>21</v>
-      </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
-      <c r="F62">
-        <v>19</v>
-      </c>
-      <c r="G62">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>13</v>
-      </c>
-      <c r="D63">
-        <v>21</v>
-      </c>
-      <c r="E63">
-        <v>16</v>
-      </c>
-      <c r="F63">
-        <v>19</v>
-      </c>
-      <c r="G63">
-        <v>17.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>10</v>
-      </c>
-      <c r="D64">
-        <v>16</v>
-      </c>
-      <c r="E64">
-        <v>15</v>
-      </c>
-      <c r="F64">
-        <v>16</v>
-      </c>
-      <c r="G64">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>12</v>
-      </c>
-      <c r="D65">
-        <v>21</v>
-      </c>
-      <c r="E65">
-        <v>20</v>
-      </c>
-      <c r="F65">
-        <v>19</v>
-      </c>
-      <c r="G65">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -8171,7 +6625,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -8438,16 +6892,16 @@
         <v>46</v>
       </c>
       <c r="D12">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E12">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F12">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="G12">
-        <v>943.25</v>
+        <v>943</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -8484,7 +6938,7 @@
         <v>35</v>
       </c>
       <c r="D14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14">
         <v>320</v>
@@ -8493,7 +6947,7 @@
         <v>1622</v>
       </c>
       <c r="G14">
-        <v>523.25</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -8665,42 +7119,42 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D22">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="E22">
-        <v>60</v>
+        <v>995</v>
       </c>
       <c r="F22">
-        <v>61</v>
+        <v>3952</v>
       </c>
       <c r="G22">
-        <v>54.25</v>
+        <v>1314.25</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D23">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="E23">
-        <v>995</v>
+        <v>290</v>
       </c>
       <c r="F23">
-        <v>3952</v>
+        <v>978</v>
       </c>
       <c r="G23">
-        <v>1314.25</v>
+        <v>347.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -8711,19 +7165,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D24">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E24">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="F24">
-        <v>978</v>
+        <v>1335</v>
       </c>
       <c r="G24">
-        <v>347.75</v>
+        <v>452.5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -8734,19 +7188,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D25">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E25">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="F25">
-        <v>1341</v>
+        <v>1304</v>
       </c>
       <c r="G25">
-        <v>453.75</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -8757,19 +7211,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="E26">
-        <v>346</v>
+        <v>491</v>
       </c>
       <c r="F26">
-        <v>1304</v>
+        <v>1953</v>
       </c>
       <c r="G26">
-        <v>443.5</v>
+        <v>652</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -8780,19 +7234,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E27">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F27">
-        <v>1953</v>
+        <v>1942</v>
       </c>
       <c r="G27">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -8803,19 +7257,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D28">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="E28">
-        <v>496</v>
+        <v>690</v>
       </c>
       <c r="F28">
-        <v>1949</v>
+        <v>2862</v>
       </c>
       <c r="G28">
-        <v>653.5</v>
+        <v>943</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -8826,19 +7280,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D29">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="E29">
-        <v>691</v>
+        <v>320</v>
       </c>
       <c r="F29">
-        <v>2863</v>
+        <v>1622</v>
       </c>
       <c r="G29">
-        <v>943.25</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -8849,19 +7303,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D30">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E30">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F30">
-        <v>1622</v>
+        <v>1029</v>
       </c>
       <c r="G30">
-        <v>523.25</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -8875,16 +7329,16 @@
         <v>38</v>
       </c>
       <c r="D31">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E31">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F31">
-        <v>1029</v>
+        <v>1100</v>
       </c>
       <c r="G31">
-        <v>364</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -8895,19 +7349,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D32">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="E32">
-        <v>296</v>
+        <v>711</v>
       </c>
       <c r="F32">
-        <v>1096</v>
+        <v>2787</v>
       </c>
       <c r="G32">
-        <v>379</v>
+        <v>932</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -8918,19 +7372,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="E33">
-        <v>711</v>
+        <v>29</v>
       </c>
       <c r="F33">
-        <v>2787</v>
+        <v>31</v>
       </c>
       <c r="G33">
-        <v>932</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -8941,19 +7395,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D34">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G34">
-        <v>27.25</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -8964,19 +7418,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35">
         <v>39</v>
       </c>
       <c r="E35">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G35">
-        <v>32.75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -8987,19 +7441,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E36">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G36">
-        <v>38</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -9010,19 +7464,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D37">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F37">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G37">
-        <v>35.75</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -9033,134 +7487,134 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D38">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F38">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G38">
-        <v>27.25</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D39">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="E39">
-        <v>29</v>
+        <v>337</v>
       </c>
       <c r="F39">
-        <v>29</v>
+        <v>1335</v>
       </c>
       <c r="G39">
-        <v>27.25</v>
+        <v>452.5</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D40">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E40">
-        <v>30</v>
+        <v>346</v>
       </c>
       <c r="F40">
-        <v>31</v>
+        <v>1304</v>
       </c>
       <c r="G40">
-        <v>29.5</v>
+        <v>443.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D41">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E41">
-        <v>54</v>
+        <v>350</v>
       </c>
       <c r="F41">
-        <v>54</v>
+        <v>1311</v>
       </c>
       <c r="G41">
-        <v>48.75</v>
+        <v>446.75</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D42">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="E42">
-        <v>55</v>
+        <v>496</v>
       </c>
       <c r="F42">
-        <v>56</v>
+        <v>1942</v>
       </c>
       <c r="G42">
-        <v>49.5</v>
+        <v>651</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D43">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E43">
-        <v>60</v>
+        <v>295</v>
       </c>
       <c r="F43">
-        <v>61</v>
+        <v>1100</v>
       </c>
       <c r="G43">
-        <v>54.25</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -9171,19 +7625,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D44">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="E44">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>1341</v>
+        <v>31</v>
       </c>
       <c r="G44">
-        <v>453.75</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -9194,19 +7648,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D45">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E45">
-        <v>346</v>
+        <v>34</v>
       </c>
       <c r="F45">
-        <v>1304</v>
+        <v>34</v>
       </c>
       <c r="G45">
-        <v>443.5</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -9217,19 +7671,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D46">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="E46">
-        <v>351</v>
+        <v>35</v>
       </c>
       <c r="F46">
-        <v>1315</v>
+        <v>35</v>
       </c>
       <c r="G46">
-        <v>448</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -9240,433 +7694,65 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D47">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="E47">
-        <v>496</v>
+        <v>30</v>
       </c>
       <c r="F47">
-        <v>1949</v>
+        <v>31</v>
       </c>
       <c r="G47">
-        <v>653.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
       </c>
       <c r="C48">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D48">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E48">
-        <v>296</v>
+        <v>350</v>
       </c>
       <c r="F48">
-        <v>1096</v>
+        <v>1311</v>
       </c>
       <c r="G48">
-        <v>379</v>
+        <v>446.75</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D49">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F49">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G49">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>22</v>
-      </c>
-      <c r="D50">
-        <v>34</v>
-      </c>
-      <c r="E50">
-        <v>38</v>
-      </c>
-      <c r="F50">
-        <v>37</v>
-      </c>
-      <c r="G50">
-        <v>32.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>22</v>
-      </c>
-      <c r="D51">
-        <v>39</v>
-      </c>
-      <c r="E51">
-        <v>34</v>
-      </c>
-      <c r="F51">
-        <v>34</v>
-      </c>
-      <c r="G51">
         <v>32.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>22</v>
-      </c>
-      <c r="D52">
-        <v>39</v>
-      </c>
-      <c r="E52">
-        <v>35</v>
-      </c>
-      <c r="F52">
-        <v>35</v>
-      </c>
-      <c r="G52">
-        <v>32.75</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>25</v>
-      </c>
-      <c r="D53">
-        <v>37</v>
-      </c>
-      <c r="E53">
-        <v>39</v>
-      </c>
-      <c r="F53">
-        <v>48</v>
-      </c>
-      <c r="G53">
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>27</v>
-      </c>
-      <c r="D54">
-        <v>34</v>
-      </c>
-      <c r="E54">
-        <v>38</v>
-      </c>
-      <c r="F54">
-        <v>44</v>
-      </c>
-      <c r="G54">
-        <v>35.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>24</v>
-      </c>
-      <c r="D55">
-        <v>27</v>
-      </c>
-      <c r="E55">
-        <v>29</v>
-      </c>
-      <c r="F55">
-        <v>29</v>
-      </c>
-      <c r="G55">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>24</v>
-      </c>
-      <c r="D56">
-        <v>33</v>
-      </c>
-      <c r="E56">
-        <v>30</v>
-      </c>
-      <c r="F56">
-        <v>31</v>
-      </c>
-      <c r="G56">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>24</v>
-      </c>
-      <c r="D57">
-        <v>33</v>
-      </c>
-      <c r="E57">
-        <v>30</v>
-      </c>
-      <c r="F57">
-        <v>31</v>
-      </c>
-      <c r="G57">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>32</v>
-      </c>
-      <c r="D58">
-        <v>55</v>
-      </c>
-      <c r="E58">
-        <v>55</v>
-      </c>
-      <c r="F58">
-        <v>56</v>
-      </c>
-      <c r="G58">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>33</v>
-      </c>
-      <c r="D59">
-        <v>93</v>
-      </c>
-      <c r="E59">
-        <v>351</v>
-      </c>
-      <c r="F59">
-        <v>1315</v>
-      </c>
-      <c r="G59">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>22</v>
-      </c>
-      <c r="D60">
-        <v>34</v>
-      </c>
-      <c r="E60">
-        <v>38</v>
-      </c>
-      <c r="F60">
-        <v>37</v>
-      </c>
-      <c r="G60">
-        <v>32.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>22</v>
-      </c>
-      <c r="D61">
-        <v>39</v>
-      </c>
-      <c r="E61">
-        <v>34</v>
-      </c>
-      <c r="F61">
-        <v>34</v>
-      </c>
-      <c r="G61">
-        <v>32.25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>22</v>
-      </c>
-      <c r="D62">
-        <v>37</v>
-      </c>
-      <c r="E62">
-        <v>39</v>
-      </c>
-      <c r="F62">
-        <v>48</v>
-      </c>
-      <c r="G62">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>25</v>
-      </c>
-      <c r="D63">
-        <v>37</v>
-      </c>
-      <c r="E63">
-        <v>39</v>
-      </c>
-      <c r="F63">
-        <v>48</v>
-      </c>
-      <c r="G63">
-        <v>37.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>24</v>
-      </c>
-      <c r="D64">
-        <v>33</v>
-      </c>
-      <c r="E64">
-        <v>30</v>
-      </c>
-      <c r="F64">
-        <v>31</v>
-      </c>
-      <c r="G64">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>22</v>
-      </c>
-      <c r="D65">
-        <v>37</v>
-      </c>
-      <c r="E65">
-        <v>39</v>
-      </c>
-      <c r="F65">
-        <v>48</v>
-      </c>
-      <c r="G65">
-        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -9676,7 +7762,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -9989,7 +8075,7 @@
         <v>15</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>19</v>
@@ -9998,7 +8084,7 @@
         <v>27</v>
       </c>
       <c r="G14">
-        <v>20.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -10170,42 +8256,42 @@
         <v>27</v>
       </c>
       <c r="C22">
+        <v>13</v>
+      </c>
+      <c r="D22">
         <v>11</v>
       </c>
-      <c r="D22">
-        <v>14</v>
-      </c>
       <c r="E22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>12.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -10219,16 +8305,16 @@
         <v>14</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -10245,13 +8331,13 @@
         <v>20</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25">
-        <v>19</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -10265,16 +8351,16 @@
         <v>14</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>19.5</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -10288,16 +8374,16 @@
         <v>14</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>14.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -10308,19 +8394,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>20.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -10331,19 +8417,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29">
         <v>13</v>
       </c>
       <c r="G29">
-        <v>13</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -10363,10 +8449,10 @@
         <v>14</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -10377,19 +8463,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>14.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -10400,19 +8486,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D32">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G32">
-        <v>22.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -10426,16 +8512,16 @@
         <v>13</v>
       </c>
       <c r="D33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33">
-        <v>13</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -10446,19 +8532,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G34">
-        <v>13.75</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -10469,19 +8555,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G35">
-        <v>15.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -10495,7 +8581,7 @@
         <v>13</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>13</v>
@@ -10504,7 +8590,7 @@
         <v>13</v>
       </c>
       <c r="G36">
-        <v>13</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -10518,16 +8604,16 @@
         <v>13</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>9.25</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -10541,7 +8627,7 @@
         <v>13</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E38">
         <v>13</v>
@@ -10550,122 +8636,122 @@
         <v>13</v>
       </c>
       <c r="G38">
-        <v>13.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
         <v>44</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <v>14</v>
       </c>
       <c r="F39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39">
-        <v>14.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
         <v>45</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40">
-        <v>15.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G42">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
         <v>48</v>
       </c>
       <c r="C43">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D43">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G43">
-        <v>12</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -10676,19 +8762,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F44">
         <v>13</v>
       </c>
       <c r="G44">
-        <v>13.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -10699,19 +8785,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>14.5</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -10725,16 +8811,16 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F46">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -10745,7 +8831,7 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47">
         <v>15</v>
@@ -10757,12 +8843,12 @@
         <v>15</v>
       </c>
       <c r="G47">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -10785,393 +8871,25 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50">
-        <v>13</v>
-      </c>
-      <c r="D50">
-        <v>8</v>
-      </c>
-      <c r="E50">
-        <v>8</v>
-      </c>
-      <c r="F50">
-        <v>12</v>
-      </c>
-      <c r="G50">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51">
-        <v>15</v>
-      </c>
-      <c r="D51">
-        <v>16</v>
-      </c>
-      <c r="E51">
-        <v>16</v>
-      </c>
-      <c r="F51">
-        <v>16</v>
-      </c>
-      <c r="G51">
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
         <v>14</v>
-      </c>
-      <c r="D52">
-        <v>14</v>
-      </c>
-      <c r="E52">
-        <v>14</v>
-      </c>
-      <c r="F52">
-        <v>14</v>
-      </c>
-      <c r="G52">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>15</v>
-      </c>
-      <c r="D53">
-        <v>16</v>
-      </c>
-      <c r="E53">
-        <v>14</v>
-      </c>
-      <c r="F53">
-        <v>12</v>
-      </c>
-      <c r="G53">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>13</v>
-      </c>
-      <c r="D54">
-        <v>7</v>
-      </c>
-      <c r="E54">
-        <v>7</v>
-      </c>
-      <c r="F54">
-        <v>7</v>
-      </c>
-      <c r="G54">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>4</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>13</v>
-      </c>
-      <c r="D55">
-        <v>15</v>
-      </c>
-      <c r="E55">
-        <v>13</v>
-      </c>
-      <c r="F55">
-        <v>13</v>
-      </c>
-      <c r="G55">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>13</v>
-      </c>
-      <c r="D56">
-        <v>15</v>
-      </c>
-      <c r="E56">
-        <v>15</v>
-      </c>
-      <c r="F56">
-        <v>15</v>
-      </c>
-      <c r="G56">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>13</v>
-      </c>
-      <c r="D57">
-        <v>16</v>
-      </c>
-      <c r="E57">
-        <v>16</v>
-      </c>
-      <c r="F57">
-        <v>16</v>
-      </c>
-      <c r="G57">
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>13</v>
-      </c>
-      <c r="D58">
-        <v>13</v>
-      </c>
-      <c r="E58">
-        <v>13</v>
-      </c>
-      <c r="F58">
-        <v>13</v>
-      </c>
-      <c r="G58">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59">
-        <v>14</v>
-      </c>
-      <c r="D59">
-        <v>15</v>
-      </c>
-      <c r="E59">
-        <v>15</v>
-      </c>
-      <c r="F59">
-        <v>15</v>
-      </c>
-      <c r="G59">
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60">
-        <v>13</v>
-      </c>
-      <c r="D60">
-        <v>7</v>
-      </c>
-      <c r="E60">
-        <v>7</v>
-      </c>
-      <c r="F60">
-        <v>11</v>
-      </c>
-      <c r="G60">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61">
-        <v>14</v>
-      </c>
-      <c r="D61">
-        <v>14</v>
-      </c>
-      <c r="E61">
-        <v>14</v>
-      </c>
-      <c r="F61">
-        <v>14</v>
-      </c>
-      <c r="G61">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62">
-        <v>15</v>
-      </c>
-      <c r="D62">
-        <v>16</v>
-      </c>
-      <c r="E62">
-        <v>16</v>
-      </c>
-      <c r="F62">
-        <v>12</v>
-      </c>
-      <c r="G62">
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>14</v>
-      </c>
-      <c r="D63">
-        <v>14</v>
-      </c>
-      <c r="E63">
-        <v>13</v>
-      </c>
-      <c r="F63">
-        <v>11</v>
-      </c>
-      <c r="G63">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64">
-        <v>13</v>
-      </c>
-      <c r="D64">
-        <v>15</v>
-      </c>
-      <c r="E64">
-        <v>15</v>
-      </c>
-      <c r="F64">
-        <v>15</v>
-      </c>
-      <c r="G64">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65">
-        <v>14</v>
-      </c>
-      <c r="D65">
-        <v>14</v>
-      </c>
-      <c r="E65">
-        <v>14</v>
-      </c>
-      <c r="F65">
-        <v>11</v>
-      </c>
-      <c r="G65">
-        <v>13.25</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAD274F-60C7-45BA-9E5C-CB90F03FDB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -195,8 +189,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,1540 +253,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A*</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.7740000000000012E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.4805999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.5901999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1046846</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BDS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2.4309999999999989E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.7880000000000016E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.0415E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.6605200000000001E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BRC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.1469999999999989E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4946E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.2117000000000023E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.3046099999999994E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GL</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.1710000000000001E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.8938E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.28144E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.4270999999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>JPS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.4240000000000002E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.3186000000000001E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.6888999999999993E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0214099999999999E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PPO</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.1530000000000001E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.5517999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.6799000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1053622</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TPF</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.0360000000000011E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.2745999999999999E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.40956E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.3898200000000001E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-60DB-40DE-BFAC-2EDC9A2074EB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:hiLowLines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:hiLowLines>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="693605423"/>
-        <c:axId val="693605903"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="693605423"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693605903"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="693605903"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="id-ID"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693605423"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="id-ID"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{708ACB0B-8CB7-5EF8-1E6C-60130EA28C72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Red Orange">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1800,37 +267,37 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="505046"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E84C22"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FFBD47"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="B64926"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FF8427"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="B22600"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="CC9900"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="666699"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1864,7 +331,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1899,10 +365,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2075,11 +540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2110,22 +575,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3.7740000000000012E-4</v>
+        <v>0.0003684</v>
       </c>
       <c r="D2">
-        <v>2.4805999999999999E-3</v>
+        <v>0.0025303</v>
       </c>
       <c r="E2">
-        <v>1.5901999999999999E-2</v>
+        <v>0.0162168</v>
       </c>
       <c r="F2">
-        <v>0.1046846</v>
+        <v>0.1075875</v>
       </c>
       <c r="G2">
-        <v>3.086115E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03167575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2133,22 +598,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2.4309999999999989E-4</v>
+        <v>0.0002229</v>
       </c>
       <c r="D3">
-        <v>9.7880000000000016E-4</v>
+        <v>0.0009942000000000002</v>
       </c>
       <c r="E3">
-        <v>4.0415E-3</v>
+        <v>0.0042003</v>
       </c>
       <c r="F3">
-        <v>1.6605200000000001E-2</v>
+        <v>0.0185268</v>
       </c>
       <c r="G3">
-        <v>5.4671499999999987E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005986050000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2156,22 +621,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>4.1469999999999989E-4</v>
+        <v>0.0004456000000000001</v>
       </c>
       <c r="D4">
-        <v>1.4946E-3</v>
+        <v>0.0016104</v>
       </c>
       <c r="E4">
-        <v>8.2117000000000023E-3</v>
+        <v>0.008213399999999999</v>
       </c>
       <c r="F4">
-        <v>6.3046099999999994E-2</v>
+        <v>0.0653704</v>
       </c>
       <c r="G4">
-        <v>1.8291775E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01890995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2179,22 +644,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>3.1710000000000001E-4</v>
+        <v>0.0003297</v>
       </c>
       <c r="D5">
-        <v>1.8938E-3</v>
+        <v>0.0019097</v>
       </c>
       <c r="E5">
-        <v>1.28144E-2</v>
+        <v>0.0133614</v>
       </c>
       <c r="F5">
-        <v>8.4270999999999999E-2</v>
+        <v>0.0859236</v>
       </c>
       <c r="G5">
-        <v>2.4824075000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0253811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2202,22 +667,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>4.4240000000000002E-4</v>
+        <v>0.0004403000000000001</v>
       </c>
       <c r="D6">
-        <v>1.3186000000000001E-3</v>
+        <v>0.0013313</v>
       </c>
       <c r="E6">
-        <v>4.6888999999999993E-3</v>
+        <v>0.0048565</v>
       </c>
       <c r="F6">
-        <v>2.0214099999999999E-2</v>
+        <v>0.0208752</v>
       </c>
       <c r="G6">
-        <v>6.6660000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006875825</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2225,22 +690,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>4.1530000000000001E-4</v>
+        <v>0.0004890000000000001</v>
       </c>
       <c r="D7">
-        <v>2.5517999999999999E-3</v>
+        <v>0.0025856</v>
       </c>
       <c r="E7">
-        <v>1.6799000000000001E-2</v>
+        <v>0.0171262</v>
       </c>
       <c r="F7">
-        <v>0.1053622</v>
+        <v>0.1078525</v>
       </c>
       <c r="G7">
-        <v>3.1282074999999999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.032013325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2248,22 +713,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>4.0360000000000011E-4</v>
+        <v>0.0004246</v>
       </c>
       <c r="D8">
-        <v>2.2745999999999999E-3</v>
+        <v>0.0024571</v>
       </c>
       <c r="E8">
-        <v>1.40956E-2</v>
+        <v>0.0142885</v>
       </c>
       <c r="F8">
-        <v>9.3898200000000001E-2</v>
+        <v>0.0969194</v>
       </c>
       <c r="G8">
-        <v>2.7668000000000002E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0285224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2271,22 +736,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>3.1359999999999992E-4</v>
+        <v>0.000293</v>
       </c>
       <c r="D9">
-        <v>1.2271000000000001E-3</v>
+        <v>0.0012337</v>
       </c>
       <c r="E9">
-        <v>4.5177000000000004E-3</v>
+        <v>0.004620300000000001</v>
       </c>
       <c r="F9">
-        <v>2.0596199999999999E-2</v>
+        <v>0.0215642</v>
       </c>
       <c r="G9">
-        <v>6.6636500000000001E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0069278</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2294,22 +759,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>2.2100000000000001E-4</v>
+        <v>0.0002087</v>
       </c>
       <c r="D10">
-        <v>8.6260000000000004E-4</v>
+        <v>0.000891</v>
       </c>
       <c r="E10">
-        <v>3.7323999999999999E-3</v>
+        <v>0.003873199999999999</v>
       </c>
       <c r="F10">
-        <v>1.6401099999999998E-2</v>
+        <v>0.0173367</v>
       </c>
       <c r="G10">
-        <v>5.3042750000000007E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0055774</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2317,22 +782,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>2.4879999999999998E-4</v>
+        <v>0.0002897</v>
       </c>
       <c r="D11">
-        <v>1.0869E-3</v>
+        <v>0.0010825</v>
       </c>
       <c r="E11">
-        <v>4.3001999999999997E-3</v>
+        <v>0.004370799999999999</v>
       </c>
       <c r="F11">
-        <v>1.7132600000000001E-2</v>
+        <v>0.0181738</v>
       </c>
       <c r="G11">
-        <v>5.6921250000000001E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005979199999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2340,22 +805,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>2.6150000000000012E-4</v>
+        <v>0.0002569</v>
       </c>
       <c r="D12">
-        <v>1.0522000000000001E-3</v>
+        <v>0.0011067</v>
       </c>
       <c r="E12">
-        <v>4.9437999999999999E-3</v>
+        <v>0.0043513</v>
       </c>
       <c r="F12">
-        <v>1.7220300000000001E-2</v>
+        <v>0.0185375</v>
       </c>
       <c r="G12">
-        <v>5.86945E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0060631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2363,22 +828,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>4.5570000000000002E-4</v>
+        <v>0.0004923</v>
       </c>
       <c r="D13">
-        <v>1.6961000000000001E-3</v>
+        <v>0.0016756</v>
       </c>
       <c r="E13">
-        <v>8.3831999999999986E-3</v>
+        <v>0.008547699999999998</v>
       </c>
       <c r="F13">
-        <v>6.2768099999999993E-2</v>
+        <v>0.0660457</v>
       </c>
       <c r="G13">
-        <v>1.8325774999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.019190325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2386,22 +851,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>4.4880000000000012E-4</v>
+        <v>0.0004207</v>
       </c>
       <c r="D14">
-        <v>2.2880000000000001E-3</v>
+        <v>0.0023168</v>
       </c>
       <c r="E14">
-        <v>9.6121000000000002E-3</v>
+        <v>0.009659499999999998</v>
       </c>
       <c r="F14">
-        <v>9.1022999999999993E-2</v>
+        <v>0.0942634</v>
       </c>
       <c r="G14">
-        <v>2.5842975000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0266651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2409,22 +874,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>4.8789999999999999E-4</v>
+        <v>0.0004906999999999999</v>
       </c>
       <c r="D15">
-        <v>1.7971E-3</v>
+        <v>0.0027293</v>
       </c>
       <c r="E15">
-        <v>9.8158000000000013E-3</v>
+        <v>0.0101549</v>
       </c>
       <c r="F15">
-        <v>6.3780300000000012E-2</v>
+        <v>0.06702770000000001</v>
       </c>
       <c r="G15">
-        <v>1.8970275000000002E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02010065</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2432,22 +897,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>4.105E-4</v>
+        <v>0.0003703</v>
       </c>
       <c r="D16">
-        <v>1.9686E-3</v>
+        <v>0.0019728</v>
       </c>
       <c r="E16">
-        <v>1.3065E-2</v>
+        <v>0.0130573</v>
       </c>
       <c r="F16">
-        <v>8.49192E-2</v>
+        <v>0.08804799999999999</v>
       </c>
       <c r="G16">
-        <v>2.5090825000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0258621</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2455,22 +920,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>3.6190000000000001E-4</v>
+        <v>0.0003929</v>
       </c>
       <c r="D17">
-        <v>2.0758999999999999E-3</v>
+        <v>0.0021673</v>
       </c>
       <c r="E17">
-        <v>1.27727E-2</v>
+        <v>0.0129386</v>
       </c>
       <c r="F17">
-        <v>7.9210799999999998E-2</v>
+        <v>0.0829698</v>
       </c>
       <c r="G17">
-        <v>2.3605325E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02461715</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2478,22 +943,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3.0370000000000001E-4</v>
+        <v>0.0003028</v>
       </c>
       <c r="D18">
-        <v>9.2440000000000003E-4</v>
+        <v>0.000937</v>
       </c>
       <c r="E18">
-        <v>3.9212000000000014E-3</v>
+        <v>0.0039509</v>
       </c>
       <c r="F18">
-        <v>1.4966E-2</v>
+        <v>0.0154792</v>
       </c>
       <c r="G18">
-        <v>5.0288250000000007E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005167475</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2501,22 +966,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3.255E-4</v>
+        <v>0.0003371</v>
       </c>
       <c r="D19">
-        <v>6.6510000000000007E-4</v>
+        <v>0.0006837</v>
       </c>
       <c r="E19">
-        <v>1.8821E-3</v>
+        <v>0.0019647</v>
       </c>
       <c r="F19">
-        <v>7.3771999999999987E-3</v>
+        <v>0.007471199999999999</v>
       </c>
       <c r="G19">
-        <v>2.5624749999999998E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.002614175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2524,22 +989,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>3.613E-4</v>
+        <v>0.0003698</v>
       </c>
       <c r="D20">
-        <v>1.1864E-3</v>
+        <v>0.0012677</v>
       </c>
       <c r="E20">
-        <v>3.7368000000000002E-3</v>
+        <v>0.003837300000000001</v>
       </c>
       <c r="F20">
-        <v>1.36928E-2</v>
+        <v>0.0139038</v>
       </c>
       <c r="G20">
-        <v>4.7443249999999998E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00484465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2547,22 +1012,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>4.5760000000000001E-4</v>
+        <v>0.0004694</v>
       </c>
       <c r="D21">
-        <v>1.3073E-3</v>
+        <v>0.001364</v>
       </c>
       <c r="E21">
-        <v>4.7841999999999997E-3</v>
+        <v>0.0048813</v>
       </c>
       <c r="F21">
-        <v>2.0043800000000001E-2</v>
+        <v>0.0205531</v>
       </c>
       <c r="G21">
-        <v>6.6482250000000007E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00681695</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2570,22 +1035,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>4.5750000000000001E-4</v>
+        <v>0.0004725</v>
       </c>
       <c r="D22">
-        <v>2.4611999999999989E-3</v>
+        <v>0.0024187</v>
       </c>
       <c r="E22">
-        <v>1.41183E-2</v>
+        <v>0.0145289</v>
       </c>
       <c r="F22">
-        <v>9.3971299999999994E-2</v>
+        <v>0.09776799999999999</v>
       </c>
       <c r="G22">
-        <v>2.7752075000000001E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.028797025</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -2593,22 +1058,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>3.412E-4</v>
+        <v>0.0003681</v>
       </c>
       <c r="D23">
-        <v>1.3068999999999999E-3</v>
+        <v>0.0013251</v>
       </c>
       <c r="E23">
-        <v>4.5806000000000006E-3</v>
+        <v>0.004776</v>
       </c>
       <c r="F23">
-        <v>2.0691899999999999E-2</v>
+        <v>0.0222221</v>
       </c>
       <c r="G23">
-        <v>6.7301499999999998E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.007172825000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2616,22 +1081,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>4.0020000000000002E-4</v>
+        <v>0.0003568</v>
       </c>
       <c r="D24">
-        <v>1.377E-3</v>
+        <v>0.0014644</v>
       </c>
       <c r="E24">
-        <v>5.4014999999999992E-3</v>
+        <v>0.0057191</v>
       </c>
       <c r="F24">
-        <v>2.6498299999999999E-2</v>
+        <v>0.0283731</v>
       </c>
       <c r="G24">
-        <v>8.4192499999999997E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00897835</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2639,22 +1104,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>3.4660000000000002E-4</v>
+        <v>0.0003338</v>
       </c>
       <c r="D25">
-        <v>1.3347999999999999E-3</v>
+        <v>0.0013957</v>
       </c>
       <c r="E25">
-        <v>6.3047999999999993E-3</v>
+        <v>0.007202800000000001</v>
       </c>
       <c r="F25">
-        <v>3.5663500000000001E-2</v>
+        <v>0.0375011</v>
       </c>
       <c r="G25">
-        <v>1.0912425E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01160835</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2662,22 +1127,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>2.3389999999999999E-4</v>
+        <v>0.0002536</v>
       </c>
       <c r="D26">
-        <v>9.1959999999999991E-4</v>
+        <v>0.0009392000000000001</v>
       </c>
       <c r="E26">
-        <v>3.8601E-3</v>
+        <v>0.0040627</v>
       </c>
       <c r="F26">
-        <v>1.73811E-2</v>
+        <v>0.0180649</v>
       </c>
       <c r="G26">
-        <v>5.5986750000000009E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0058301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2685,22 +1150,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>2.296E-4</v>
+        <v>0.0002258</v>
       </c>
       <c r="D27">
-        <v>9.8780000000000005E-4</v>
+        <v>0.0010129</v>
       </c>
       <c r="E27">
-        <v>3.9772000000000002E-3</v>
+        <v>0.0040751</v>
       </c>
       <c r="F27">
-        <v>1.6949499999999999E-2</v>
+        <v>0.0174098</v>
       </c>
       <c r="G27">
-        <v>5.536025E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.005680899999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2708,22 +1173,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>3.0430000000000002E-4</v>
+        <v>0.0003099</v>
       </c>
       <c r="D28">
-        <v>1.1307000000000001E-3</v>
+        <v>0.00118</v>
       </c>
       <c r="E28">
-        <v>4.3836999999999999E-3</v>
+        <v>0.0046811</v>
       </c>
       <c r="F28">
-        <v>1.7761200000000001E-2</v>
+        <v>0.0190033</v>
       </c>
       <c r="G28">
-        <v>5.8949749999999993E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.006293575</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2731,22 +1196,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>5.0700000000000007E-4</v>
+        <v>0.0005142</v>
       </c>
       <c r="D29">
-        <v>2.3268E-3</v>
+        <v>0.0024822</v>
       </c>
       <c r="E29">
-        <v>9.9332999999999991E-3</v>
+        <v>0.0100577</v>
       </c>
       <c r="F29">
-        <v>9.2549800000000002E-2</v>
+        <v>0.0944536</v>
       </c>
       <c r="G29">
-        <v>2.6329225000000001E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.026876925</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2754,22 +1219,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>5.2720000000000002E-4</v>
+        <v>0.0005367</v>
       </c>
       <c r="D30">
-        <v>1.8767E-3</v>
+        <v>0.0020199</v>
       </c>
       <c r="E30">
-        <v>1.00535E-2</v>
+        <v>0.0103828</v>
       </c>
       <c r="F30">
-        <v>6.3950399999999991E-2</v>
+        <v>0.0676879</v>
       </c>
       <c r="G30">
-        <v>1.9101949999999999E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.020156825</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2777,22 +1242,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>4.9010000000000004E-4</v>
+        <v>0.0005577000000000001</v>
       </c>
       <c r="D31">
-        <v>1.8992E-3</v>
+        <v>0.0019003</v>
       </c>
       <c r="E31">
-        <v>1.00938E-2</v>
+        <v>0.0105248</v>
       </c>
       <c r="F31">
-        <v>6.5059400000000003E-2</v>
+        <v>0.0687319</v>
       </c>
       <c r="G31">
-        <v>1.9385625E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.020428675</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2800,22 +1265,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>4.0190000000000001E-4</v>
+        <v>0.0004254</v>
       </c>
       <c r="D32">
-        <v>2.1258000000000002E-3</v>
+        <v>0.0022286</v>
       </c>
       <c r="E32">
-        <v>1.27438E-2</v>
+        <v>0.01334</v>
       </c>
       <c r="F32">
-        <v>7.9895900000000006E-2</v>
+        <v>0.0829743</v>
       </c>
       <c r="G32">
-        <v>2.379185E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.024742075</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2823,22 +1288,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>3.2479999999999998E-4</v>
+        <v>0.0003314999999999999</v>
       </c>
       <c r="D33">
-        <v>7.3510000000000003E-4</v>
+        <v>0.0008112</v>
       </c>
       <c r="E33">
-        <v>2.2307999999999998E-3</v>
+        <v>0.0022966</v>
       </c>
       <c r="F33">
-        <v>9.0025999999999995E-3</v>
+        <v>0.009259100000000001</v>
       </c>
       <c r="G33">
-        <v>3.073325E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003174600000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2846,22 +1311,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>2.4860000000000003E-4</v>
+        <v>0.0002867</v>
       </c>
       <c r="D34">
-        <v>8.7519999999999991E-4</v>
+        <v>0.0008856000000000001</v>
       </c>
       <c r="E34">
-        <v>2.634200000000001E-3</v>
+        <v>0.0026571</v>
       </c>
       <c r="F34">
-        <v>1.01519E-2</v>
+        <v>0.0100678</v>
       </c>
       <c r="G34">
-        <v>3.4774750000000011E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0034743</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2869,22 +1334,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>3.1300000000000002E-4</v>
+        <v>0.0003219</v>
       </c>
       <c r="D35">
-        <v>9.9259999999999995E-4</v>
+        <v>0.0010294</v>
       </c>
       <c r="E35">
-        <v>3.9971E-3</v>
+        <v>0.0040139</v>
       </c>
       <c r="F35">
-        <v>1.5155999999999999E-2</v>
+        <v>0.0153738</v>
       </c>
       <c r="G35">
-        <v>5.114675E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00518475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2892,22 +1357,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>3.9390000000000009E-4</v>
+        <v>0.0004085</v>
       </c>
       <c r="D36">
-        <v>7.3220000000000002E-4</v>
+        <v>0.0007631</v>
       </c>
       <c r="E36">
-        <v>1.89E-3</v>
+        <v>0.0020071</v>
       </c>
       <c r="F36">
-        <v>7.3714000000000002E-3</v>
+        <v>0.007525799999999999</v>
       </c>
       <c r="G36">
-        <v>2.5968749999999998E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.002676125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2915,22 +1380,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>3.635E-4</v>
+        <v>0.000345</v>
       </c>
       <c r="D37">
-        <v>9.0679999999999992E-4</v>
+        <v>0.0009407</v>
       </c>
       <c r="E37">
-        <v>2.4930999999999998E-3</v>
+        <v>0.0025912</v>
       </c>
       <c r="F37">
-        <v>9.791300000000001E-3</v>
+        <v>0.0100947</v>
       </c>
       <c r="G37">
-        <v>3.3886749999999998E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0034929</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2938,22 +1403,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>4.0979999999999999E-4</v>
+        <v>0.0004224</v>
       </c>
       <c r="D38">
-        <v>1.2853999999999999E-3</v>
+        <v>0.0012833</v>
       </c>
       <c r="E38">
-        <v>3.8685E-3</v>
+        <v>0.0040225</v>
       </c>
       <c r="F38">
-        <v>1.4049499999999999E-2</v>
+        <v>0.0142209</v>
       </c>
       <c r="G38">
-        <v>4.9032999999999993E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.004987275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -2961,22 +1426,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>3.9550000000000002E-4</v>
+        <v>0.0004081000000000001</v>
       </c>
       <c r="D39">
-        <v>1.5529999999999999E-3</v>
+        <v>0.0015859</v>
       </c>
       <c r="E39">
-        <v>5.5418999999999998E-3</v>
+        <v>0.005953699999999999</v>
       </c>
       <c r="F39">
-        <v>2.7463100000000001E-2</v>
+        <v>0.0292137</v>
       </c>
       <c r="G39">
-        <v>8.7383749999999996E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.009290349999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -2984,22 +1449,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>3.6309999999999999E-4</v>
+        <v>0.0004257999999999999</v>
       </c>
       <c r="D40">
-        <v>1.5108000000000001E-3</v>
+        <v>0.0016288</v>
       </c>
       <c r="E40">
-        <v>6.8602999999999997E-3</v>
+        <v>0.0067264</v>
       </c>
       <c r="F40">
-        <v>3.7648599999999997E-2</v>
+        <v>0.0390701</v>
       </c>
       <c r="G40">
-        <v>1.15957E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.011962775</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -3007,22 +1472,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>3.5970000000000002E-4</v>
+        <v>0.0003619</v>
       </c>
       <c r="D41">
-        <v>1.5156E-3</v>
+        <v>0.0014979</v>
       </c>
       <c r="E41">
-        <v>6.6635000000000002E-3</v>
+        <v>0.006693599999999999</v>
       </c>
       <c r="F41">
-        <v>3.4248199999999993E-2</v>
+        <v>0.0364288</v>
       </c>
       <c r="G41">
-        <v>1.069675E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01124555</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -3030,22 +1495,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>2.8729999999999999E-4</v>
+        <v>0.000295</v>
       </c>
       <c r="D42">
-        <v>1.0277999999999999E-3</v>
+        <v>0.0010965</v>
       </c>
       <c r="E42">
-        <v>4.1537999999999992E-3</v>
+        <v>0.004369899999999999</v>
       </c>
       <c r="F42">
-        <v>1.7581300000000001E-2</v>
+        <v>0.0185596</v>
       </c>
       <c r="G42">
-        <v>5.76255E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.00608025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -3053,22 +1518,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>5.4379999999999999E-4</v>
+        <v>0.0005930999999999999</v>
       </c>
       <c r="D43">
-        <v>2.026E-3</v>
+        <v>0.0019415</v>
       </c>
       <c r="E43">
-        <v>1.04452E-2</v>
+        <v>0.0105921</v>
       </c>
       <c r="F43">
-        <v>6.6992499999999996E-2</v>
+        <v>0.06949449999999999</v>
       </c>
       <c r="G43">
-        <v>2.0001874999999999E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02065529999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3076,22 +1541,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>3.3270000000000001E-4</v>
+        <v>0.0003291</v>
       </c>
       <c r="D44">
-        <v>8.0160000000000008E-4</v>
+        <v>0.0008488</v>
       </c>
       <c r="E44">
-        <v>2.3365999999999999E-3</v>
+        <v>0.0024474</v>
       </c>
       <c r="F44">
-        <v>9.0867000000000014E-3</v>
+        <v>0.009378600000000001</v>
       </c>
       <c r="G44">
-        <v>3.139400000000001E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.003250975</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3099,22 +1564,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>3.4390000000000001E-4</v>
+        <v>0.0003216000000000001</v>
       </c>
       <c r="D45">
-        <v>1.0326999999999999E-3</v>
+        <v>0.0010721</v>
       </c>
       <c r="E45">
-        <v>2.9713000000000009E-3</v>
+        <v>0.0028567</v>
       </c>
       <c r="F45">
-        <v>1.0685500000000001E-2</v>
+        <v>0.0112756</v>
       </c>
       <c r="G45">
-        <v>3.7583500000000001E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0038815</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3122,22 +1587,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>2.7099999999999997E-4</v>
+        <v>0.0002792</v>
       </c>
       <c r="D46">
-        <v>9.1430000000000005E-4</v>
+        <v>0.0008925000000000001</v>
       </c>
       <c r="E46">
-        <v>2.7100000000000002E-3</v>
+        <v>0.002747</v>
       </c>
       <c r="F46">
-        <v>1.02296E-2</v>
+        <v>0.0104949</v>
       </c>
       <c r="G46">
-        <v>3.5312249999999998E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0036034</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3145,22 +1610,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>3.6650000000000002E-4</v>
+        <v>0.0003884</v>
       </c>
       <c r="D47">
-        <v>9.0700000000000004E-4</v>
+        <v>0.0010208</v>
       </c>
       <c r="E47">
-        <v>2.6023000000000001E-3</v>
+        <v>0.0026856</v>
       </c>
       <c r="F47">
-        <v>1.00707E-2</v>
+        <v>0.010242</v>
       </c>
       <c r="G47">
-        <v>3.4866250000000001E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0035842</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -3168,22 +1633,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>3.8020000000000003E-4</v>
+        <v>0.0003817</v>
       </c>
       <c r="D48">
-        <v>1.6184999999999999E-3</v>
+        <v>0.0016549</v>
       </c>
       <c r="E48">
-        <v>6.7567E-3</v>
+        <v>0.006988800000000001</v>
       </c>
       <c r="F48">
-        <v>3.5299200000000003E-2</v>
+        <v>0.037747</v>
       </c>
       <c r="G48">
-        <v>1.101365E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0116931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -3191,33 +1656,32 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>3.3720000000000001E-4</v>
+        <v>0.0003648</v>
       </c>
       <c r="D49">
-        <v>1.1295999999999999E-3</v>
+        <v>0.0011643</v>
       </c>
       <c r="E49">
-        <v>2.9031999999999999E-3</v>
+        <v>0.0031348</v>
       </c>
       <c r="F49">
-        <v>1.0902800000000001E-2</v>
+        <v>0.0113568</v>
       </c>
       <c r="G49">
-        <v>3.8181999999999999E-3</v>
+        <v>0.004005175</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3240,7 +1704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3263,7 +1727,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3286,7 +1750,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3309,7 +1773,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3332,7 +1796,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3355,7 +1819,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3378,7 +1842,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3401,7 +1865,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3424,7 +1888,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3447,7 +1911,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3470,7 +1934,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3493,7 +1957,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3516,7 +1980,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3539,7 +2003,7 @@
         <v>100.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3562,7 +2026,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3585,7 +2049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3608,7 +2072,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -3631,7 +2095,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -3654,7 +2118,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -3677,7 +2141,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -3700,7 +2164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -3723,7 +2187,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -3746,7 +2210,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -3769,7 +2233,7 @@
         <v>95.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -3792,7 +2256,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -3815,7 +2279,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -3838,7 +2302,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -3861,7 +2325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -3884,7 +2348,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3907,7 +2371,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -3930,7 +2394,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -3953,7 +2417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -3976,7 +2440,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -3999,7 +2463,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4022,7 +2486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4045,7 +2509,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4068,7 +2532,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4091,7 +2555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -4114,7 +2578,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -4137,7 +2601,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -4160,7 +2624,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -4183,7 +2647,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -4206,7 +2670,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4229,7 +2693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4252,7 +2716,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4275,7 +2739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4298,7 +2762,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -4321,7 +2785,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -4350,11 +2814,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4377,7 +2841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4385,22 +2849,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D2">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E2">
         <v>105.4974746830583</v>
       </c>
       <c r="F2">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G2">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4408,7 +2872,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D3">
         <v>52.87005768508881</v>
@@ -4417,13 +2881,13 @@
         <v>106.3259018078045</v>
       </c>
       <c r="F3">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="G3">
-        <v>99.436814511278499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.4368145112785</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4431,22 +2895,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D4">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E4">
         <v>111.8406204335659</v>
       </c>
       <c r="F4">
-        <v>226.85281374238571</v>
+        <v>226.8528137423857</v>
       </c>
       <c r="G4">
-        <v>104.86574669941299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>104.865746699413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4454,22 +2918,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D5">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E5">
         <v>105.4974746830583</v>
       </c>
       <c r="F5">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G5">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4477,22 +2941,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D6">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E6">
         <v>105.4974746830583</v>
       </c>
       <c r="F6">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G6">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4500,22 +2964,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>25.090832649702559</v>
+        <v>25.09083264970256</v>
       </c>
       <c r="D7">
-        <v>50.851952406436453</v>
+        <v>50.85195240643645</v>
       </c>
       <c r="E7">
-        <v>102.22089893573281</v>
+        <v>102.2208989357328</v>
       </c>
       <c r="F7">
-        <v>206.20172566370999</v>
+        <v>206.20172566371</v>
       </c>
       <c r="G7">
-        <v>96.091352413895436</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.09135241389544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4523,22 +2987,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D8">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E8">
         <v>105.4974746830583</v>
       </c>
       <c r="F8">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G8">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -4546,7 +3010,7 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D9">
         <v>54.87005768508881</v>
@@ -4555,13 +3019,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F9">
-        <v>220.40916292848979</v>
+        <v>220.4091629284898</v>
       </c>
       <c r="G9">
         <v>102.8761543394987</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4569,22 +3033,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D10">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E10">
         <v>108.6690475583121</v>
       </c>
       <c r="F10">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G10">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4592,22 +3056,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D11">
-        <v>50.942677103220838</v>
+        <v>50.94267710322084</v>
       </c>
       <c r="E11">
         <v>102.3124613687156</v>
       </c>
       <c r="F11">
-        <v>204.60732654518389</v>
+        <v>204.6073265451839</v>
       </c>
       <c r="G11">
-        <v>95.794043379026277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.79404337902628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4615,22 +3079,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D12">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E12">
         <v>106.3259018078045</v>
       </c>
       <c r="F12">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="G12">
-        <v>99.229707730091974</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.22970773009197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4641,19 +3105,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D13">
-        <v>53.155440970874849</v>
+        <v>53.15544097087485</v>
       </c>
       <c r="E13">
         <v>108.4816898532232</v>
       </c>
       <c r="F13">
-        <v>219.24876739829651</v>
+        <v>219.2487673982965</v>
       </c>
       <c r="G13">
         <v>101.8589186747198</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4661,22 +3125,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D14">
-        <v>57.798989873223341</v>
+        <v>57.79898987322334</v>
       </c>
       <c r="E14">
-        <v>117.35533905932741</v>
+        <v>117.3553390593274</v>
       </c>
       <c r="F14">
-        <v>237.29646455628159</v>
+        <v>237.2964645562816</v>
       </c>
       <c r="G14">
-        <v>109.79467888754751</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>109.7946788875475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4684,22 +3148,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D15">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E15">
-        <v>111.25483399593899</v>
+        <v>111.254833995939</v>
       </c>
       <c r="F15">
-        <v>221.33809511662429</v>
+        <v>221.3380951166243</v>
       </c>
       <c r="G15">
         <v>103.3406204335659</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4707,22 +3171,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D16">
-        <v>50.536273206137643</v>
+        <v>50.53627320613764</v>
       </c>
       <c r="E16">
         <v>101.5116887917378</v>
       </c>
       <c r="F16">
-        <v>203.62020384855049</v>
+        <v>203.6202038485505</v>
       </c>
       <c r="G16">
-        <v>95.245468586352686</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.24546858635269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4730,22 +3194,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D17">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E17">
         <v>105.4974746830583</v>
       </c>
       <c r="F17">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G17">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4753,22 +3217,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D18">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E18">
         <v>105.4974746830583</v>
       </c>
       <c r="F18">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G18">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4776,22 +3240,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D19">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E19">
         <v>105.4974746830583</v>
       </c>
       <c r="F19">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G19">
-        <v>99.315494167718867</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.31549416771887</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4799,22 +3263,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D20">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E20">
         <v>105.4974746830583</v>
       </c>
       <c r="F20">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G20">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4822,10 +3286,10 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D21">
-        <v>51.789694658137911</v>
+        <v>51.78969465813791</v>
       </c>
       <c r="E21">
         <v>104.870607101803</v>
@@ -4834,10 +3298,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G21">
-        <v>98.259155902012651</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.25915590201265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4845,22 +3309,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D22">
-        <v>49.846941716980723</v>
+        <v>49.84694171698072</v>
       </c>
       <c r="E22">
-        <v>101.47397718311861</v>
+        <v>101.4739771831186</v>
       </c>
       <c r="F22">
-        <v>204.98245579924691</v>
+        <v>204.9824557992469</v>
       </c>
       <c r="G22">
-        <v>95.404270799582747</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.40427079958275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -4871,19 +3335,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D23">
-        <v>53.831713714764781</v>
+        <v>53.83171371476478</v>
       </c>
       <c r="E23">
         <v>107.0191148045464</v>
       </c>
       <c r="F23">
-        <v>216.31798086904371</v>
+        <v>216.3179808690437</v>
       </c>
       <c r="G23">
         <v>100.9296464662099</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4891,22 +3355,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D24">
-        <v>56.627416997969519</v>
+        <v>56.62741699796952</v>
       </c>
       <c r="E24">
         <v>113.8406204335659</v>
       </c>
       <c r="F24">
-        <v>230.26702730475881</v>
+        <v>230.2670273047588</v>
       </c>
       <c r="G24">
-        <v>106.86574669941299</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>106.865746699413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4914,22 +3378,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D25">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E25">
         <v>110.6690475583121</v>
       </c>
       <c r="F25">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="G25">
-        <v>102.75483399593899</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102.754833995939</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4940,19 +3404,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D26">
-        <v>52.181907122806606</v>
+        <v>52.18190712280661</v>
       </c>
       <c r="E26">
-        <v>104.11728699804451</v>
+        <v>104.1172869980445</v>
       </c>
       <c r="F26">
-        <v>208.24061365691611</v>
+        <v>208.2406136569161</v>
       </c>
       <c r="G26">
-        <v>97.772396063562951</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.77239606356295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4960,7 +3424,7 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D27">
         <v>54.87005768508881</v>
@@ -4969,13 +3433,13 @@
         <v>109.4974746830583</v>
       </c>
       <c r="F27">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G27">
-        <v>102.25483399593899</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102.254833995939</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4983,22 +3447,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D28">
-        <v>50.445063357834727</v>
+        <v>50.44506335783473</v>
       </c>
       <c r="E28">
         <v>102.0661260637976</v>
       </c>
       <c r="F28">
-        <v>205.49070842301589</v>
+        <v>205.4907084230159</v>
       </c>
       <c r="G28">
-        <v>95.828901585908241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.82890158590824</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5009,7 +3473,7 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D29">
-        <v>55.193957223724922</v>
+        <v>55.19395722372492</v>
       </c>
       <c r="E29">
         <v>109.8662799826854</v>
@@ -5021,7 +3485,7 @@
         <v>103.4295116012851</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5038,13 +3502,13 @@
         <v>105.0403618691834</v>
       </c>
       <c r="F30">
-        <v>211.73407903147461</v>
+        <v>211.7340790314746</v>
       </c>
       <c r="G30">
-        <v>98.955329637182359</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.95532963718236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5052,22 +3516,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D31">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E31">
-        <v>111.25483399593899</v>
+        <v>111.254833995939</v>
       </c>
       <c r="F31">
         <v>224.9949493661166</v>
       </c>
       <c r="G31">
-        <v>104.25483399593899</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>104.254833995939</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5075,22 +3539,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D32">
-        <v>50.536273206137643</v>
+        <v>50.53627320613764</v>
       </c>
       <c r="E32">
         <v>101.5116887917378</v>
       </c>
       <c r="F32">
-        <v>203.62020384855049</v>
+        <v>203.6202038485505</v>
       </c>
       <c r="G32">
-        <v>95.245468586352686</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>95.24546858635269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5098,22 +3562,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D33">
-        <v>52.041630560342618</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E33">
         <v>105.4974746830583</v>
       </c>
       <c r="F33">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G33">
-        <v>98.815494167718867</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.81549416771887</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5121,22 +3585,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D34">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E34">
         <v>108.6690475583121</v>
       </c>
       <c r="F34">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G34">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5144,10 +3608,10 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D35">
-        <v>50.942677103220838</v>
+        <v>50.94267710322084</v>
       </c>
       <c r="E35">
         <v>102.6712897929513</v>
@@ -5156,10 +3620,10 @@
         <v>206.2505164179251</v>
       </c>
       <c r="G35">
-        <v>96.294547953270495</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>96.2945479532705</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5167,10 +3631,10 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D36">
-        <v>53.789694658137911</v>
+        <v>53.78969465813791</v>
       </c>
       <c r="E36">
         <v>104.870607101803</v>
@@ -5179,10 +3643,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G36">
-        <v>98.759155902012651</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.75915590201265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5190,22 +3654,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D37">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E37">
         <v>108.6690475583121</v>
       </c>
       <c r="F37">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G37">
         <v>101.4870670429727</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5213,10 +3677,10 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D38">
-        <v>51.789694658137911</v>
+        <v>51.78969465813791</v>
       </c>
       <c r="E38">
         <v>104.870607101803</v>
@@ -5225,10 +3689,10 @@
         <v>211.062613349125</v>
       </c>
       <c r="G38">
-        <v>98.259155902012651</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.25915590201265</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -5239,19 +3703,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D39">
-        <v>54.038067022199172</v>
+        <v>54.03806702219917</v>
       </c>
       <c r="E39">
-        <v>108.66299557933429</v>
+        <v>108.6629955793343</v>
       </c>
       <c r="F39">
         <v>219.4050796727812</v>
       </c>
       <c r="G39">
-        <v>102.16397968769979</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>102.1639796876998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -5268,13 +3732,13 @@
         <v>104.7154540633544</v>
       </c>
       <c r="F40">
-        <v>211.29746103441209</v>
+        <v>211.2974610344121</v>
       </c>
       <c r="G40">
-        <v>98.764948186459506</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98.76494818645951</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -5282,22 +3746,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D41">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E41">
         <v>110.6690475583121</v>
       </c>
       <c r="F41">
-        <v>223.23759005323589</v>
+        <v>223.2375900532359</v>
       </c>
       <c r="G41">
         <v>103.6690475583121</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -5308,19 +3772,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D42">
-        <v>52.181907122806606</v>
+        <v>52.18190712280661</v>
       </c>
       <c r="E42">
         <v>104.5993450099368</v>
       </c>
       <c r="F42">
-        <v>208.24061365691611</v>
+        <v>208.2406136569161</v>
       </c>
       <c r="G42">
-        <v>97.892910566535988</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>97.89291056653599</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -5337,13 +3801,13 @@
         <v>105.0924763437464</v>
       </c>
       <c r="F43">
-        <v>213.87174654405101</v>
+        <v>213.871746544051</v>
       </c>
       <c r="G43">
-        <v>99.502775133967219</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.50277513396722</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5351,22 +3815,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D44">
-        <v>51.285822853728483</v>
+        <v>51.28582285372848</v>
       </c>
       <c r="E44">
         <v>103.6168719392922</v>
       </c>
       <c r="F44">
-        <v>208.36951419039531</v>
+        <v>208.3695141903953</v>
       </c>
       <c r="G44">
         <v>97.14647937060019</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -5374,22 +3838,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>26.727922061357859</v>
+        <v>26.72792206135786</v>
       </c>
       <c r="D45">
-        <v>54.041630560342618</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E45">
         <v>108.6690475583121</v>
       </c>
       <c r="F45">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G45">
         <v>101.8406204335659</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -5400,19 +3864,19 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D46">
-        <v>53.498586721382473</v>
+        <v>53.49858672138247</v>
       </c>
       <c r="E46">
         <v>106.8493377268543</v>
       </c>
       <c r="F46">
-        <v>214.33647357812561</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="G46">
-        <v>100.30854362571171</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>100.3085436257117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5420,22 +3884,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>25.313708498984759</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D47">
-        <v>53.789694658137911</v>
+        <v>53.78969465813791</v>
       </c>
       <c r="E47">
         <v>108.0421799770567</v>
       </c>
       <c r="F47">
-        <v>216.57733197488639</v>
+        <v>216.5773319748864</v>
       </c>
       <c r="G47">
         <v>100.9307287772664</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -5452,13 +3916,13 @@
         <v>104.7675685379174</v>
       </c>
       <c r="F48">
-        <v>213.43512854698861</v>
+        <v>213.4351285469886</v>
       </c>
       <c r="G48">
-        <v>99.312393683244352</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>99.31239368324435</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -5469,16 +3933,16 @@
         <v>26.54977647648456</v>
       </c>
       <c r="D49">
-        <v>53.498586721382473</v>
+        <v>53.49858672138247</v>
       </c>
       <c r="E49">
         <v>106.8493377268543</v>
       </c>
       <c r="F49">
-        <v>214.33647357812561</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="G49">
-        <v>100.30854362571171</v>
+        <v>100.3085436257117</v>
       </c>
     </row>
   </sheetData>
@@ -5487,11 +3951,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +3978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5537,7 +4001,7 @@
         <v>111.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5560,7 +4024,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5583,7 +4047,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5606,7 +4070,7 @@
         <v>116.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5629,7 +4093,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5652,7 +4116,7 @@
         <v>111.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5675,7 +4139,7 @@
         <v>100.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5698,7 +4162,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5721,7 +4185,7 @@
         <v>178.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5744,7 +4208,7 @@
         <v>162.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5767,7 +4231,7 @@
         <v>127.75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5790,7 +4254,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5813,7 +4277,7 @@
         <v>175.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5836,7 +4300,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5859,7 +4323,7 @@
         <v>116.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5882,7 +4346,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5905,7 +4369,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5928,7 +4392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5951,7 +4415,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5974,7 +4438,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5997,7 +4461,7 @@
         <v>100.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -6020,7 +4484,7 @@
         <v>203.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -6043,7 +4507,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6066,7 +4530,7 @@
         <v>190.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -6089,7 +4553,7 @@
         <v>178.25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -6112,7 +4576,7 @@
         <v>180.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6135,7 +4599,7 @@
         <v>127.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -6158,7 +4622,7 @@
         <v>175.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6181,7 +4645,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6204,7 +4668,7 @@
         <v>211.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -6227,7 +4691,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -6250,7 +4714,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6273,7 +4737,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6296,7 +4760,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6319,7 +4783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6342,7 +4806,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -6365,7 +4829,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -6388,7 +4852,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -6411,7 +4875,7 @@
         <v>190.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -6434,7 +4898,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -6457,7 +4921,7 @@
         <v>180.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -6480,7 +4944,7 @@
         <v>211.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6503,7 +4967,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6526,7 +4990,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6549,7 +5013,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6572,7 +5036,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -6595,7 +5059,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -6624,11 +5088,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6651,7 +5115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6674,7 +5138,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6697,7 +5161,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6720,7 +5184,7 @@
         <v>376.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6743,7 +5207,7 @@
         <v>923.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6766,7 +5230,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6789,7 +5253,7 @@
         <v>1300.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6812,7 +5276,7 @@
         <v>1314.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6835,7 +5299,7 @@
         <v>347.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6858,7 +5322,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6881,7 +5345,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6904,7 +5368,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6927,7 +5391,7 @@
         <v>376.25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6950,7 +5414,7 @@
         <v>523.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6973,7 +5437,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6996,7 +5460,7 @@
         <v>923.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7019,7 +5483,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7042,7 +5506,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7065,7 +5529,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7088,7 +5552,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7111,7 +5575,7 @@
         <v>54.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7134,7 +5598,7 @@
         <v>1314.25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -7157,7 +5621,7 @@
         <v>347.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7180,7 +5644,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7203,7 +5667,7 @@
         <v>443.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7226,7 +5690,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7249,7 +5713,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7272,7 +5736,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7295,7 +5759,7 @@
         <v>523.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7318,7 +5782,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7341,7 +5805,7 @@
         <v>379.5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7364,7 +5828,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7387,7 +5851,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7410,7 +5874,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7433,7 +5897,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7456,7 +5920,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7479,7 +5943,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7502,7 +5966,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -7525,7 +5989,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -7548,7 +6012,7 @@
         <v>443.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -7571,7 +6035,7 @@
         <v>446.75</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -7594,7 +6058,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -7617,7 +6081,7 @@
         <v>379.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7640,7 +6104,7 @@
         <v>27.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7663,7 +6127,7 @@
         <v>32.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7686,7 +6150,7 @@
         <v>32.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7709,7 +6173,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -7732,7 +6196,7 @@
         <v>446.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>
@@ -7761,11 +6225,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,7 +6252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7811,7 +6275,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7834,7 +6298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7857,7 +6321,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -7880,7 +6344,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -7903,7 +6367,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -7926,7 +6390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -7949,7 +6413,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2</v>
       </c>
@@ -7972,7 +6436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -7995,7 +6459,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8018,7 +6482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8041,7 +6505,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8064,7 +6528,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8087,7 +6551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8110,7 +6574,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8133,7 +6597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8156,7 +6620,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8179,7 +6643,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8202,7 +6666,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8225,7 +6689,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8248,7 +6712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8271,7 +6735,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8294,7 +6758,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8317,7 +6781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8340,7 +6804,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8363,7 +6827,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8386,7 +6850,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8409,7 +6873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8432,7 +6896,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8455,7 +6919,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8478,7 +6942,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8501,7 +6965,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8524,7 +6988,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8547,7 +7011,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8570,7 +7034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8593,7 +7057,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8616,7 +7080,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8639,7 +7103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>4</v>
       </c>
@@ -8662,7 +7126,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>4</v>
       </c>
@@ -8685,7 +7149,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>4</v>
       </c>
@@ -8708,7 +7172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4</v>
       </c>
@@ -8731,7 +7195,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>4</v>
       </c>
@@ -8754,7 +7218,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>4</v>
       </c>
@@ -8777,7 +7241,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>4</v>
       </c>
@@ -8800,7 +7264,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>4</v>
       </c>
@@ -8823,7 +7287,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>4</v>
       </c>
@@ -8846,7 +7310,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>5</v>
       </c>
@@ -8869,7 +7333,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>5</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0003802</v>
+        <v>0.0003684</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0024911</v>
+        <v>0.002488</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0158681</v>
+        <v>0.0161375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1031649</v>
+        <v>0.1062307</v>
       </c>
       <c r="G2" t="n">
-        <v>0.030476075</v>
+        <v>0.03130615</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002222</v>
+        <v>0.0002294</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009986000000000001</v>
+        <v>0.0009770999999999998</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004080499999999999</v>
+        <v>0.004214299999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0168028</v>
+        <v>0.0172086</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005526025</v>
+        <v>0.00565735</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004516</v>
+        <v>0.0003502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0015549</v>
+        <v>0.0016868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008260100000000001</v>
+        <v>0.008989199999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06199880000000001</v>
+        <v>0.06481820000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01806635</v>
+        <v>0.0189611</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0003232</v>
+        <v>0.0003276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0018906</v>
+        <v>0.0018667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0127174</v>
+        <v>0.0130855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08409269999999999</v>
+        <v>0.08517719999999998</v>
       </c>
       <c r="G5" t="n">
-        <v>0.024755975</v>
+        <v>0.02511424999999999</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0004144999999999999</v>
+        <v>0.0004492</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0012784</v>
+        <v>0.0013391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0047411</v>
+        <v>0.0047131</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0202226</v>
+        <v>0.0205463</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00666415</v>
+        <v>0.006761925</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0004073999999999999</v>
+        <v>0.0004438999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0025583</v>
+        <v>0.0025576</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0177946</v>
+        <v>0.017688</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1037405</v>
+        <v>0.1068749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0311252</v>
+        <v>0.0318911</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0004411000000000001</v>
+        <v>0.0004229</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0023357</v>
+        <v>0.0023426</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0139193</v>
+        <v>0.0142637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0924581</v>
+        <v>0.09560349999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02728855</v>
+        <v>0.028158175</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003429</v>
+        <v>0.0003074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0012162</v>
+        <v>0.0012196</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0044695</v>
+        <v>0.006206999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0206305</v>
+        <v>0.0205205</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006664775</v>
+        <v>0.007063625</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001922</v>
+        <v>0.0001956</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008248999999999999</v>
+        <v>0.0008329000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0037518</v>
+        <v>0.0038716</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0165166</v>
+        <v>0.016938</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005321375</v>
+        <v>0.005459525000000001</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002458</v>
+        <v>0.0002513</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0010747</v>
+        <v>0.0010628</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0044468</v>
+        <v>0.0047366</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0171686</v>
+        <v>0.0179176</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005733975000000001</v>
+        <v>0.005992074999999999</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0002798</v>
+        <v>0.0002563</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0010874</v>
+        <v>0.0010639</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004147199999999999</v>
+        <v>0.0048908</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0179055</v>
+        <v>0.0179692</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005854974999999999</v>
+        <v>0.00604505</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004494</v>
+        <v>0.0003731</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0016798</v>
+        <v>0.0018096</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0084387</v>
+        <v>0.008654999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0626008</v>
+        <v>0.06560050000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.018292175</v>
+        <v>0.01910955</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004409</v>
+        <v>0.0003939</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00228</v>
+        <v>0.0017928</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009727999999999999</v>
+        <v>0.0090501</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08959969999999999</v>
+        <v>0.0628485</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02551215</v>
+        <v>0.018521325</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0004871</v>
+        <v>0.000378</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0018072</v>
+        <v>0.0019325</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009892799999999998</v>
+        <v>0.009461300000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06354599999999999</v>
+        <v>0.06156940000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.018933275</v>
+        <v>0.0183353</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003576</v>
+        <v>0.000399</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0020286</v>
+        <v>0.0020134</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0130217</v>
+        <v>0.0134854</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0856179</v>
+        <v>0.08622579999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02525645</v>
+        <v>0.0255309</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003725</v>
+        <v>0.0003868</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0021584</v>
+        <v>0.0020861</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0127624</v>
+        <v>0.0131498</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07841430000000001</v>
+        <v>0.0818528</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0234269</v>
+        <v>0.024368875</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002842</v>
+        <v>0.0002976</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009480000000000001</v>
+        <v>0.0009486</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0038932</v>
+        <v>0.0039951</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0150894</v>
+        <v>0.0152038</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0050537</v>
+        <v>0.005111275</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003402</v>
+        <v>0.0003508</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0006731</v>
+        <v>0.0006152</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0018104</v>
+        <v>0.0017814</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007290100000000001</v>
+        <v>0.0064014</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00252845</v>
+        <v>0.0022872</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003997</v>
+        <v>0.0003984</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001191</v>
+        <v>0.0011823</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0038188</v>
+        <v>0.0038796</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0137285</v>
+        <v>0.0140266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0047845</v>
+        <v>0.004871725</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004435</v>
+        <v>0.0004354</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0013306</v>
+        <v>0.0013793</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004756400000000001</v>
+        <v>0.0048141</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0203236</v>
+        <v>0.0206799</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006713525000000001</v>
+        <v>0.006827175</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004867</v>
+        <v>0.0004432</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0024897</v>
+        <v>0.0024017</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0141537</v>
+        <v>0.0146608</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0930156</v>
+        <v>0.0958478</v>
       </c>
       <c r="G22" t="n">
-        <v>0.027536425</v>
+        <v>0.028338375</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0003234</v>
+        <v>0.000354</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0012461</v>
+        <v>0.001293</v>
       </c>
       <c r="E23" t="n">
-        <v>0.004929</v>
+        <v>0.005294500000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02095439999999999</v>
+        <v>0.0213876</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006863224999999999</v>
+        <v>0.007082275</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003900999999999999</v>
+        <v>0.0003289</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0013998</v>
+        <v>0.0013463</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0054866</v>
+        <v>0.0051778</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0274053</v>
+        <v>0.0213258</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00867045</v>
+        <v>0.007044700000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003623</v>
+        <v>0.000323</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0013745</v>
+        <v>0.0013866</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0065056</v>
+        <v>0.0065552</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0380145</v>
+        <v>0.03612070000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.011564225</v>
+        <v>0.011096375</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002173</v>
+        <v>0.0002311</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0009245</v>
+        <v>0.0009181999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0039424</v>
+        <v>0.0040453</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0170781</v>
+        <v>0.0174383</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005540575</v>
+        <v>0.005658225</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002373</v>
+        <v>0.0002251</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0009251000000000001</v>
+        <v>0.0009665</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0040049</v>
+        <v>0.0040287</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0170979</v>
+        <v>0.0183482</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005566300000000001</v>
+        <v>0.005892125000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.000286</v>
+        <v>0.0002975</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001165</v>
+        <v>0.0011321</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0044052</v>
+        <v>0.005083800000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0188083</v>
+        <v>0.0184513</v>
       </c>
       <c r="G28" t="n">
-        <v>0.006166125</v>
+        <v>0.006241175</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0004980999999999999</v>
+        <v>0.0004409</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0023678</v>
+        <v>0.0018648</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009801199999999999</v>
+        <v>0.009269099999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09221070000000001</v>
+        <v>0.06486100000000002</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02621945</v>
+        <v>0.01910895</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0005197999999999999</v>
+        <v>0.0004292000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0018407</v>
+        <v>0.0019512</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0103634</v>
+        <v>0.009592199999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0636881</v>
+        <v>0.06253600000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.019103</v>
+        <v>0.01862715</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0005059</v>
+        <v>0.0004117</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0018648</v>
+        <v>0.0022117</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0102805</v>
+        <v>0.0103962</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0660184</v>
+        <v>0.06119030000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0196674</v>
+        <v>0.018552475</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0003882</v>
+        <v>0.0003904</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0021154</v>
+        <v>0.0021697</v>
       </c>
       <c r="E32" t="n">
-        <v>0.012829</v>
+        <v>0.0132219</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07924699999999998</v>
+        <v>0.08200270000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0236449</v>
+        <v>0.024446175</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003117</v>
+        <v>0.0003058000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.000769</v>
+        <v>0.0007485</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002189</v>
+        <v>0.0022917</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0090112</v>
+        <v>0.009020799999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003070225</v>
+        <v>0.0030917</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002702</v>
+        <v>0.0002469</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0008922999999999998</v>
+        <v>0.0008591</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0026597</v>
+        <v>0.0026835</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0100241</v>
+        <v>0.0102389</v>
       </c>
       <c r="G34" t="n">
-        <v>0.003461575</v>
+        <v>0.0035071</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0002996</v>
+        <v>0.0003072</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0010024</v>
+        <v>0.0010439</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004058699999999999</v>
+        <v>0.0040808</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0153943</v>
+        <v>0.0157237</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00518875</v>
+        <v>0.0052889</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003647</v>
+        <v>0.0003565</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0007126</v>
+        <v>0.0006316</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001893</v>
+        <v>0.001766900000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.007457799999999999</v>
+        <v>0.006362700000000002</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002607025</v>
+        <v>0.002279425000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0003788</v>
+        <v>0.0003214</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0008942000000000001</v>
+        <v>0.0008312999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002509700000000001</v>
+        <v>0.002774</v>
       </c>
       <c r="F37" t="n">
-        <v>0.009805699999999999</v>
+        <v>0.0101042</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0033971</v>
+        <v>0.003507725</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0003911</v>
+        <v>0.000407</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0012497</v>
+        <v>0.0012059</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0037453</v>
+        <v>0.003948200000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0140604</v>
+        <v>0.0140218</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004861625</v>
+        <v>0.004895725</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004257</v>
+        <v>0.000398</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0014702</v>
+        <v>0.0014296</v>
       </c>
       <c r="E39" t="n">
-        <v>0.005616999999999999</v>
+        <v>0.005594600000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0273891</v>
+        <v>0.0221935</v>
       </c>
       <c r="G39" t="n">
-        <v>0.008725499999999999</v>
+        <v>0.007403925</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0003506</v>
+        <v>0.0003831</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0014625</v>
+        <v>0.0014085</v>
       </c>
       <c r="E40" t="n">
-        <v>0.006522099999999999</v>
+        <v>0.006494700000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0359814</v>
+        <v>0.0368505</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01107915</v>
+        <v>0.0112842</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0003835999999999999</v>
+        <v>0.0003421</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0015144</v>
+        <v>0.0014808</v>
       </c>
       <c r="E41" t="n">
-        <v>0.006626</v>
+        <v>0.0067362</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0339376</v>
+        <v>0.033001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0106154</v>
+        <v>0.010390025</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0002607999999999999</v>
+        <v>0.0002755</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0010495</v>
+        <v>0.0010742</v>
       </c>
       <c r="E42" t="n">
-        <v>0.004189099999999999</v>
+        <v>0.0041947</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0176665</v>
+        <v>0.0178922</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005791474999999999</v>
+        <v>0.00585915</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0005575000000000001</v>
+        <v>0.0004483999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0019216</v>
+        <v>0.0021871</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0103046</v>
+        <v>0.0108363</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0652185</v>
+        <v>0.062236</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01950055</v>
+        <v>0.01892695</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003532</v>
+        <v>0.0003462</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007993999999999999</v>
+        <v>0.0007460999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0022837</v>
+        <v>0.0024127</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0092254</v>
+        <v>0.008991099999999998</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003165425</v>
+        <v>0.003124024999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0003643</v>
+        <v>0.0003279</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0010731</v>
+        <v>0.0010974</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0029754</v>
+        <v>0.0030093</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0107384</v>
+        <v>0.0111732</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0037878</v>
+        <v>0.00390195</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0002634</v>
+        <v>0.0002713</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0009214999999999999</v>
+        <v>0.000924</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0027912</v>
+        <v>0.002649</v>
       </c>
       <c r="F46" t="n">
-        <v>0.010114</v>
+        <v>0.0104546</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003522525</v>
+        <v>0.003574725</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003728</v>
+        <v>0.0003829</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0009112</v>
+        <v>0.0008588000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0027094</v>
+        <v>0.0027321</v>
       </c>
       <c r="F47" t="n">
-        <v>0.009963200000000002</v>
+        <v>0.0102487</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00348915</v>
+        <v>0.003555625</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0004006</v>
+        <v>0.0003747</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0016041</v>
+        <v>0.0015609</v>
       </c>
       <c r="E48" t="n">
-        <v>0.006669899999999999</v>
+        <v>0.0068438</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0354965</v>
+        <v>0.0335948</v>
       </c>
       <c r="G48" t="n">
-        <v>0.011042775</v>
+        <v>0.01059355</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0003581</v>
+        <v>0.000351</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0011095</v>
+        <v>0.0011243</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0030103</v>
+        <v>0.0031106</v>
       </c>
       <c r="F49" t="n">
-        <v>0.010972</v>
+        <v>0.0111645</v>
       </c>
       <c r="G49" t="n">
-        <v>0.003862475</v>
+        <v>0.0039376</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1813,13 @@
         <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G4" t="n">
-        <v>93.75</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="5">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -1894,7 +1894,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1982,19 +1982,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
         <v>13</v>
       </c>
-      <c r="F11" t="n">
-        <v>14</v>
-      </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="12">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
@@ -2044,7 +2044,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="14">
@@ -2060,16 +2060,16 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>100.75</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="15">
@@ -2088,13 +2088,13 @@
         <v>48</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G15" t="n">
-        <v>91.5</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="16">
@@ -2110,16 +2110,16 @@
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -2188,13 +2188,13 @@
         <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="20">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
@@ -2241,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>13.5</v>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
         <v>11</v>
@@ -2269,7 +2269,7 @@
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="23">
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
@@ -2294,7 +2294,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="24">
@@ -2310,16 +2310,16 @@
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F24" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G24" t="n">
-        <v>95.75</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="25">
@@ -2338,13 +2338,13 @@
         <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" t="n">
         <v>192</v>
       </c>
       <c r="G25" t="n">
-        <v>90.5</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="26">
@@ -2360,16 +2360,16 @@
         <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>15.5</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="27">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
         <v>13</v>
@@ -2419,7 +2419,7 @@
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
         <v>15</v>
@@ -2444,7 +2444,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="30">
@@ -2463,13 +2463,13 @@
         <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>14.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="31">
@@ -2488,13 +2488,13 @@
         <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F31" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G31" t="n">
-        <v>92</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="32">
@@ -2510,16 +2510,16 @@
         <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -2582,19 +2582,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" t="n">
         <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="36">
@@ -2607,19 +2607,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
       </c>
       <c r="E36" t="n">
+        <v>16</v>
+      </c>
+      <c r="F36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
         <v>15</v>
-      </c>
-      <c r="F36" t="n">
-        <v>15</v>
-      </c>
-      <c r="G36" t="n">
-        <v>14.25</v>
       </c>
     </row>
     <row r="37">
@@ -2660,16 +2660,16 @@
         <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G38" t="n">
-        <v>14.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="39">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
         <v>15</v>
@@ -2694,7 +2694,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="n">
-        <v>14.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="40">
@@ -2713,13 +2713,13 @@
         <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G40" t="n">
-        <v>14.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="41">
@@ -2738,13 +2738,13 @@
         <v>48</v>
       </c>
       <c r="E41" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F41" t="n">
         <v>194</v>
       </c>
       <c r="G41" t="n">
-        <v>91</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="42">
@@ -2760,16 +2760,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G42" t="n">
-        <v>15.5</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="43">
@@ -2785,16 +2785,16 @@
         <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
         <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="44">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
         <v>13</v>
       </c>
       <c r="E44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="45">
@@ -2860,16 +2860,16 @@
         <v>13</v>
       </c>
       <c r="D46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>14.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="47">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
@@ -2894,7 +2894,7 @@
         <v>17</v>
       </c>
       <c r="G47" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="48">
@@ -2910,16 +2910,16 @@
         <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" t="n">
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G48" t="n">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="49">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
@@ -2944,7 +2944,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="n">
-        <v>14.5</v>
+        <v>14.75</v>
       </c>
     </row>
   </sheetData>
@@ -3061,16 +3061,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D4" t="n">
-        <v>54.04163056034262</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E4" t="n">
-        <v>111.8406204335659</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F4" t="n">
-        <v>226.8528137423857</v>
+        <v>226.5096679918781</v>
       </c>
       <c r="G4" t="n">
-        <v>104.865746699413</v>
+        <v>104.6083873865323</v>
       </c>
     </row>
     <row r="5">
@@ -3133,19 +3133,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.51166563067375</v>
+        <v>24.55639589508264</v>
       </c>
       <c r="D7" t="n">
-        <v>50.09463980253433</v>
+        <v>49.99028453499244</v>
       </c>
       <c r="E7" t="n">
-        <v>100.7355745101724</v>
+        <v>100.6498597519346</v>
       </c>
       <c r="F7" t="n">
-        <v>203.2847069008655</v>
+        <v>203.2060918012439</v>
       </c>
       <c r="G7" t="n">
-        <v>94.65664671106151</v>
+        <v>94.60065799581339</v>
       </c>
     </row>
     <row r="8">
@@ -3186,16 +3186,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D9" t="n">
-        <v>54.87005768508881</v>
+        <v>55.69848480983499</v>
       </c>
       <c r="E9" t="n">
-        <v>109.4974746830583</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F9" t="n">
-        <v>220.4091629284898</v>
+        <v>222.0660171779821</v>
       </c>
       <c r="G9" t="n">
-        <v>102.8761543394987</v>
+        <v>103.7045814642449</v>
       </c>
     </row>
     <row r="10">
@@ -3233,19 +3233,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28821486957266</v>
+        <v>50.18385960203077</v>
       </c>
       <c r="E11" t="n">
-        <v>101.3106672740879</v>
+        <v>100.873966870703</v>
       </c>
       <c r="F11" t="n">
-        <v>202.7558815510495</v>
+        <v>202.5819648476051</v>
       </c>
       <c r="G11" t="n">
-        <v>94.77232629366651</v>
+        <v>94.60476576617593</v>
       </c>
     </row>
     <row r="12">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D13" t="n">
-        <v>52.16431182490464</v>
+        <v>53.00865358333435</v>
       </c>
       <c r="E13" t="n">
-        <v>106.4081818960021</v>
+        <v>105.8051828191882</v>
       </c>
       <c r="F13" t="n">
-        <v>213.9018613939792</v>
+        <v>213.5856092072074</v>
       </c>
       <c r="G13" t="n">
-        <v>99.63732995997091</v>
+        <v>99.62978514978414</v>
       </c>
     </row>
     <row r="14">
@@ -3311,16 +3311,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D14" t="n">
-        <v>57.79898987322334</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E14" t="n">
-        <v>117.3553390593274</v>
+        <v>111.4974746830583</v>
       </c>
       <c r="F14" t="n">
-        <v>237.2964645562816</v>
+        <v>225.9238815542512</v>
       </c>
       <c r="G14" t="n">
-        <v>109.7946788875475</v>
+        <v>104.754833995939</v>
       </c>
     </row>
     <row r="15">
@@ -3339,13 +3339,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E15" t="n">
-        <v>111.254833995939</v>
+        <v>109.254833995939</v>
       </c>
       <c r="F15" t="n">
-        <v>221.3380951166243</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G15" t="n">
-        <v>103.3406204335659</v>
+        <v>102.1941738241592</v>
       </c>
     </row>
     <row r="16">
@@ -3361,16 +3361,16 @@
         <v>24.77927174436484</v>
       </c>
       <c r="D16" t="n">
-        <v>50.07562676884913</v>
+        <v>49.97127150130724</v>
       </c>
       <c r="E16" t="n">
-        <v>100.7133916940067</v>
+        <v>100.6276769357689</v>
       </c>
       <c r="F16" t="n">
-        <v>202.1164240699425</v>
+        <v>202.0378089703209</v>
       </c>
       <c r="G16" t="n">
-        <v>94.42117856929082</v>
+        <v>94.35400728794046</v>
       </c>
     </row>
     <row r="17">
@@ -3439,13 +3439,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E19" t="n">
-        <v>105.4974746830583</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F19" t="n">
-        <v>212.4091629284898</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="G19" t="n">
-        <v>99.31549416771887</v>
+        <v>101.4870670429727</v>
       </c>
     </row>
     <row r="20">
@@ -3483,19 +3483,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.91268706482925</v>
+        <v>24.95741732923815</v>
       </c>
       <c r="D21" t="n">
-        <v>51.78969465813791</v>
+        <v>51.68533939059601</v>
       </c>
       <c r="E21" t="n">
-        <v>104.870607101803</v>
+        <v>104.7848923435651</v>
       </c>
       <c r="F21" t="n">
-        <v>211.062613349125</v>
+        <v>208.865000477033</v>
       </c>
       <c r="G21" t="n">
-        <v>98.15890054347378</v>
+        <v>97.57316238510808</v>
       </c>
     </row>
     <row r="22">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D22" t="n">
-        <v>49.63823118189693</v>
+        <v>49.53387591435503</v>
       </c>
       <c r="E22" t="n">
-        <v>100.5762275063179</v>
+        <v>100.49051274808</v>
       </c>
       <c r="F22" t="n">
-        <v>202.6930670518368</v>
+        <v>202.6144519522151</v>
       </c>
       <c r="G22" t="n">
-        <v>94.41051680500189</v>
+        <v>94.35452808975376</v>
       </c>
     </row>
     <row r="23">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D23" t="n">
-        <v>52.16431182490464</v>
+        <v>53.00865358333435</v>
       </c>
       <c r="E23" t="n">
-        <v>104.9456068473253</v>
+        <v>105.8051828191882</v>
       </c>
       <c r="F23" t="n">
-        <v>210.9710748647263</v>
+        <v>210.6548226779546</v>
       </c>
       <c r="G23" t="n">
-        <v>98.53898956548846</v>
+        <v>98.89708851747093</v>
       </c>
     </row>
     <row r="24">
@@ -3561,16 +3561,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D24" t="n">
-        <v>56.62741699796952</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E24" t="n">
-        <v>113.8406204335659</v>
+        <v>111.7401153701776</v>
       </c>
       <c r="F24" t="n">
-        <v>230.2670273047588</v>
+        <v>221.2375900532359</v>
       </c>
       <c r="G24" t="n">
-        <v>106.865746699413</v>
+        <v>103.6439212924651</v>
       </c>
     </row>
     <row r="25">
@@ -3589,13 +3589,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E25" t="n">
-        <v>110.6690475583121</v>
+        <v>109.254833995939</v>
       </c>
       <c r="F25" t="n">
-        <v>219.5807358037436</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="G25" t="n">
-        <v>102.754833995939</v>
+        <v>102.1941738241592</v>
       </c>
     </row>
     <row r="26">
@@ -3611,16 +3611,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D26" t="n">
-        <v>52.12986930905443</v>
+        <v>52.02551404151253</v>
       </c>
       <c r="E26" t="n">
-        <v>104.1104143878834</v>
+        <v>104.0246996296456</v>
       </c>
       <c r="F26" t="n">
-        <v>208.238780480961</v>
+        <v>208.1601653813395</v>
       </c>
       <c r="G26" t="n">
-        <v>97.64968979182635</v>
+        <v>97.58251851047601</v>
       </c>
     </row>
     <row r="27">
@@ -3658,19 +3658,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D28" t="n">
-        <v>49.68775075393261</v>
+        <v>49.58339548639072</v>
       </c>
       <c r="E28" t="n">
-        <v>100.5352189129114</v>
+        <v>100.4495041546735</v>
       </c>
       <c r="F28" t="n">
-        <v>202.6185530612044</v>
+        <v>202.5399379615828</v>
       </c>
       <c r="G28" t="n">
-        <v>94.39401605200109</v>
+        <v>94.33802733675296</v>
       </c>
     </row>
     <row r="29">
@@ -3683,19 +3683,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D29" t="n">
-        <v>54.86891619381502</v>
+        <v>52.88838368210894</v>
       </c>
       <c r="E29" t="n">
-        <v>108.9083792447049</v>
+        <v>105.3137170479438</v>
       </c>
       <c r="F29" t="n">
-        <v>218.889304818762</v>
+        <v>212.7803199337219</v>
       </c>
       <c r="G29" t="n">
-        <v>102.1853912455699</v>
+        <v>99.27552891329529</v>
       </c>
     </row>
     <row r="30">
@@ -3708,19 +3708,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D30" t="n">
-        <v>52.04404192367922</v>
+        <v>51.93968665613734</v>
       </c>
       <c r="E30" t="n">
-        <v>104.9195290080072</v>
+        <v>104.0707552199418</v>
       </c>
       <c r="F30" t="n">
-        <v>210.5251826880072</v>
+        <v>208.1469038539547</v>
       </c>
       <c r="G30" t="n">
-        <v>98.3909295861728</v>
+        <v>97.56926017986011</v>
       </c>
     </row>
     <row r="31">
@@ -3736,16 +3736,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D31" t="n">
-        <v>54.04163056034262</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E31" t="n">
-        <v>111.254833995939</v>
+        <v>110.9116882454314</v>
       </c>
       <c r="F31" t="n">
-        <v>224.9949493661166</v>
+        <v>223.2375900532359</v>
       </c>
       <c r="G31" t="n">
-        <v>104.254833995939</v>
+        <v>103.9368145112785</v>
       </c>
     </row>
     <row r="32">
@@ -3761,16 +3761,16 @@
         <v>24.77927174436484</v>
       </c>
       <c r="D32" t="n">
-        <v>50.07562676884913</v>
+        <v>49.97127150130724</v>
       </c>
       <c r="E32" t="n">
-        <v>100.7133916940067</v>
+        <v>100.6276769357689</v>
       </c>
       <c r="F32" t="n">
-        <v>202.1164240699425</v>
+        <v>202.0378089703209</v>
       </c>
       <c r="G32" t="n">
-        <v>94.42117856929082</v>
+        <v>94.35400728794046</v>
       </c>
     </row>
     <row r="33">
@@ -3833,19 +3833,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D35" t="n">
-        <v>50.73396656813706</v>
+        <v>50.62961130059517</v>
       </c>
       <c r="E35" t="n">
-        <v>102.4998602764756</v>
+        <v>101.4685633718968</v>
       </c>
       <c r="F35" t="n">
-        <v>206.0932862186818</v>
+        <v>203.8956733465899</v>
       </c>
       <c r="G35" t="n">
-        <v>96.01541363581259</v>
+        <v>95.19327994086169</v>
       </c>
     </row>
     <row r="36">
@@ -3858,19 +3858,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D36" t="n">
-        <v>53.44654890763028</v>
+        <v>53.34219364008838</v>
       </c>
       <c r="E36" t="n">
-        <v>104.870607101803</v>
+        <v>107.010883072478</v>
       </c>
       <c r="F36" t="n">
-        <v>211.062613349125</v>
+        <v>214.3797191027945</v>
       </c>
       <c r="G36" t="n">
-        <v>98.52857770962854</v>
+        <v>99.87801688993142</v>
       </c>
     </row>
     <row r="37">
@@ -3911,16 +3911,16 @@
         <v>24.77927174436484</v>
       </c>
       <c r="D38" t="n">
-        <v>51.78969465813791</v>
+        <v>51.34219364008838</v>
       </c>
       <c r="E38" t="n">
-        <v>104.870607101803</v>
+        <v>103.8393101972242</v>
       </c>
       <c r="F38" t="n">
-        <v>211.062613349125</v>
+        <v>208.865000477033</v>
       </c>
       <c r="G38" t="n">
-        <v>98.12554671335766</v>
+        <v>97.2064440146776</v>
       </c>
     </row>
     <row r="39">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D39" t="n">
-        <v>53.71302599228926</v>
+        <v>52.88838368210894</v>
       </c>
       <c r="E39" t="n">
-        <v>107.4930298063066</v>
+        <v>105.0360348523933</v>
       </c>
       <c r="F39" t="n">
-        <v>215.9835446283804</v>
+        <v>209.8495334044691</v>
       </c>
       <c r="G39" t="n">
-        <v>100.8161412879935</v>
+        <v>98.47341173209446</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D40" t="n">
-        <v>52.04404192367922</v>
+        <v>51.93968665613734</v>
       </c>
       <c r="E40" t="n">
-        <v>104.5946212021782</v>
+        <v>104.0707552199418</v>
       </c>
       <c r="F40" t="n">
-        <v>210.0885646909448</v>
+        <v>208.1469038539547</v>
       </c>
       <c r="G40" t="n">
-        <v>98.20054813544995</v>
+        <v>97.56926017986011</v>
       </c>
     </row>
     <row r="41">
@@ -3986,16 +3986,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D41" t="n">
-        <v>54.04163056034262</v>
+        <v>54.87005768508881</v>
       </c>
       <c r="E41" t="n">
-        <v>110.6690475583121</v>
+        <v>110.9116882454314</v>
       </c>
       <c r="F41" t="n">
         <v>223.2375900532359</v>
       </c>
       <c r="G41" t="n">
-        <v>103.6690475583121</v>
+        <v>103.9368145112785</v>
       </c>
     </row>
     <row r="42">
@@ -4011,16 +4011,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D42" t="n">
-        <v>52.12986930905443</v>
+        <v>52.02551404151253</v>
       </c>
       <c r="E42" t="n">
-        <v>104.5924723997756</v>
+        <v>104.5067576415378</v>
       </c>
       <c r="F42" t="n">
-        <v>208.238780480961</v>
+        <v>208.1601653813395</v>
       </c>
       <c r="G42" t="n">
-        <v>97.77020429479941</v>
+        <v>97.70303301344907</v>
       </c>
     </row>
     <row r="43">
@@ -4033,19 +4033,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D43" t="n">
-        <v>52.04404192367922</v>
+        <v>52.88838368210894</v>
       </c>
       <c r="E43" t="n">
-        <v>104.9195290080072</v>
+        <v>105.481659072179</v>
       </c>
       <c r="F43" t="n">
-        <v>211.5758187952866</v>
+        <v>209.8495334044691</v>
       </c>
       <c r="G43" t="n">
-        <v>98.65358861299265</v>
+        <v>98.58481778704089</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D44" t="n">
-        <v>51.07711231864469</v>
+        <v>50.97275705110279</v>
       </c>
       <c r="E44" t="n">
-        <v>103.4454424228165</v>
+        <v>102.4141455182377</v>
       </c>
       <c r="F44" t="n">
-        <v>208.2122839911521</v>
+        <v>206.0146711190602</v>
       </c>
       <c r="G44" t="n">
-        <v>96.86734505314232</v>
+        <v>96.04521135819138</v>
       </c>
     </row>
     <row r="45">
@@ -4111,16 +4111,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D46" t="n">
-        <v>53.44654890763028</v>
+        <v>52.99904788958077</v>
       </c>
       <c r="E46" t="n">
-        <v>106.8203763569287</v>
+        <v>105.7890794523499</v>
       </c>
       <c r="F46" t="n">
-        <v>214.3213788747858</v>
+        <v>212.123766002694</v>
       </c>
       <c r="G46" t="n">
-        <v>100.1769997821878</v>
+        <v>99.2578970835078</v>
       </c>
     </row>
     <row r="47">
@@ -4133,19 +4133,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.73454147995595</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D47" t="n">
-        <v>53.44654890763028</v>
+        <v>53.34219364008838</v>
       </c>
       <c r="E47" t="n">
-        <v>108.0421799770567</v>
+        <v>107.9564652188189</v>
       </c>
       <c r="F47" t="n">
-        <v>216.5773319748864</v>
+        <v>216.4987168752647</v>
       </c>
       <c r="G47" t="n">
-        <v>100.7001505848823</v>
+        <v>100.6441618696342</v>
       </c>
     </row>
     <row r="48">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D48" t="n">
-        <v>52.04404192367922</v>
+        <v>52.88838368210894</v>
       </c>
       <c r="E48" t="n">
-        <v>104.5946212021782</v>
+        <v>105.481659072179</v>
       </c>
       <c r="F48" t="n">
-        <v>211.1392007982242</v>
+        <v>209.8495334044691</v>
       </c>
       <c r="G48" t="n">
-        <v>98.46320716226978</v>
+        <v>98.58481778704089</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26.07496472499763</v>
+        <v>26.11969498940653</v>
       </c>
       <c r="D49" t="n">
-        <v>53.44654890763028</v>
+        <v>53.34219364008838</v>
       </c>
       <c r="E49" t="n">
-        <v>106.8203763569287</v>
+        <v>106.7346615986908</v>
       </c>
       <c r="F49" t="n">
-        <v>214.3213788747858</v>
+        <v>214.2427637751643</v>
       </c>
       <c r="G49" t="n">
-        <v>100.1658172160856</v>
+        <v>100.1098285008375</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F4" t="n">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="G4" t="n">
-        <v>197.5</v>
+        <v>212.25</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="F9" t="n">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="G9" t="n">
-        <v>203.75</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F13" t="n">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="G13" t="n">
-        <v>197.5</v>
+        <v>212.25</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="F14" t="n">
-        <v>426</v>
+        <v>565</v>
       </c>
       <c r="G14" t="n">
-        <v>175.25</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="15">
@@ -4584,19 +4584,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
         <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F15" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G15" t="n">
-        <v>217.5</v>
+        <v>216.75</v>
       </c>
     </row>
     <row r="16">
@@ -4684,19 +4684,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="F23" t="n">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="G23" t="n">
-        <v>203.75</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F24" t="n">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="G24" t="n">
-        <v>202</v>
+        <v>197.25</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F25" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="G25" t="n">
-        <v>190.75</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="F29" t="n">
-        <v>426</v>
+        <v>565</v>
       </c>
       <c r="G29" t="n">
-        <v>175.25</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="30">
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
         <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F30" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G30" t="n">
-        <v>217.5</v>
+        <v>216.75</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F31" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="G31" t="n">
-        <v>211.5</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32">
@@ -5037,7 +5037,7 @@
         <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
         <v>13</v>
@@ -5046,7 +5046,7 @@
         <v>14</v>
       </c>
       <c r="G33" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -5109,19 +5109,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
         <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="37">
@@ -5137,10 +5137,10 @@
         <v>10</v>
       </c>
       <c r="D37" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" t="n">
         <v>16</v>
-      </c>
-      <c r="E37" t="n">
-        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E39" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F39" t="n">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="G39" t="n">
-        <v>202</v>
+        <v>197.25</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F40" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="G40" t="n">
-        <v>190.75</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="41">
@@ -5237,16 +5237,16 @@
         <v>22</v>
       </c>
       <c r="D41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F41" t="n">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="G41" t="n">
-        <v>202.5</v>
+        <v>185.75</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D43" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E43" t="n">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F43" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="G43" t="n">
-        <v>211.5</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44">
@@ -5312,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44" t="n">
         <v>13</v>
@@ -5321,7 +5321,7 @@
         <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -5387,10 +5387,10 @@
         <v>10</v>
       </c>
       <c r="D47" t="n">
+        <v>15</v>
+      </c>
+      <c r="E47" t="n">
         <v>16</v>
-      </c>
-      <c r="E47" t="n">
-        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -5412,16 +5412,16 @@
         <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E48" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F48" t="n">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="G48" t="n">
-        <v>202.5</v>
+        <v>185.75</v>
       </c>
     </row>
     <row r="49">
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F4" t="n">
-        <v>1117</v>
+        <v>1079</v>
       </c>
       <c r="G4" t="n">
-        <v>376.25</v>
+        <v>367.75</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
         <v>91</v>
       </c>
       <c r="E9" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="F9" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G9" t="n">
-        <v>347.75</v>
+        <v>357.25</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F13" t="n">
-        <v>1117</v>
+        <v>1079</v>
       </c>
       <c r="G13" t="n">
-        <v>376.25</v>
+        <v>367.75</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E14" t="n">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="F14" t="n">
-        <v>1622</v>
+        <v>1053</v>
       </c>
       <c r="G14" t="n">
-        <v>523.5</v>
+        <v>365.5</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F15" t="n">
-        <v>1029</v>
+        <v>994</v>
       </c>
       <c r="G15" t="n">
-        <v>364</v>
+        <v>353.5</v>
       </c>
     </row>
     <row r="16">
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E19" t="n">
+        <v>26</v>
+      </c>
+      <c r="F19" t="n">
         <v>27</v>
       </c>
-      <c r="E19" t="n">
-        <v>29</v>
-      </c>
-      <c r="F19" t="n">
-        <v>29</v>
-      </c>
       <c r="G19" t="n">
-        <v>27.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>91</v>
       </c>
       <c r="E23" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="F23" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G23" t="n">
-        <v>347.75</v>
+        <v>357.25</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E24" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F24" t="n">
-        <v>1335</v>
+        <v>980</v>
       </c>
       <c r="G24" t="n">
-        <v>452.5</v>
+        <v>358.25</v>
       </c>
     </row>
     <row r="25">
@@ -6088,16 +6088,16 @@
         <v>33</v>
       </c>
       <c r="D25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F25" t="n">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="G25" t="n">
-        <v>443.5</v>
+        <v>446.5</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="E29" t="n">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="F29" t="n">
-        <v>1622</v>
+        <v>1053</v>
       </c>
       <c r="G29" t="n">
-        <v>523.5</v>
+        <v>365.5</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E30" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F30" t="n">
-        <v>1029</v>
+        <v>994</v>
       </c>
       <c r="G30" t="n">
-        <v>364</v>
+        <v>353.5</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E31" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="F31" t="n">
-        <v>1100</v>
+        <v>1052</v>
       </c>
       <c r="G31" t="n">
-        <v>379.5</v>
+        <v>371.75</v>
       </c>
     </row>
     <row r="32">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
+        <v>26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26</v>
+      </c>
+      <c r="F36" t="n">
         <v>27</v>
       </c>
-      <c r="E36" t="n">
-        <v>29</v>
-      </c>
-      <c r="F36" t="n">
-        <v>29</v>
-      </c>
       <c r="G36" t="n">
-        <v>27.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="37">
@@ -6385,19 +6385,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F37" t="n">
         <v>31</v>
       </c>
       <c r="G37" t="n">
-        <v>29.5</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D39" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E39" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="F39" t="n">
-        <v>1335</v>
+        <v>980</v>
       </c>
       <c r="G39" t="n">
-        <v>452.5</v>
+        <v>358.25</v>
       </c>
     </row>
     <row r="40">
@@ -6463,16 +6463,16 @@
         <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E40" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F40" t="n">
-        <v>1304</v>
+        <v>1313</v>
       </c>
       <c r="G40" t="n">
-        <v>443.5</v>
+        <v>446.5</v>
       </c>
     </row>
     <row r="41">
@@ -6488,16 +6488,16 @@
         <v>33</v>
       </c>
       <c r="D41" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E41" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F41" t="n">
-        <v>1311</v>
+        <v>1297</v>
       </c>
       <c r="G41" t="n">
-        <v>446.75</v>
+        <v>444.75</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E43" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="F43" t="n">
-        <v>1100</v>
+        <v>1052</v>
       </c>
       <c r="G43" t="n">
-        <v>379.5</v>
+        <v>371.75</v>
       </c>
     </row>
     <row r="44">
@@ -6635,19 +6635,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F47" t="n">
         <v>31</v>
       </c>
       <c r="G47" t="n">
-        <v>29.5</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="48">
@@ -6663,16 +6663,16 @@
         <v>33</v>
       </c>
       <c r="D48" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E48" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F48" t="n">
-        <v>1311</v>
+        <v>1297</v>
       </c>
       <c r="G48" t="n">
-        <v>446.75</v>
+        <v>444.75</v>
       </c>
     </row>
     <row r="49">
@@ -6817,13 +6817,13 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>19.75</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -6898,7 +6898,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -6936,19 +6936,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10">
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="12">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>13</v>
@@ -7048,7 +7048,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="14">
@@ -7064,16 +7064,16 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="15">
@@ -7089,16 +7089,16 @@
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="16">
@@ -7114,16 +7114,16 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>10.75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -7192,13 +7192,13 @@
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="20">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>13</v>
@@ -7245,7 +7245,7 @@
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>11.5</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
@@ -7273,7 +7273,7 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
@@ -7298,7 +7298,7 @@
         <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="24">
@@ -7317,13 +7317,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="25">
@@ -7339,16 +7339,16 @@
         <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="26">
@@ -7364,16 +7364,16 @@
         <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="27">
@@ -7411,7 +7411,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
         <v>11</v>
@@ -7423,7 +7423,7 @@
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
         <v>13</v>
@@ -7448,7 +7448,7 @@
         <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="30">
@@ -7467,13 +7467,13 @@
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="31">
@@ -7492,13 +7492,13 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>22.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="32">
@@ -7514,16 +7514,16 @@
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>10.75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -7586,19 +7586,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
         <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="36">
@@ -7611,19 +7611,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
         <v>13</v>
       </c>
       <c r="E36" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="n">
         <v>13</v>
-      </c>
-      <c r="F36" t="n">
-        <v>13</v>
-      </c>
-      <c r="G36" t="n">
-        <v>12.25</v>
       </c>
     </row>
     <row r="37">
@@ -7664,16 +7664,16 @@
         <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" t="n">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="39">
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
         <v>13</v>
@@ -7698,7 +7698,7 @@
         <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="40">
@@ -7717,13 +7717,13 @@
         <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="41">
@@ -7742,13 +7742,13 @@
         <v>20</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -7764,16 +7764,16 @@
         <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="43">
@@ -7789,16 +7789,16 @@
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
         <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="44">
@@ -7811,19 +7811,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
         <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="45">
@@ -7864,16 +7864,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>12.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="47">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
         <v>13</v>
@@ -7898,7 +7898,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>13.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="48">
@@ -7914,16 +7914,16 @@
         <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" t="n">
         <v>13</v>
       </c>
       <c r="F48" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G48" t="n">
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="49">
@@ -7936,7 +7936,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
         <v>13</v>
@@ -7948,7 +7948,7 @@
         <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
         <v>152</v>
       </c>
       <c r="D4" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E4" t="n">
-        <v>1596</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>494</v>
+        <v>552</v>
       </c>
       <c r="E9" t="n">
-        <v>1491</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
         <v>152</v>
       </c>
       <c r="D13" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="E13" t="n">
-        <v>1596</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="14">
@@ -8230,13 +8230,13 @@
         <v>53</v>
       </c>
       <c r="C14" t="n">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="D14" t="n">
         <v>507</v>
       </c>
       <c r="E14" t="n">
-        <v>2048</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="15">
@@ -8249,13 +8249,13 @@
         <v>54</v>
       </c>
       <c r="C15" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D15" t="n">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="E15" t="n">
-        <v>1600</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" t="n">
+        <v>37</v>
+      </c>
+      <c r="E19" t="n">
         <v>39</v>
-      </c>
-      <c r="D19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" t="n">
-        <v>494</v>
+        <v>552</v>
       </c>
       <c r="E23" t="n">
-        <v>1491</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D24" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E24" t="n">
-        <v>1867</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D25" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E25" t="n">
-        <v>1764</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="26">
@@ -8515,13 +8515,13 @@
         <v>53</v>
       </c>
       <c r="C29" t="n">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="D29" t="n">
         <v>507</v>
       </c>
       <c r="E29" t="n">
-        <v>2048</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="30">
@@ -8534,13 +8534,13 @@
         <v>54</v>
       </c>
       <c r="C30" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D30" t="n">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="E30" t="n">
-        <v>1600</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D31" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E31" t="n">
-        <v>1640</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="32">
@@ -8591,7 +8591,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" t="n">
         <v>42</v>
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
+        <v>37</v>
+      </c>
+      <c r="D36" t="n">
+        <v>37</v>
+      </c>
+      <c r="E36" t="n">
         <v>39</v>
-      </c>
-      <c r="D36" t="n">
-        <v>40</v>
-      </c>
-      <c r="E36" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -8664,13 +8664,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D37" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E37" t="n">
         <v>47</v>
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D39" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E39" t="n">
-        <v>1867</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C40" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D40" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E40" t="n">
-        <v>1764</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="41">
@@ -8743,13 +8743,13 @@
         <v>55</v>
       </c>
       <c r="C41" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D41" t="n">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E41" t="n">
-        <v>1805</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="n">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D43" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E43" t="n">
-        <v>1640</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="44">
@@ -8800,7 +8800,7 @@
         <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" t="n">
         <v>42</v>
@@ -8854,13 +8854,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E47" t="n">
         <v>47</v>
@@ -8876,13 +8876,13 @@
         <v>55</v>
       </c>
       <c r="C48" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D48" t="n">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E48" t="n">
-        <v>1805</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="49">

--- a/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_2_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0003684</v>
+        <v>0.0003786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002488</v>
+        <v>0.002459499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0161375</v>
+        <v>0.015765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1062307</v>
+        <v>0.1020895</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03130615</v>
+        <v>0.03017315</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002294</v>
+        <v>0.0002603</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009770999999999998</v>
+        <v>0.000967</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004214299999999999</v>
+        <v>0.0039869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0172086</v>
+        <v>0.016616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00565735</v>
+        <v>0.005457549999999999</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0003502</v>
+        <v>0.0002895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0016868</v>
+        <v>0.0013014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008989199999999999</v>
+        <v>0.008706700000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06481820000000001</v>
+        <v>0.0652737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0189611</v>
+        <v>0.018892825</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0003276</v>
+        <v>0.0003137</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0018667</v>
+        <v>0.0018837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0130855</v>
+        <v>0.0125769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08517719999999998</v>
+        <v>0.08295180000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02511424999999999</v>
+        <v>0.024431525</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0004492</v>
+        <v>0.0003942</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0013391</v>
+        <v>0.0012408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0047131</v>
+        <v>0.0046645</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0205463</v>
+        <v>0.0199562</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006761925</v>
+        <v>0.006563925</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0004438999999999999</v>
+        <v>0.0004014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0025576</v>
+        <v>0.0025718</v>
       </c>
       <c r="E7" t="n">
-        <v>0.017688</v>
+        <v>0.0172327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1068749</v>
+        <v>0.102782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0318911</v>
+        <v>0.030746975</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0004229</v>
+        <v>0.0004208999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0023426</v>
+        <v>0.0023288</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0142637</v>
+        <v>0.0138775</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09560349999999999</v>
+        <v>0.091304</v>
       </c>
       <c r="G8" t="n">
-        <v>0.028158175</v>
+        <v>0.0269828</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0003074</v>
+        <v>0.0003859000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0012196</v>
+        <v>0.0015016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006206999999999999</v>
+        <v>0.007045899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0205205</v>
+        <v>0.0500694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007063625</v>
+        <v>0.0147507</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0001956</v>
+        <v>0.0002086</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008329000000000001</v>
+        <v>0.0008114</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0038716</v>
+        <v>0.0037747</v>
       </c>
       <c r="F10" t="n">
-        <v>0.016938</v>
+        <v>0.0163489</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005459525000000001</v>
+        <v>0.005285900000000001</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002513</v>
+        <v>0.0002461</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0010628</v>
+        <v>0.0010417</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0047366</v>
+        <v>0.004291400000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0179176</v>
+        <v>0.0170104</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005992074999999999</v>
+        <v>0.0056474</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0002563</v>
+        <v>0.0002528</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0010639</v>
+        <v>0.001046</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0048908</v>
+        <v>0.0041608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0179692</v>
+        <v>0.0174055</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00604505</v>
+        <v>0.005716275</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0003731</v>
+        <v>0.0003184</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0018096</v>
+        <v>0.0013973</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008654999999999999</v>
+        <v>0.0088679</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06560050000000001</v>
+        <v>0.0653053</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01910955</v>
+        <v>0.018972225</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0003939</v>
+        <v>0.0003083</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0017928</v>
+        <v>0.0015527</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0090501</v>
+        <v>0.0087175</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0628485</v>
+        <v>0.0645131</v>
       </c>
       <c r="G14" t="n">
-        <v>0.018521325</v>
+        <v>0.0187729</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.000378</v>
+        <v>0.000316</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0019325</v>
+        <v>0.0017797</v>
       </c>
       <c r="E15" t="n">
-        <v>0.009461300000000001</v>
+        <v>0.0118183</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06156940000000001</v>
+        <v>0.0779162</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0183353</v>
+        <v>0.02295755</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000399</v>
+        <v>0.0003385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0020134</v>
+        <v>0.002006</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0134854</v>
+        <v>0.013008</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08622579999999999</v>
+        <v>0.0830791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0255309</v>
+        <v>0.0246079</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003868</v>
+        <v>0.0003681</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0020861</v>
+        <v>0.0020199</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0131498</v>
+        <v>0.0126164</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0818528</v>
+        <v>0.07907900000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.024368875</v>
+        <v>0.02352085</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002976</v>
+        <v>0.0002647</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0009486</v>
+        <v>0.0009048999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0039951</v>
+        <v>0.0039163</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0152038</v>
+        <v>0.0149901</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005111275</v>
+        <v>0.005018999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003508</v>
+        <v>0.0004807</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0006152</v>
+        <v>0.0014169</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0017814</v>
+        <v>0.0044688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0064014</v>
+        <v>0.0164675</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0022872</v>
+        <v>0.005708475000000001</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0003984</v>
+        <v>0.0003567</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011823</v>
+        <v>0.0011459</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0038796</v>
+        <v>0.0036871</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0140266</v>
+        <v>0.0135344</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004871725</v>
+        <v>0.004681025</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004354</v>
+        <v>0.0004112</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0013793</v>
+        <v>0.0012718</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0048141</v>
+        <v>0.0047535</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0206799</v>
+        <v>0.0200979</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006827175</v>
+        <v>0.0066336</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004432</v>
+        <v>0.0004614</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0024017</v>
+        <v>0.0023653</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0146608</v>
+        <v>0.0143297</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0958478</v>
+        <v>0.0921133</v>
       </c>
       <c r="G22" t="n">
-        <v>0.028338375</v>
+        <v>0.027317425</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000354</v>
+        <v>0.0004045</v>
       </c>
       <c r="D23" t="n">
-        <v>0.001293</v>
+        <v>0.0015233</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005294500000000001</v>
+        <v>0.0074101</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0213876</v>
+        <v>0.0502965</v>
       </c>
       <c r="G23" t="n">
-        <v>0.007082275</v>
+        <v>0.0149086</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003289</v>
+        <v>0.000361</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0013463</v>
+        <v>0.0013466</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0051778</v>
+        <v>0.0067716</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0213258</v>
+        <v>0.0554752</v>
       </c>
       <c r="G24" t="n">
-        <v>0.007044700000000001</v>
+        <v>0.0159886</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.000323</v>
+        <v>0.0003405</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0013866</v>
+        <v>0.0015914</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0065552</v>
+        <v>0.008986999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03612070000000001</v>
+        <v>0.06489160000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.011096375</v>
+        <v>0.018952625</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002311</v>
+        <v>0.0002215</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0009181999999999999</v>
+        <v>0.000907</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0040453</v>
+        <v>0.0038228</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0174383</v>
+        <v>0.016715</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005658225</v>
+        <v>0.005416575</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002251</v>
+        <v>0.0002277</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0009665</v>
+        <v>0.0009075</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0040287</v>
+        <v>0.0039246</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0183482</v>
+        <v>0.01677</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005892125000000001</v>
+        <v>0.00545745</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002975</v>
+        <v>0.0002787</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0011321</v>
+        <v>0.0011036</v>
       </c>
       <c r="E28" t="n">
-        <v>0.005083800000000001</v>
+        <v>0.0043012</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0184513</v>
+        <v>0.0180695</v>
       </c>
       <c r="G28" t="n">
-        <v>0.006241175</v>
+        <v>0.005938249999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0004409</v>
+        <v>0.000339</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0018648</v>
+        <v>0.0015759</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009269099999999999</v>
+        <v>0.0091185</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06486100000000002</v>
+        <v>0.0660766</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01910895</v>
+        <v>0.0192775</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0004292000000000001</v>
+        <v>0.0003371</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0019512</v>
+        <v>0.0018115</v>
       </c>
       <c r="E30" t="n">
-        <v>0.009592199999999999</v>
+        <v>0.0121434</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06253600000000001</v>
+        <v>0.07683740000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01862715</v>
+        <v>0.02278235</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0004117</v>
+        <v>0.0003623</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0022117</v>
+        <v>0.0019198</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0103962</v>
+        <v>0.0120505</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06119030000000001</v>
+        <v>0.0851102</v>
       </c>
       <c r="G31" t="n">
-        <v>0.018552475</v>
+        <v>0.0248607</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0003904</v>
+        <v>0.0004025</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0021697</v>
+        <v>0.0020999</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0132219</v>
+        <v>0.0129639</v>
       </c>
       <c r="F32" t="n">
-        <v>0.08200270000000001</v>
+        <v>0.0802476</v>
       </c>
       <c r="G32" t="n">
-        <v>0.024446175</v>
+        <v>0.023928475</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003058000000000001</v>
+        <v>0.0002369</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0007485</v>
+        <v>0.0008399</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0022917</v>
+        <v>0.0022537</v>
       </c>
       <c r="F33" t="n">
-        <v>0.009020799999999999</v>
+        <v>0.007091200000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0030917</v>
+        <v>0.002605425</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0002469</v>
+        <v>0.0002337</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0008591</v>
+        <v>0.0008489999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0026835</v>
+        <v>0.0026058</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0102389</v>
+        <v>0.0099659</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0035071</v>
+        <v>0.0034136</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0003072</v>
+        <v>0.0002773</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0010439</v>
+        <v>0.0009379</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0040808</v>
+        <v>0.003955</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0157237</v>
+        <v>0.0149139</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0052889</v>
+        <v>0.005021025</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003565</v>
+        <v>0.0005220000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0006316</v>
+        <v>0.0014268</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001766900000000001</v>
+        <v>0.0045181</v>
       </c>
       <c r="F36" t="n">
-        <v>0.006362700000000002</v>
+        <v>0.0165218</v>
       </c>
       <c r="G36" t="n">
-        <v>0.002279425000000001</v>
+        <v>0.005747175</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0003214</v>
+        <v>0.0004187</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0008312999999999999</v>
+        <v>0.0013111</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002774</v>
+        <v>0.0039867</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0101042</v>
+        <v>0.0142887</v>
       </c>
       <c r="G37" t="n">
-        <v>0.003507725</v>
+        <v>0.005001299999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.000407</v>
+        <v>0.0003674</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0012059</v>
+        <v>0.0011958</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003948200000000001</v>
+        <v>0.003686399999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0140218</v>
+        <v>0.0137004</v>
       </c>
       <c r="G38" t="n">
-        <v>0.004895725</v>
+        <v>0.0047375</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.000398</v>
+        <v>0.0003793</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0014296</v>
+        <v>0.001418</v>
       </c>
       <c r="E39" t="n">
-        <v>0.005594600000000001</v>
+        <v>0.0070255</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0221935</v>
+        <v>0.055791</v>
       </c>
       <c r="G39" t="n">
-        <v>0.007403925</v>
+        <v>0.01615345</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0003831</v>
+        <v>0.0003519</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0014085</v>
+        <v>0.0016463</v>
       </c>
       <c r="E40" t="n">
-        <v>0.006494700000000001</v>
+        <v>0.009249299999999998</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0368505</v>
+        <v>0.06626889999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0112842</v>
+        <v>0.0193791</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0003421</v>
+        <v>0.0003471</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0014808</v>
+        <v>0.0017493</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0067362</v>
+        <v>0.0102309</v>
       </c>
       <c r="F41" t="n">
-        <v>0.033001</v>
+        <v>0.0703699</v>
       </c>
       <c r="G41" t="n">
-        <v>0.010390025</v>
+        <v>0.0206743</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0002755</v>
+        <v>0.0002525</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0010742</v>
+        <v>0.0009961</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0041947</v>
+        <v>0.0042599</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0178922</v>
+        <v>0.017268</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00585915</v>
+        <v>0.005694125</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0004483999999999999</v>
+        <v>0.0003848</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0021871</v>
+        <v>0.0019412</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0108363</v>
+        <v>0.0123586</v>
       </c>
       <c r="F43" t="n">
-        <v>0.062236</v>
+        <v>0.08455599999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01892695</v>
+        <v>0.02481015</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003462</v>
+        <v>0.0002564000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007460999999999999</v>
+        <v>0.0008865999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0024127</v>
+        <v>0.0023377</v>
       </c>
       <c r="F44" t="n">
-        <v>0.008991099999999998</v>
+        <v>0.0076418</v>
       </c>
       <c r="G44" t="n">
-        <v>0.003124024999999999</v>
+        <v>0.002780625</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0003279</v>
+        <v>0.0002978</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0010974</v>
+        <v>0.0007859</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0030093</v>
+        <v>0.0024645</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0111732</v>
+        <v>0.0104706</v>
       </c>
       <c r="G45" t="n">
-        <v>0.00390195</v>
+        <v>0.0035047</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0002713</v>
+        <v>0.0002502</v>
       </c>
       <c r="D46" t="n">
-        <v>0.000924</v>
+        <v>0.0008561</v>
       </c>
       <c r="E46" t="n">
-        <v>0.002649</v>
+        <v>0.0026757</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0104546</v>
+        <v>0.0101007</v>
       </c>
       <c r="G46" t="n">
-        <v>0.003574725</v>
+        <v>0.003470675</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003829</v>
+        <v>0.000434</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0008588000000000001</v>
+        <v>0.0013292</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0027321</v>
+        <v>0.003906200000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0102487</v>
+        <v>0.0142128</v>
       </c>
       <c r="G47" t="n">
-        <v>0.003555625</v>
+        <v>0.004970550000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0003747</v>
+        <v>0.0003773</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0015609</v>
+        <v>0.0018223</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0068438</v>
+        <v>0.0104343</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0335948</v>
+        <v>0.07089809999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01059355</v>
+        <v>0.020883</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.000351</v>
+        <v>0.0003272</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0011243</v>
+        <v>0.0008252000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0031106</v>
+        <v>0.0026913</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0111645</v>
+        <v>0.0105714</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0039376</v>
+        <v>0.003603775</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1813,13 @@
         <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="G4" t="n">
-        <v>92.25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -1932,19 +1932,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="10">
@@ -2035,16 +2035,16 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>14.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="14">
@@ -2063,13 +2063,13 @@
         <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G14" t="n">
-        <v>92.5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15">
@@ -2088,13 +2088,13 @@
         <v>48</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G15" t="n">
-        <v>90.25</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="16">
@@ -2185,16 +2185,16 @@
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>23.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="20">
@@ -2282,19 +2282,19 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>11</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
         <v>14</v>
       </c>
-      <c r="D23" t="n">
-        <v>15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>15</v>
-      </c>
-      <c r="F23" t="n">
-        <v>15</v>
-      </c>
       <c r="G23" t="n">
-        <v>14.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2307,19 +2307,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G24" t="n">
-        <v>90.25</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="25">
@@ -2332,19 +2332,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" t="n">
         <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
         <v>192</v>
       </c>
       <c r="G25" t="n">
-        <v>90.25</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="26">
@@ -2438,13 +2438,13 @@
         <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>14.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -2466,10 +2466,10 @@
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>13.75</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="31">
@@ -2488,13 +2488,13 @@
         <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F31" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G31" t="n">
-        <v>90.75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="32">
@@ -2532,19 +2532,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>22.25</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="34">
@@ -2613,13 +2613,13 @@
         <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="37">
@@ -2632,19 +2632,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G37" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="38">
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>14.75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
         <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>14</v>
@@ -2732,19 +2732,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E41" t="n">
         <v>97</v>
       </c>
       <c r="F41" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G41" t="n">
-        <v>90.75</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="42">
@@ -2785,16 +2785,16 @@
         <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -2807,19 +2807,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
         <v>24</v>
@@ -2844,7 +2844,7 @@
         <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>22.75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F47" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G47" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="48">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
@@ -2919,7 +2919,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="49">
@@ -2932,19 +2932,19 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="n">
         <v>14</v>
       </c>
-      <c r="D49" t="n">
-        <v>15</v>
-      </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>14.75</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3061,16 +3061,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D4" t="n">
-        <v>54.87005768508881</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E4" t="n">
-        <v>110.3259018078045</v>
+        <v>106.3259018078045</v>
       </c>
       <c r="F4" t="n">
-        <v>226.5096679918781</v>
+        <v>214.0660171779821</v>
       </c>
       <c r="G4" t="n">
-        <v>104.6083873865323</v>
+        <v>100.2903679018718</v>
       </c>
     </row>
     <row r="5">
@@ -3183,19 +3183,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.72792206135786</v>
+        <v>28.14213562373095</v>
       </c>
       <c r="D9" t="n">
-        <v>55.69848480983499</v>
+        <v>57.45584412271571</v>
       </c>
       <c r="E9" t="n">
-        <v>110.3259018078045</v>
+        <v>113.4974746830583</v>
       </c>
       <c r="F9" t="n">
-        <v>222.0660171779821</v>
+        <v>230.4091629284898</v>
       </c>
       <c r="G9" t="n">
-        <v>103.7045814642449</v>
+        <v>107.3761543394987</v>
       </c>
     </row>
     <row r="10">
@@ -3286,16 +3286,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D13" t="n">
-        <v>53.00865358333435</v>
+        <v>52.18022645858817</v>
       </c>
       <c r="E13" t="n">
-        <v>105.8051828191882</v>
+        <v>101.1647927692761</v>
       </c>
       <c r="F13" t="n">
-        <v>213.5856092072074</v>
+        <v>203.5899290720917</v>
       </c>
       <c r="G13" t="n">
-        <v>99.62978514978414</v>
+        <v>95.76366082234064</v>
       </c>
     </row>
     <row r="14">
@@ -3314,13 +3314,13 @@
         <v>54.87005768508881</v>
       </c>
       <c r="E14" t="n">
-        <v>111.4974746830583</v>
+        <v>106.3259018078045</v>
       </c>
       <c r="F14" t="n">
-        <v>225.9238815542512</v>
+        <v>214.8944443027283</v>
       </c>
       <c r="G14" t="n">
-        <v>104.754833995939</v>
+        <v>100.7045814642449</v>
       </c>
     </row>
     <row r="15">
@@ -3339,13 +3339,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E15" t="n">
-        <v>109.254833995939</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="F15" t="n">
-        <v>218.7523086789974</v>
+        <v>213.5807358037436</v>
       </c>
       <c r="G15" t="n">
-        <v>102.1941738241592</v>
+        <v>100.754833995939</v>
       </c>
     </row>
     <row r="16">
@@ -3436,16 +3436,16 @@
         <v>25.31370849898476</v>
       </c>
       <c r="D19" t="n">
-        <v>54.04163056034262</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E19" t="n">
-        <v>108.6690475583121</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="F19" t="n">
-        <v>217.9238815542512</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G19" t="n">
-        <v>101.4870670429727</v>
+        <v>98.81549416771887</v>
       </c>
     </row>
     <row r="20">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.11969498940653</v>
+        <v>26.30713578936527</v>
       </c>
       <c r="D23" t="n">
-        <v>53.00865358333435</v>
+        <v>53.61158258374464</v>
       </c>
       <c r="E23" t="n">
-        <v>105.8051828191882</v>
+        <v>105.7349061791382</v>
       </c>
       <c r="F23" t="n">
-        <v>210.6548226779546</v>
+        <v>212.5135348331762</v>
       </c>
       <c r="G23" t="n">
-        <v>98.89708851747093</v>
+        <v>99.54178984635607</v>
       </c>
     </row>
     <row r="24">
@@ -3558,19 +3558,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.72792206135786</v>
+        <v>27.31370849898476</v>
       </c>
       <c r="D24" t="n">
-        <v>54.87005768508881</v>
+        <v>56.62741699796952</v>
       </c>
       <c r="E24" t="n">
-        <v>111.7401153701776</v>
+        <v>112.6690475583121</v>
       </c>
       <c r="F24" t="n">
-        <v>221.2375900532359</v>
+        <v>228.7523086789974</v>
       </c>
       <c r="G24" t="n">
-        <v>103.6439212924651</v>
+        <v>106.3406204335659</v>
       </c>
     </row>
     <row r="25">
@@ -3583,19 +3583,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.72792206135786</v>
+        <v>26.14213562373095</v>
       </c>
       <c r="D25" t="n">
         <v>54.04163056034262</v>
       </c>
       <c r="E25" t="n">
-        <v>109.254833995939</v>
+        <v>110.3259018078045</v>
       </c>
       <c r="F25" t="n">
-        <v>218.7523086789974</v>
+        <v>221.2375900532359</v>
       </c>
       <c r="G25" t="n">
-        <v>102.1941738241592</v>
+        <v>102.9368145112785</v>
       </c>
     </row>
     <row r="26">
@@ -3686,16 +3686,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D29" t="n">
-        <v>52.88838368210894</v>
+        <v>53.12892348455978</v>
       </c>
       <c r="E29" t="n">
-        <v>105.3137170479438</v>
+        <v>101.1647927692761</v>
       </c>
       <c r="F29" t="n">
-        <v>212.7803199337219</v>
+        <v>203.5899290720917</v>
       </c>
       <c r="G29" t="n">
-        <v>99.27552891329529</v>
+        <v>96.00083507883355</v>
       </c>
     </row>
     <row r="30">
@@ -3711,16 +3711,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D30" t="n">
-        <v>51.93968665613734</v>
+        <v>52.02551404151253</v>
       </c>
       <c r="E30" t="n">
-        <v>104.0707552199418</v>
+        <v>104.0026108698811</v>
       </c>
       <c r="F30" t="n">
-        <v>208.1469038539547</v>
+        <v>202.0378089703209</v>
       </c>
       <c r="G30" t="n">
-        <v>97.56926017986011</v>
+        <v>96.04640721778026</v>
       </c>
     </row>
     <row r="31">
@@ -3736,16 +3736,16 @@
         <v>26.72792206135786</v>
       </c>
       <c r="D31" t="n">
-        <v>54.87005768508881</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="E31" t="n">
-        <v>110.9116882454314</v>
+        <v>107.1543289325507</v>
       </c>
       <c r="F31" t="n">
-        <v>223.2375900532359</v>
+        <v>216.8944443027283</v>
       </c>
       <c r="G31" t="n">
-        <v>103.9368145112785</v>
+        <v>101.2045814642449</v>
       </c>
     </row>
     <row r="32">
@@ -3783,19 +3783,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.31370849898476</v>
+        <v>26.48528137423857</v>
       </c>
       <c r="D33" t="n">
-        <v>52.04163056034262</v>
+        <v>54.38477631085023</v>
       </c>
       <c r="E33" t="n">
-        <v>105.4974746830583</v>
+        <v>110.1837661840736</v>
       </c>
       <c r="F33" t="n">
         <v>212.4091629284898</v>
       </c>
       <c r="G33" t="n">
-        <v>98.81549416771887</v>
+        <v>100.8657466994131</v>
       </c>
     </row>
     <row r="34">
@@ -3861,16 +3861,16 @@
         <v>24.77927174436484</v>
       </c>
       <c r="D36" t="n">
-        <v>53.34219364008838</v>
+        <v>51.68533939059601</v>
       </c>
       <c r="E36" t="n">
-        <v>107.010883072478</v>
+        <v>104.7848923435651</v>
       </c>
       <c r="F36" t="n">
-        <v>214.3797191027945</v>
+        <v>210.9839982495033</v>
       </c>
       <c r="G36" t="n">
-        <v>99.87801688993142</v>
+        <v>98.05837543200732</v>
       </c>
     </row>
     <row r="37">
@@ -3886,16 +3886,16 @@
         <v>25.31370849898476</v>
       </c>
       <c r="D37" t="n">
-        <v>54.04163056034262</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E37" t="n">
-        <v>108.6690475583121</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="F37" t="n">
-        <v>217.9238815542512</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G37" t="n">
-        <v>101.4870670429727</v>
+        <v>98.81549416771887</v>
       </c>
     </row>
     <row r="38">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26.11969498940653</v>
+        <v>26.30713578936527</v>
       </c>
       <c r="D39" t="n">
-        <v>52.88838368210894</v>
+        <v>53.5704146322387</v>
       </c>
       <c r="E39" t="n">
-        <v>105.0360348523933</v>
+        <v>105.5523625471808</v>
       </c>
       <c r="F39" t="n">
-        <v>209.8495334044691</v>
+        <v>212.228582981152</v>
       </c>
       <c r="G39" t="n">
-        <v>98.47341173209446</v>
+        <v>99.41462398748419</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>26.11969498940653</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D40" t="n">
-        <v>51.93968665613734</v>
+        <v>52.02551404151253</v>
       </c>
       <c r="E40" t="n">
-        <v>104.0707552199418</v>
+        <v>104.2495560744203</v>
       </c>
       <c r="F40" t="n">
         <v>208.1469038539547</v>
       </c>
       <c r="G40" t="n">
-        <v>97.56926017986011</v>
+        <v>97.30031142856308</v>
       </c>
     </row>
     <row r="41">
@@ -3983,19 +3983,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>26.72792206135786</v>
+        <v>26.14213562373095</v>
       </c>
       <c r="D41" t="n">
-        <v>54.87005768508881</v>
+        <v>55.45584412271571</v>
       </c>
       <c r="E41" t="n">
-        <v>110.9116882454314</v>
+        <v>116.7106781186548</v>
       </c>
       <c r="F41" t="n">
-        <v>223.2375900532359</v>
+        <v>239.7645019878172</v>
       </c>
       <c r="G41" t="n">
-        <v>103.9368145112785</v>
+        <v>109.5182899632296</v>
       </c>
     </row>
     <row r="42">
@@ -4036,16 +4036,16 @@
         <v>26.11969498940653</v>
       </c>
       <c r="D43" t="n">
-        <v>52.88838368210894</v>
+        <v>52.05995655736275</v>
       </c>
       <c r="E43" t="n">
-        <v>105.481659072179</v>
+        <v>100.8138071241291</v>
       </c>
       <c r="F43" t="n">
-        <v>209.8495334044691</v>
+        <v>203.1681082487978</v>
       </c>
       <c r="G43" t="n">
-        <v>98.58481778704089</v>
+        <v>95.54039172992404</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24.77927174436484</v>
+        <v>26.30713578936527</v>
       </c>
       <c r="D44" t="n">
-        <v>50.97275705110279</v>
+        <v>53.26476041720318</v>
       </c>
       <c r="E44" t="n">
-        <v>102.4141455182377</v>
+        <v>106.3726311528253</v>
       </c>
       <c r="F44" t="n">
-        <v>206.0146711190602</v>
+        <v>203.8956733465899</v>
       </c>
       <c r="G44" t="n">
-        <v>96.04521135819138</v>
+        <v>97.46005017649594</v>
       </c>
     </row>
     <row r="45">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>26.72792206135786</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D45" t="n">
         <v>54.04163056034262</v>
@@ -4095,7 +4095,7 @@
         <v>217.9238815542512</v>
       </c>
       <c r="G45" t="n">
-        <v>101.8406204335659</v>
+        <v>101.4870670429727</v>
       </c>
     </row>
     <row r="46">
@@ -4136,16 +4136,16 @@
         <v>24.77927174436484</v>
       </c>
       <c r="D47" t="n">
-        <v>53.34219364008838</v>
+        <v>51.34219364008838</v>
       </c>
       <c r="E47" t="n">
-        <v>107.9564652188189</v>
+        <v>103.8393101972242</v>
       </c>
       <c r="F47" t="n">
-        <v>216.4987168752647</v>
+        <v>208.865000477033</v>
       </c>
       <c r="G47" t="n">
-        <v>100.6441618696342</v>
+        <v>97.2064440146776</v>
       </c>
     </row>
     <row r="48">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26.11969498940653</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D48" t="n">
-        <v>52.88838368210894</v>
+        <v>52.22495672299706</v>
       </c>
       <c r="E48" t="n">
-        <v>105.481659072179</v>
+        <v>107.4487397890024</v>
       </c>
       <c r="F48" t="n">
-        <v>209.8495334044691</v>
+        <v>213.2740286294842</v>
       </c>
       <c r="G48" t="n">
-        <v>98.58481778704089</v>
+        <v>99.43174922146214</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26.11969498940653</v>
+        <v>24.77927174436484</v>
       </c>
       <c r="D49" t="n">
-        <v>53.34219364008838</v>
+        <v>52.68385384080047</v>
       </c>
       <c r="E49" t="n">
-        <v>106.7346615986908</v>
+        <v>105.0764971128567</v>
       </c>
       <c r="F49" t="n">
-        <v>214.2427637751643</v>
+        <v>210.6986013237075</v>
       </c>
       <c r="G49" t="n">
-        <v>100.1098285008375</v>
+        <v>98.30955600543238</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F4" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="G4" t="n">
-        <v>212.25</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E9" t="n">
-        <v>226</v>
+        <v>370</v>
       </c>
       <c r="F9" t="n">
-        <v>539</v>
+        <v>972</v>
       </c>
       <c r="G9" t="n">
-        <v>216.5</v>
+        <v>368.75</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F13" t="n">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="G13" t="n">
-        <v>212.25</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F14" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="G14" t="n">
-        <v>217.25</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15">
@@ -4584,19 +4584,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F15" t="n">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="G15" t="n">
-        <v>216.75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>11</v>
@@ -4696,7 +4696,7 @@
         <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>10.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E23" t="n">
-        <v>226</v>
+        <v>370</v>
       </c>
       <c r="F23" t="n">
-        <v>539</v>
+        <v>972</v>
       </c>
       <c r="G23" t="n">
-        <v>216.5</v>
+        <v>368.75</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>198</v>
+        <v>352</v>
       </c>
       <c r="F24" t="n">
-        <v>497</v>
+        <v>1062</v>
       </c>
       <c r="G24" t="n">
-        <v>197.25</v>
+        <v>384.75</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F25" t="n">
-        <v>472</v>
+        <v>422</v>
       </c>
       <c r="G25" t="n">
-        <v>191.25</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E29" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F29" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="G29" t="n">
-        <v>217.25</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E30" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F30" t="n">
-        <v>573</v>
+        <v>437</v>
       </c>
       <c r="G30" t="n">
-        <v>216.75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E31" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="F31" t="n">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="G31" t="n">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17</v>
+      </c>
+      <c r="F33" t="n">
         <v>13</v>
       </c>
-      <c r="E33" t="n">
-        <v>13</v>
-      </c>
-      <c r="F33" t="n">
-        <v>14</v>
-      </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="34">
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
         <v>11</v>
@@ -5121,7 +5121,7 @@
         <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>10.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -5134,19 +5134,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
+        <v>13</v>
+      </c>
+      <c r="E37" t="n">
         <v>15</v>
       </c>
-      <c r="E37" t="n">
-        <v>16</v>
-      </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>14.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="38">
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
-        <v>198</v>
+        <v>352</v>
       </c>
       <c r="F39" t="n">
-        <v>497</v>
+        <v>1062</v>
       </c>
       <c r="G39" t="n">
-        <v>197.25</v>
+        <v>384.75</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E40" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F40" t="n">
-        <v>472</v>
+        <v>422</v>
       </c>
       <c r="G40" t="n">
-        <v>191.25</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E41" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F41" t="n">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="G41" t="n">
-        <v>185.75</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D43" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E43" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="F43" t="n">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="G43" t="n">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44">
@@ -5309,19 +5309,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" t="n">
         <v>13</v>
       </c>
-      <c r="E44" t="n">
-        <v>13</v>
-      </c>
-      <c r="F44" t="n">
-        <v>14</v>
-      </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="45">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -5384,19 +5384,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
+        <v>13</v>
+      </c>
+      <c r="E47" t="n">
         <v>15</v>
       </c>
-      <c r="E47" t="n">
-        <v>16</v>
-      </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>14.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E48" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F48" t="n">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="G48" t="n">
-        <v>185.75</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="49">
@@ -5434,19 +5434,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F4" t="n">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="G4" t="n">
-        <v>367.75</v>
+        <v>356.5</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
         <v>91</v>
       </c>
       <c r="E9" t="n">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="F9" t="n">
-        <v>979</v>
+        <v>1631</v>
       </c>
       <c r="G9" t="n">
-        <v>357.25</v>
+        <v>529.75</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F13" t="n">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="G13" t="n">
-        <v>367.75</v>
+        <v>356.5</v>
       </c>
     </row>
     <row r="14">
@@ -5810,19 +5810,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F14" t="n">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="G14" t="n">
-        <v>365.5</v>
+        <v>361.5</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="F15" t="n">
-        <v>994</v>
+        <v>1228</v>
       </c>
       <c r="G15" t="n">
-        <v>353.5</v>
+        <v>419.75</v>
       </c>
     </row>
     <row r="16">
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>25.5</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D23" t="n">
         <v>91</v>
       </c>
       <c r="E23" t="n">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="F23" t="n">
-        <v>979</v>
+        <v>1631</v>
       </c>
       <c r="G23" t="n">
-        <v>357.25</v>
+        <v>529.75</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>980</v>
+        <v>1796</v>
       </c>
       <c r="G24" t="n">
-        <v>358.25</v>
+        <v>554.75</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E25" t="n">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="F25" t="n">
-        <v>1313</v>
+        <v>1513</v>
       </c>
       <c r="G25" t="n">
-        <v>446.5</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26">
@@ -6185,19 +6185,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E29" t="n">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F29" t="n">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="G29" t="n">
-        <v>365.5</v>
+        <v>361.5</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E30" t="n">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="F30" t="n">
-        <v>994</v>
+        <v>1228</v>
       </c>
       <c r="G30" t="n">
-        <v>353.5</v>
+        <v>419.75</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D31" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E31" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="F31" t="n">
-        <v>1052</v>
+        <v>1274</v>
       </c>
       <c r="G31" t="n">
-        <v>371.75</v>
+        <v>428.75</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F33" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>27.25</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="34">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G36" t="n">
-        <v>25.5</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="37">
@@ -6385,19 +6385,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E37" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F37" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G37" t="n">
-        <v>29.25</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E39" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F39" t="n">
-        <v>980</v>
+        <v>1796</v>
       </c>
       <c r="G39" t="n">
-        <v>358.25</v>
+        <v>554.75</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E40" t="n">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="F40" t="n">
-        <v>1313</v>
+        <v>1513</v>
       </c>
       <c r="G40" t="n">
-        <v>446.5</v>
+        <v>508</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E41" t="n">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="F41" t="n">
-        <v>1297</v>
+        <v>1529</v>
       </c>
       <c r="G41" t="n">
-        <v>444.75</v>
+        <v>516</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E43" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="F43" t="n">
-        <v>1052</v>
+        <v>1274</v>
       </c>
       <c r="G43" t="n">
-        <v>371.75</v>
+        <v>428.75</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F44" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G44" t="n">
-        <v>27.25</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="45">
@@ -6588,16 +6588,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E45" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G45" t="n">
-        <v>32.25</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="46">
@@ -6635,19 +6635,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D47" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G47" t="n">
-        <v>29.25</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D48" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E48" t="n">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="F48" t="n">
-        <v>1297</v>
+        <v>1529</v>
       </c>
       <c r="G48" t="n">
-        <v>444.75</v>
+        <v>516</v>
       </c>
     </row>
     <row r="49">
@@ -6688,16 +6688,16 @@
         <v>22</v>
       </c>
       <c r="D49" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E49" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G49" t="n">
-        <v>32.25</v>
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>
@@ -6814,16 +6814,16 @@
         <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
         <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>20.5</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="5">
@@ -6936,19 +6936,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="10">
@@ -7039,16 +7039,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="14">
@@ -7064,16 +7064,16 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>21.25</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="15">
@@ -7089,16 +7089,16 @@
         <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>22.25</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="16">
@@ -7189,16 +7189,16 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>15.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="20">
@@ -7286,19 +7286,19 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
         <v>12</v>
       </c>
-      <c r="D23" t="n">
-        <v>13</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13</v>
-      </c>
-      <c r="F23" t="n">
-        <v>13</v>
-      </c>
       <c r="G23" t="n">
-        <v>12.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="24">
@@ -7311,19 +7311,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>20.75</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="25">
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
         <v>22</v>
@@ -7345,10 +7345,10 @@
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="26">
@@ -7442,13 +7442,13 @@
         <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -7470,10 +7470,10 @@
         <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>11.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="31">
@@ -7489,16 +7489,16 @@
         <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>19.25</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="32">
@@ -7536,19 +7536,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
         <v>14</v>
       </c>
       <c r="G33" t="n">
-        <v>13.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="34">
@@ -7617,13 +7617,13 @@
         <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37">
@@ -7639,16 +7639,16 @@
         <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G37" t="n">
-        <v>15.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="38">
@@ -7686,19 +7686,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G39" t="n">
-        <v>12.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="40">
@@ -7711,13 +7711,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
         <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" t="n">
         <v>12</v>
@@ -7736,19 +7736,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -7789,16 +7789,16 @@
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G43" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -7811,19 +7811,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
         <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
         <v>16</v>
@@ -7848,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="n">
-        <v>15.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="46">
@@ -7886,19 +7886,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="48">
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
         <v>13</v>
@@ -7923,7 +7923,7 @@
         <v>13</v>
       </c>
       <c r="G48" t="n">
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="49">
@@ -7936,19 +7936,19 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="n">
         <v>12</v>
       </c>
-      <c r="D49" t="n">
-        <v>13</v>
-      </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>12.75</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D4" t="n">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E4" t="n">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>552</v>
+        <v>731</v>
       </c>
       <c r="E9" t="n">
-        <v>1518</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D13" t="n">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E13" t="n">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="E14" t="n">
-        <v>1618</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="15">
@@ -8246,16 +8246,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C15" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D15" t="n">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="E15" t="n">
-        <v>1567</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C23" t="n">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D23" t="n">
-        <v>552</v>
+        <v>731</v>
       </c>
       <c r="E23" t="n">
-        <v>1518</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D24" t="n">
-        <v>520</v>
+        <v>671</v>
       </c>
       <c r="E24" t="n">
-        <v>1477</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D25" t="n">
-        <v>544</v>
+        <v>588</v>
       </c>
       <c r="E25" t="n">
-        <v>1785</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C29" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D29" t="n">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="E29" t="n">
-        <v>1618</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="30">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C30" t="n">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="D30" t="n">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="E30" t="n">
-        <v>1567</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D31" t="n">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="E31" t="n">
-        <v>1563</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E33" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C36" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D36" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E36" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C37" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E37" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D39" t="n">
-        <v>520</v>
+        <v>671</v>
       </c>
       <c r="E39" t="n">
-        <v>1477</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C40" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D40" t="n">
-        <v>544</v>
+        <v>588</v>
       </c>
       <c r="E40" t="n">
-        <v>1785</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="41">
@@ -8743,13 +8743,13 @@
         <v>55</v>
       </c>
       <c r="C41" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D41" t="n">
-        <v>560</v>
+        <v>628</v>
       </c>
       <c r="E41" t="n">
-        <v>1732</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C43" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D43" t="n">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="E43" t="n">
-        <v>1563</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C44" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E44" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E45" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E47" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -8876,13 +8876,13 @@
         <v>55</v>
       </c>
       <c r="C48" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D48" t="n">
-        <v>560</v>
+        <v>628</v>
       </c>
       <c r="E48" t="n">
-        <v>1732</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="49">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C49" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
